--- a/mobile_legends_heroes_updated.xlsx
+++ b/mobile_legends_heroes_updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\__Projects\AI Projects\mlbb-drafter-v2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D51F5FA-A04B-4258-A0A4-BF2FC8FE27C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42001A9-D510-472C-A218-AFE56AB36387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2051" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="636">
   <si>
     <t>id</t>
   </si>
@@ -1767,6 +1767,186 @@
   </si>
   <si>
     <t>hanzo</t>
+  </si>
+  <si>
+    <t>High-damage charge combos punish sustained-mobility heroes.</t>
+  </si>
+  <si>
+    <t>Mobility skill and CC chain disrupt dash-reliant divers.</t>
+  </si>
+  <si>
+    <t>Continuous slow and movement speed kites sustain-melee heroes.</t>
+  </si>
+  <si>
+    <t>HP-stacking frontliner absorbs and neutralizes burst attempts.</t>
+  </si>
+  <si>
+    <t>Passive deals percent Max HP True Damage shredding tank HP pools.</t>
+  </si>
+  <si>
+    <t>Passive retaliation punishes physical attackers, stacking with taunt.</t>
+  </si>
+  <si>
+    <t>Bouncing Ball and Charging Roar interrupt high-mobility assassins.</t>
+  </si>
+  <si>
+    <t>Skill 2 knocks up enemies dashing through Khufra.</t>
+  </si>
+  <si>
+    <t>Bush-regen burst punishes burst heroes who overextend.</t>
+  </si>
+  <si>
+    <t>Point-and-click airborne kills squishy assassin divers.</t>
+  </si>
+  <si>
+    <t>Lock-on ring ultimate deletes Hanzo before he can escape.</t>
+  </si>
+  <si>
+    <t>Slow and root deny Harley teleport-in burst window. Prevents burst kill of Harley</t>
+  </si>
+  <si>
+    <t>Passive converts enemy shields into her own health.</t>
+  </si>
+  <si>
+    <t>Passive reduces enemy healing and shield output by 50%.</t>
+  </si>
+  <si>
+    <t>Dark Form converts Magic Pen into percent HP magic damage.</t>
+  </si>
+  <si>
+    <t>Skill 2 shreds up to 75% Physical Defense for early trade wins.</t>
+  </si>
+  <si>
+    <t>Defense shred negates sustain-tank regen.</t>
+  </si>
+  <si>
+    <t>Ultimate disables dash, blink, and mobility skills.</t>
+  </si>
+  <si>
+    <t>King Calling denies wall-climbing and continuous mobility.</t>
+  </si>
+  <si>
+    <t>Suppression drags blink divers into the team.</t>
+  </si>
+  <si>
+    <t>Passive thorns reflect Max HP damage at attack-speed heroes.</t>
+  </si>
+  <si>
+    <t>Thorned retaliation punishes sustained marksman output.</t>
+  </si>
+  <si>
+    <t>Skill 2 Purify removes point-and-click stuns.</t>
+  </si>
+  <si>
+    <t>Built-in CC cleanse denies hard-engage ults.</t>
+  </si>
+  <si>
+    <t>Continuous knockbacks keep melee divers at distance.</t>
+  </si>
+  <si>
+    <t>Burning damage kites sustain brawlers before they close.</t>
+  </si>
+  <si>
+    <t>Skill 2 grants full CC immunity during execution.</t>
+  </si>
+  <si>
+    <t>CC immunity ignores multi-target crowd control.</t>
+  </si>
+  <si>
+    <t>Ultimate knockback interrupts channeled area ults.</t>
+  </si>
+  <si>
+    <t>Move-while-attacking circles directional skillshots.</t>
+  </si>
+  <si>
+    <t>Ultimate hits clones triggering Demon Hunter Sword stacks.</t>
+  </si>
+  <si>
+    <t>Stealth range and True Damage poke down short-range MMs.</t>
+  </si>
+  <si>
+    <t>Invisible repositioning punishes sustained DPS heroes.</t>
+  </si>
+  <si>
+    <t>Converts Physical Pen into Magic Pen bypassing armor.</t>
+  </si>
+  <si>
+    <t>Passive mark locking executes squishy backliners.</t>
+  </si>
+  <si>
+    <t>Physical burst deletes immobile mages.</t>
+  </si>
+  <si>
+    <t>Point-and-click stun chain freezes fast assassins.</t>
+  </si>
+  <si>
+    <t>AoE freeze punishes high-mobility divers.</t>
+  </si>
+  <si>
+    <t>Umbrella purge removes debuffs and grants dash.</t>
+  </si>
+  <si>
+    <t>Nightmarish Spawn disjoints targeted burst spells.</t>
+  </si>
+  <si>
+    <t>Spawn body-blocks point-and-click control.</t>
+  </si>
+  <si>
+    <t>Skill 1 grants CC immunity on initiation.</t>
+  </si>
+  <si>
+    <t>CC immunity lets her dive through disengage blinks.</t>
+  </si>
+  <si>
+    <t>True Damage melts sustain tanks before they reach backline.</t>
+  </si>
+  <si>
+    <t>Skill 1 poke burns through shields from safe distance.</t>
+  </si>
+  <si>
+    <t>Teleport and lock-on ultimate dive static mages.</t>
+  </si>
+  <si>
+    <t>Passive damage reduction wins long trades vs sustained DPS.</t>
+  </si>
+  <si>
+    <t>Skill 1 True Damage ignores armor and lifesteal.</t>
+  </si>
+  <si>
+    <t>True Damage bypasses shield mechanics.</t>
+  </si>
+  <si>
+    <t>Lava True Damage and regen out-sustain basic-attack brawlers.</t>
+  </si>
+  <si>
+    <t>Ultimate links Gloo clones to chain entire team.</t>
+  </si>
+  <si>
+    <t>Black Dragon bypasses frontliners to hit backline.</t>
+  </si>
+  <si>
+    <t>Flight and CC immunity dive immobile mages.</t>
+  </si>
+  <si>
+    <t>Passive grants Skill 2 dash resets vs mobile heroes.</t>
+  </si>
+  <si>
+    <t>Skill 2 grants CC immunity and reflects stuns.</t>
+  </si>
+  <si>
+    <t>Passive causes summons to explode for chain AoE.</t>
+  </si>
+  <si>
+    <t>Summons create extra hitboxes for Skill 1 resets.</t>
+  </si>
+  <si>
+    <t>Extra targets grant cable energy and stacks.</t>
+  </si>
+  <si>
+    <t>Three HP bars absorb burst combos, leaving Masha alive.</t>
+  </si>
+  <si>
+    <t>HP bars absorb point-and-click burst rotations.</t>
   </si>
 </sst>
 </file>
@@ -10008,7 +10188,9 @@
       <c r="E51" s="4">
         <v>-12</v>
       </c>
-      <c r="F51" s="3"/>
+      <c r="F51" s="3" t="s">
+        <v>576</v>
+      </c>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
@@ -10026,7 +10208,9 @@
       <c r="E52" s="4">
         <v>-10</v>
       </c>
-      <c r="F52" s="3"/>
+      <c r="F52" s="3" t="s">
+        <v>577</v>
+      </c>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
@@ -10044,7 +10228,9 @@
       <c r="E53" s="4">
         <v>-7</v>
       </c>
-      <c r="F53" s="3"/>
+      <c r="F53" s="3" t="s">
+        <v>578</v>
+      </c>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
@@ -10062,7 +10248,9 @@
       <c r="E54" s="4">
         <v>-12</v>
       </c>
-      <c r="F54" s="3"/>
+      <c r="F54" s="3" t="s">
+        <v>579</v>
+      </c>
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
@@ -10080,7 +10268,9 @@
       <c r="E55" s="4">
         <v>20</v>
       </c>
-      <c r="F55" s="3"/>
+      <c r="F55" s="3" t="s">
+        <v>580</v>
+      </c>
     </row>
     <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
@@ -10098,7 +10288,9 @@
       <c r="E56" s="4">
         <v>-12</v>
       </c>
-      <c r="F56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>581</v>
+      </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
@@ -10116,7 +10308,9 @@
       <c r="E57" s="4">
         <v>-4</v>
       </c>
-      <c r="F57" s="3"/>
+      <c r="F57" s="3" t="s">
+        <v>582</v>
+      </c>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
@@ -10134,7 +10328,9 @@
       <c r="E58" s="4">
         <v>-5</v>
       </c>
-      <c r="F58" s="3"/>
+      <c r="F58" s="3" t="s">
+        <v>583</v>
+      </c>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
@@ -10152,7 +10348,9 @@
       <c r="E59" s="4">
         <v>-14</v>
       </c>
-      <c r="F59" s="3"/>
+      <c r="F59" s="3" t="s">
+        <v>584</v>
+      </c>
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
@@ -10170,7 +10368,9 @@
       <c r="E60" s="4">
         <v>-10</v>
       </c>
-      <c r="F60" s="3"/>
+      <c r="F60" s="3" t="s">
+        <v>585</v>
+      </c>
     </row>
     <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
@@ -10188,7 +10388,9 @@
       <c r="E61" s="4">
         <v>-20</v>
       </c>
-      <c r="F61" s="3"/>
+      <c r="F61" s="3" t="s">
+        <v>586</v>
+      </c>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
@@ -10206,382 +10408,969 @@
       <c r="E62" s="4">
         <v>-18</v>
       </c>
-      <c r="F62" s="3"/>
+      <c r="F62" s="3" t="s">
+        <v>587</v>
+      </c>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="4"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="3"/>
+      <c r="A63" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D63" s="4">
+        <v>12</v>
+      </c>
+      <c r="E63" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="4"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="3"/>
+      <c r="A64" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D64" s="4">
+        <v>14</v>
+      </c>
+      <c r="E64" s="4">
+        <v>-12</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>589</v>
+      </c>
     </row>
     <row r="65" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="4"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="3"/>
+      <c r="A65" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D65" s="4">
+        <v>14</v>
+      </c>
+      <c r="E65" s="4">
+        <v>-12</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>590</v>
+      </c>
     </row>
     <row r="66" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="4"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="3"/>
+      <c r="A66" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D66" s="4">
+        <v>12</v>
+      </c>
+      <c r="E66" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="67" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="4"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="3"/>
+      <c r="A67" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D67" s="4">
+        <v>10</v>
+      </c>
+      <c r="E67" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>592</v>
+      </c>
     </row>
     <row r="68" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="4"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="3"/>
+      <c r="A68" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D68" s="4">
+        <v>18</v>
+      </c>
+      <c r="E68" s="4">
+        <v>-20</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>593</v>
+      </c>
     </row>
     <row r="69" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="4"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="3"/>
+      <c r="A69" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D69" s="4">
+        <v>15</v>
+      </c>
+      <c r="E69" s="4">
+        <v>-18</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>594</v>
+      </c>
     </row>
     <row r="70" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="4"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="3"/>
+      <c r="A70" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D70" s="4">
+        <v>8</v>
+      </c>
+      <c r="E70" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>595</v>
+      </c>
     </row>
     <row r="71" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="4"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="3"/>
+      <c r="A71" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="4">
+        <v>12</v>
+      </c>
+      <c r="E71" s="4">
+        <v>-12</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>596</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="4"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="3"/>
+      <c r="A72" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D72" s="4">
+        <v>8</v>
+      </c>
+      <c r="E72" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>597</v>
+      </c>
     </row>
     <row r="73" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="4"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="3"/>
+      <c r="A73" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D73" s="4">
+        <v>10</v>
+      </c>
+      <c r="E73" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row r="74" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="4"/>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="3"/>
+      <c r="A74" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D74" s="4">
+        <v>8</v>
+      </c>
+      <c r="E74" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>599</v>
+      </c>
     </row>
     <row r="75" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="4"/>
+      <c r="A75" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B75" t="s">
+        <v>369</v>
+      </c>
+      <c r="C75" t="s">
+        <v>112</v>
+      </c>
+      <c r="D75">
+        <v>10</v>
+      </c>
+      <c r="E75">
+        <v>-12</v>
+      </c>
+      <c r="F75" t="s">
+        <v>600</v>
+      </c>
     </row>
     <row r="76" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="4"/>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="3"/>
+      <c r="A76" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D76" s="4">
+        <v>8</v>
+      </c>
+      <c r="E76" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>601</v>
+      </c>
     </row>
     <row r="77" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="4"/>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="3"/>
+      <c r="A77" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D77" s="4">
+        <v>8</v>
+      </c>
+      <c r="E77" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>602</v>
+      </c>
     </row>
     <row r="78" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="4"/>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="3"/>
+      <c r="A78" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D78" s="4">
+        <v>6</v>
+      </c>
+      <c r="E78" s="4">
+        <v>-6</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>603</v>
+      </c>
     </row>
     <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="4"/>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="3"/>
+      <c r="A79" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D79" s="4">
+        <v>8</v>
+      </c>
+      <c r="E79" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>604</v>
+      </c>
     </row>
     <row r="80" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="4"/>
-      <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="3"/>
+      <c r="A80" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D80" s="4">
+        <v>8</v>
+      </c>
+      <c r="E80" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>605</v>
+      </c>
     </row>
     <row r="81" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="4"/>
-      <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="3"/>
+      <c r="A81" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D81" s="4">
+        <v>14</v>
+      </c>
+      <c r="E81" s="4">
+        <v>-14</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>606</v>
+      </c>
     </row>
     <row r="82" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="4"/>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="3"/>
+      <c r="A82" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D82" s="4">
+        <v>8</v>
+      </c>
+      <c r="E82" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>607</v>
+      </c>
     </row>
     <row r="83" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="4"/>
-      <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="3"/>
+      <c r="A83" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D83" s="4">
+        <v>6</v>
+      </c>
+      <c r="E83" s="4">
+        <v>-6</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>608</v>
+      </c>
     </row>
     <row r="84" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="4"/>
-      <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="3"/>
+      <c r="A84" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D84" s="4">
+        <v>10</v>
+      </c>
+      <c r="E84" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>609</v>
+      </c>
     </row>
     <row r="85" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="4"/>
-      <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="3"/>
+      <c r="A85" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D85" s="4">
+        <v>8</v>
+      </c>
+      <c r="E85" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>610</v>
+      </c>
     </row>
     <row r="86" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="4"/>
-      <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="3"/>
+      <c r="A86" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D86" s="4">
+        <v>8</v>
+      </c>
+      <c r="E86" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>611</v>
+      </c>
     </row>
     <row r="87" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="4"/>
-      <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="3"/>
+      <c r="A87" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D87" s="4">
+        <v>10</v>
+      </c>
+      <c r="E87" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>612</v>
+      </c>
     </row>
     <row r="88" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="4"/>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="3"/>
+      <c r="A88" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D88" s="4">
+        <v>10</v>
+      </c>
+      <c r="E88" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="89" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="4"/>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="3"/>
+      <c r="A89" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D89" s="4">
+        <v>8</v>
+      </c>
+      <c r="E89" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>614</v>
+      </c>
     </row>
     <row r="90" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="4"/>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="3"/>
+      <c r="A90" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D90" s="4">
+        <v>8</v>
+      </c>
+      <c r="E90" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>615</v>
+      </c>
     </row>
     <row r="91" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="3"/>
+      <c r="A91" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D91" s="4">
+        <v>6</v>
+      </c>
+      <c r="E91" s="4">
+        <v>-6</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="92" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="3"/>
+      <c r="A92" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D92" s="4">
+        <v>8</v>
+      </c>
+      <c r="E92" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>617</v>
+      </c>
     </row>
     <row r="93" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="4"/>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="3"/>
+      <c r="A93" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D93" s="4">
+        <v>6</v>
+      </c>
+      <c r="E93" s="4">
+        <v>-6</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>618</v>
+      </c>
     </row>
     <row r="94" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="3"/>
+      <c r="A94" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D94" s="4">
+        <v>8</v>
+      </c>
+      <c r="E94" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>619</v>
+      </c>
     </row>
     <row r="95" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="3"/>
+      <c r="A95" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D95" s="4">
+        <v>6</v>
+      </c>
+      <c r="E95" s="4">
+        <v>-6</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="96" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="3"/>
+      <c r="A96" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D96" s="4">
+        <v>8</v>
+      </c>
+      <c r="E96" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="97" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="4"/>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="3"/>
+      <c r="A97" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D97" s="4">
+        <v>8</v>
+      </c>
+      <c r="E97" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="98" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="4"/>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="3"/>
+      <c r="A98" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D98" s="4">
+        <v>12</v>
+      </c>
+      <c r="E98" s="4">
+        <v>-12</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>623</v>
+      </c>
     </row>
     <row r="99" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="4"/>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="3"/>
+      <c r="A99" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D99" s="4">
+        <v>10</v>
+      </c>
+      <c r="E99" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>624</v>
+      </c>
     </row>
     <row r="100" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="4"/>
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="3"/>
+      <c r="A100" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D100" s="4">
+        <v>8</v>
+      </c>
+      <c r="E100" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>625</v>
+      </c>
     </row>
     <row r="101" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="4"/>
-      <c r="F101" s="3"/>
+      <c r="A101" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B101" t="s">
+        <v>374</v>
+      </c>
+      <c r="C101" t="s">
+        <v>274</v>
+      </c>
+      <c r="D101">
+        <v>16</v>
+      </c>
+      <c r="E101">
+        <v>-16</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>626</v>
+      </c>
     </row>
     <row r="102" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="4"/>
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="3"/>
+      <c r="A102" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D102" s="4">
+        <v>10</v>
+      </c>
+      <c r="E102" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>627</v>
+      </c>
     </row>
     <row r="103" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="4"/>
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
-      <c r="E103" s="4"/>
-      <c r="F103" s="3"/>
+      <c r="A103" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D103" s="4">
+        <v>10</v>
+      </c>
+      <c r="E103" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>628</v>
+      </c>
     </row>
     <row r="104" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="4"/>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="3"/>
+      <c r="A104" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D104" s="4">
+        <v>10</v>
+      </c>
+      <c r="E104" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>629</v>
+      </c>
     </row>
     <row r="105" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="4"/>
-      <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
-      <c r="D105" s="4"/>
-      <c r="E105" s="4"/>
-      <c r="F105" s="3"/>
+      <c r="A105" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D105" s="4">
+        <v>10</v>
+      </c>
+      <c r="E105" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>630</v>
+      </c>
     </row>
     <row r="106" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="4"/>
-      <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="4"/>
-      <c r="F106" s="3"/>
+      <c r="A106" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D106" s="4">
+        <v>14</v>
+      </c>
+      <c r="E106" s="4">
+        <v>-14</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>631</v>
+      </c>
     </row>
     <row r="107" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="4"/>
-      <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
-      <c r="F107" s="3"/>
+      <c r="A107" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D107" s="4">
+        <v>10</v>
+      </c>
+      <c r="E107" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>632</v>
+      </c>
     </row>
     <row r="108" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="4"/>
-      <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-      <c r="E108" s="4"/>
-      <c r="F108" s="3"/>
+      <c r="A108" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D108" s="4">
+        <v>10</v>
+      </c>
+      <c r="E108" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>633</v>
+      </c>
     </row>
     <row r="109" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="4"/>
-      <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
-      <c r="D109" s="4"/>
-      <c r="E109" s="4"/>
-      <c r="F109" s="3"/>
+      <c r="A109" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D109" s="4">
+        <v>8</v>
+      </c>
+      <c r="E109" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>634</v>
+      </c>
     </row>
     <row r="110" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="4"/>
-      <c r="B110" s="4"/>
-      <c r="C110" s="4"/>
-      <c r="D110" s="4"/>
-      <c r="E110" s="4"/>
-      <c r="F110" s="3"/>
+      <c r="A110" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D110" s="4">
+        <v>6</v>
+      </c>
+      <c r="E110" s="4">
+        <v>-6</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="111" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4"/>
@@ -22936,7 +23725,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>A190:B1189 A29:A128</xm:sqref>
+          <xm:sqref>A190:B1189 A29:A62 A111:A128</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000004000000}">
           <x14:formula1>
@@ -22945,7 +23734,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>C29:C128</xm:sqref>
+          <xm:sqref>C29:C62 C111:C128</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -30435,19 +31224,19 @@
       </c>
       <c r="Q51">
         <f t="shared" si="18"/>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="R51">
         <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A51&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q51)</f>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="S51">
         <f t="shared" si="19"/>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="T51">
         <f t="shared" si="20"/>
-        <v>3.0000051000000001</v>
+        <v>19.000005099999999</v>
       </c>
       <c r="U51" t="str">
         <f>Heroes!$M51</f>
@@ -30471,7 +31260,7 @@
       </c>
       <c r="Z51">
         <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A51)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A51)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A51)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A51)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A51)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE51" t="str">
         <f>Heroes!$R51</f>
@@ -34919,19 +35708,19 @@
       </c>
       <c r="Q89">
         <f t="shared" si="30"/>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="R89">
         <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A89&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q89)</f>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="S89">
         <f t="shared" si="31"/>
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="T89">
         <f t="shared" si="32"/>
-        <v>3.0000089000000001</v>
+        <v>19.000008900000001</v>
       </c>
       <c r="U89" t="str">
         <f>Heroes!$M89</f>
@@ -34955,7 +35744,7 @@
       </c>
       <c r="Z89">
         <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A89)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A89)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A89)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A89)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A89)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE89" t="str">
         <f>Heroes!$R89</f>

--- a/mobile_legends_heroes_updated.xlsx
+++ b/mobile_legends_heroes_updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\__Projects\AI Projects\mlbb-drafter-v2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42001A9-D510-472C-A218-AFE56AB36387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40940371-C781-4C74-B25C-03822E98B95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2255" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2335" uniqueCount="656">
   <si>
     <t>id</t>
   </si>
@@ -1947,6 +1947,66 @@
   </si>
   <si>
     <t>HP bars absorb point-and-click burst rotations.</t>
+  </si>
+  <si>
+    <t>Abyssal Pull ultimate drags and binds the entire enemy team, hard-countering global-dive engage comps before they can scatter.</t>
+  </si>
+  <si>
+    <t>Boulder Toss wall physically blocks dash/blink paths, denying clean engage routes for divers.</t>
+  </si>
+  <si>
+    <t>Passive AoE regeneration to the whole team blunts coordinated burst-kill attempts.</t>
+  </si>
+  <si>
+    <t>Ultimate bonds to an ally with heal-over-time and mitigation, denying burst execution windows on the carry.</t>
+  </si>
+  <si>
+    <t>Void Strike's true-damage proc ignores defense and lifesteal, wearing down sustain-heavy opponents over extended trades.</t>
+  </si>
+  <si>
+    <t>Passive true-damage marks stack up over a fight, shredding tank HP pools that scale purely on defense.</t>
+  </si>
+  <si>
+    <t>Ultimate copies an enemy mage's own ultimate, turning their signature burst tool directly against them.</t>
+  </si>
+  <si>
+    <t>Resonating Point's mark-and-dash chain lets her reposition through and punish melee divers who commit onto her.</t>
+  </si>
+  <si>
+    <t>Charge and grapple mechanics yank dash-committed divers off their intended path.</t>
+  </si>
+  <si>
+    <t>Illusion clone poke and true-damage marks whittle down squishy marksmen from range before they can retaliate.</t>
+  </si>
+  <si>
+    <t>Implosion's knock-up and displacement punish immobile backline mages who get caught out of position.</t>
+  </si>
+  <si>
+    <t>Mark-fueled movement speed and dash let him stick to and run down sustained-mobility divers.</t>
+  </si>
+  <si>
+    <t>Burst combo plus innate mobility deletes squishy marksmen before they can kite to safety.</t>
+  </si>
+  <si>
+    <t>Judgment of Talas execute damage scales off missing HP, punishing sustain heroes who try to outlast her in prolonged trades.</t>
+  </si>
+  <si>
+    <t>Passive stacking rewards prolonged engagements, letting him out-trade sustain-heavy opponents the longer a fight runs.</t>
+  </si>
+  <si>
+    <t>Passive slow-immunity and hybrid damage switching let her out-range and out-poke rival poke mages.</t>
+  </si>
+  <si>
+    <t>Totem zone denial and long-range traps contest space and out-position poke compositions.</t>
+  </si>
+  <si>
+    <t>Weapon-swap burst combo (Renner into Wesker) deletes low-HP mages before they can retaliate.</t>
+  </si>
+  <si>
+    <t>Zone-control burst outranges and out-damages rival poke mages contesting the same lane space.</t>
+  </si>
+  <si>
+    <t>Rapid-fire piercing shots delete squishy, immobile mages before they can complete their cast animation.</t>
   </si>
 </sst>
 </file>
@@ -2111,10 +2171,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9325,7 +9385,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:W1189"/>
+  <dimension ref="A1:W1190"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -9719,10 +9779,10 @@
         <v>112</v>
       </c>
       <c r="D29" s="4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E29" s="4">
-        <v>-25</v>
+        <v>-23</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>370</v>
@@ -9745,10 +9805,10 @@
         <v>89</v>
       </c>
       <c r="D30" s="4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E30" s="4">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>372</v>
@@ -9768,10 +9828,10 @@
         <v>86</v>
       </c>
       <c r="D31" s="4">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E31" s="4">
-        <v>-14</v>
+        <v>-23</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>373</v>
@@ -9837,10 +9897,10 @@
         <v>112</v>
       </c>
       <c r="D34" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E34" s="4">
-        <v>-18</v>
+        <v>-13</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>378</v>
@@ -9860,10 +9920,10 @@
         <v>89</v>
       </c>
       <c r="D35" s="4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E35" s="4">
-        <v>-15</v>
+        <v>-13</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>379</v>
@@ -10183,10 +10243,10 @@
         <v>89</v>
       </c>
       <c r="D51" s="4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E51" s="4">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>576</v>
@@ -10203,10 +10263,10 @@
         <v>112</v>
       </c>
       <c r="D52" s="4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E52" s="4">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>577</v>
@@ -10266,7 +10326,7 @@
         <v>20</v>
       </c>
       <c r="E55" s="4">
-        <v>20</v>
+        <v>-20</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>580</v>
@@ -10303,10 +10363,10 @@
         <v>89</v>
       </c>
       <c r="D57" s="4">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E57" s="4">
-        <v>-4</v>
+        <v>-14</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>582</v>
@@ -10323,10 +10383,10 @@
         <v>112</v>
       </c>
       <c r="D58" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E58" s="4">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>583</v>
@@ -10343,10 +10403,10 @@
         <v>42</v>
       </c>
       <c r="D59" s="4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E59" s="4">
-        <v>-14</v>
+        <v>-20</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>584</v>
@@ -10363,10 +10423,10 @@
         <v>41</v>
       </c>
       <c r="D60" s="4">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E60" s="4">
-        <v>-10</v>
+        <v>-18</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>585</v>
@@ -10383,10 +10443,10 @@
         <v>203</v>
       </c>
       <c r="D61" s="4">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E61" s="4">
-        <v>-20</v>
+        <v>-12</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>586</v>
@@ -10403,10 +10463,10 @@
         <v>149</v>
       </c>
       <c r="D62" s="4">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E62" s="4">
-        <v>-18</v>
+        <v>-12</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>587</v>
@@ -10443,10 +10503,10 @@
         <v>81</v>
       </c>
       <c r="D64" s="4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E64" s="4">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>589</v>
@@ -10463,10 +10523,10 @@
         <v>58</v>
       </c>
       <c r="D65" s="4">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E65" s="4">
-        <v>-12</v>
+        <v>-21</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>590</v>
@@ -10483,10 +10543,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="4">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E66" s="4">
-        <v>-10</v>
+        <v>-21</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>591</v>
@@ -10503,10 +10563,10 @@
         <v>32</v>
       </c>
       <c r="D67" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E67" s="4">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>592</v>
@@ -10523,10 +10583,10 @@
         <v>112</v>
       </c>
       <c r="D68" s="4">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E68" s="4">
-        <v>-20</v>
+        <v>-12</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>593</v>
@@ -10543,10 +10603,10 @@
         <v>89</v>
       </c>
       <c r="D69" s="4">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E69" s="4">
-        <v>-18</v>
+        <v>-8</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>594</v>
@@ -10563,7 +10623,7 @@
         <v>112</v>
       </c>
       <c r="D70" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E70" s="4">
         <v>-10</v>
@@ -10583,10 +10643,10 @@
         <v>21</v>
       </c>
       <c r="D71" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E71" s="4">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>596</v>
@@ -10603,10 +10663,10 @@
         <v>20</v>
       </c>
       <c r="D72" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E72" s="4">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>597</v>
@@ -10623,10 +10683,10 @@
         <v>43</v>
       </c>
       <c r="D73" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E73" s="4">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>598</v>
@@ -10663,10 +10723,10 @@
         <v>112</v>
       </c>
       <c r="D75">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E75">
-        <v>-12</v>
+        <v>-6</v>
       </c>
       <c r="F75" t="s">
         <v>600</v>
@@ -10723,10 +10783,10 @@
         <v>59</v>
       </c>
       <c r="D78" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E78" s="4">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>603</v>
@@ -10763,10 +10823,10 @@
         <v>53</v>
       </c>
       <c r="D80" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E80" s="4">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>605</v>
@@ -10783,10 +10843,10 @@
         <v>115</v>
       </c>
       <c r="D81" s="4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E81" s="4">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>606</v>
@@ -10823,10 +10883,10 @@
         <v>21</v>
       </c>
       <c r="D83" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E83" s="4">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>608</v>
@@ -10863,10 +10923,10 @@
         <v>20</v>
       </c>
       <c r="D85" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E85" s="4">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>610</v>
@@ -10903,10 +10963,10 @@
         <v>89</v>
       </c>
       <c r="D87" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E87" s="4">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>612</v>
@@ -10923,10 +10983,10 @@
         <v>89</v>
       </c>
       <c r="D88" s="4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E88" s="4">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>613</v>
@@ -10963,10 +11023,10 @@
         <v>42</v>
       </c>
       <c r="D90" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E90" s="4">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>615</v>
@@ -10983,10 +11043,10 @@
         <v>43</v>
       </c>
       <c r="D91" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E91" s="4">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>616</v>
@@ -11003,10 +11063,10 @@
         <v>60</v>
       </c>
       <c r="D92" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E92" s="4">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>617</v>
@@ -11023,10 +11083,10 @@
         <v>112</v>
       </c>
       <c r="D93" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E93" s="4">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>618</v>
@@ -11063,10 +11123,10 @@
         <v>67</v>
       </c>
       <c r="D95" s="4">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E95" s="4">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>620</v>
@@ -11083,10 +11143,10 @@
         <v>49</v>
       </c>
       <c r="D96" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E96" s="4">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>621</v>
@@ -11123,10 +11183,10 @@
         <v>32</v>
       </c>
       <c r="D98" s="4">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E98" s="4">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>623</v>
@@ -11163,10 +11223,10 @@
         <v>21</v>
       </c>
       <c r="D100" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E100" s="4">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>625</v>
@@ -11183,10 +11243,10 @@
         <v>274</v>
       </c>
       <c r="D101">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E101">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>626</v>
@@ -11223,10 +11283,10 @@
         <v>49</v>
       </c>
       <c r="D103" s="4">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E103" s="4">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>628</v>
@@ -11283,10 +11343,10 @@
         <v>115</v>
       </c>
       <c r="D106" s="4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E106" s="4">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>631</v>
@@ -11303,10 +11363,10 @@
         <v>115</v>
       </c>
       <c r="D107" s="4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E107" s="4">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>632</v>
@@ -11323,10 +11383,10 @@
         <v>115</v>
       </c>
       <c r="D108" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E108" s="4">
-        <v>-10</v>
+        <v>-18</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>633</v>
@@ -11343,10 +11403,10 @@
         <v>42</v>
       </c>
       <c r="D109" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E109" s="4">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>634</v>
@@ -11363,205 +11423,443 @@
         <v>43</v>
       </c>
       <c r="D110" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E110" s="4">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>635</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="4"/>
-      <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
-      <c r="D111" s="4"/>
-      <c r="E111" s="4"/>
-      <c r="F111" s="3"/>
+      <c r="A111" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D111" s="4">
+        <v>15</v>
+      </c>
+      <c r="E111" s="4">
+        <v>-18</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>636</v>
+      </c>
     </row>
     <row r="112" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="4"/>
-      <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
-      <c r="E112" s="4"/>
-      <c r="F112" s="3"/>
+      <c r="A112" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D112" s="4">
+        <v>10</v>
+      </c>
+      <c r="E112" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>637</v>
+      </c>
     </row>
     <row r="113" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="4"/>
-      <c r="B113" s="4"/>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4"/>
-      <c r="E113" s="4"/>
-      <c r="F113" s="3"/>
+      <c r="A113" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D113" s="4">
+        <v>8</v>
+      </c>
+      <c r="E113" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>638</v>
+      </c>
     </row>
     <row r="114" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="4"/>
-      <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
-      <c r="D114" s="4"/>
-      <c r="E114" s="4"/>
-      <c r="F114" s="3"/>
+      <c r="A114" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D114" s="4">
+        <v>8</v>
+      </c>
+      <c r="E114" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>639</v>
+      </c>
     </row>
     <row r="115" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="4"/>
-      <c r="B115" s="4"/>
-      <c r="C115" s="4"/>
-      <c r="D115" s="4"/>
-      <c r="E115" s="4"/>
-      <c r="F115" s="3"/>
+      <c r="A115" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D115" s="4">
+        <v>10</v>
+      </c>
+      <c r="E115" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="116" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="4"/>
-      <c r="B116" s="4"/>
-      <c r="C116" s="4"/>
-      <c r="D116" s="4"/>
-      <c r="E116" s="4"/>
-      <c r="F116" s="3"/>
+      <c r="A116" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B116" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D116" s="4">
+        <v>12</v>
+      </c>
+      <c r="E116" s="4">
+        <v>-12</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="117" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="4"/>
-      <c r="B117" s="4"/>
-      <c r="C117" s="4"/>
-      <c r="D117" s="4"/>
-      <c r="E117" s="4"/>
-      <c r="F117" s="3"/>
+      <c r="A117" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D117" s="4">
+        <v>10</v>
+      </c>
+      <c r="E117" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>642</v>
+      </c>
     </row>
     <row r="118" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="4"/>
-      <c r="B118" s="4"/>
-      <c r="C118" s="4"/>
-      <c r="D118" s="4"/>
-      <c r="E118" s="4"/>
-      <c r="F118" s="3"/>
+      <c r="A118" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D118" s="4">
+        <v>10</v>
+      </c>
+      <c r="E118" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>643</v>
+      </c>
     </row>
     <row r="119" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="4"/>
-      <c r="B119" s="4"/>
-      <c r="C119" s="4"/>
-      <c r="D119" s="4"/>
-      <c r="E119" s="4"/>
-      <c r="F119" s="3"/>
+      <c r="A119" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D119" s="4">
+        <v>8</v>
+      </c>
+      <c r="E119" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>644</v>
+      </c>
     </row>
     <row r="120" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="4"/>
-      <c r="B120" s="4"/>
-      <c r="C120" s="4"/>
-      <c r="D120" s="4"/>
-      <c r="E120" s="4"/>
-      <c r="F120" s="3"/>
+      <c r="A120" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D120" s="4">
+        <v>8</v>
+      </c>
+      <c r="E120" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row r="121" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="4"/>
-      <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-      <c r="E121" s="4"/>
-      <c r="F121" s="3"/>
+      <c r="A121" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D121" s="4">
+        <v>8</v>
+      </c>
+      <c r="E121" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>646</v>
+      </c>
     </row>
     <row r="122" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="4"/>
-      <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
-      <c r="E122" s="4"/>
-      <c r="F122" s="3"/>
+      <c r="A122" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D122" s="4">
+        <v>10</v>
+      </c>
+      <c r="E122" s="4">
+        <v>-10</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>647</v>
+      </c>
     </row>
     <row r="123" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="4"/>
-      <c r="B123" s="4"/>
-      <c r="C123" s="4"/>
-      <c r="D123" s="4"/>
-      <c r="E123" s="4"/>
-      <c r="F123" s="3"/>
+      <c r="A123" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D123" s="4">
+        <v>8</v>
+      </c>
+      <c r="E123" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="124" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="4"/>
-      <c r="B124" s="4"/>
-      <c r="C124" s="4"/>
-      <c r="D124" s="4"/>
-      <c r="E124" s="4"/>
-      <c r="F124" s="3"/>
+      <c r="A124" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D124" s="4">
+        <v>8</v>
+      </c>
+      <c r="E124" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>649</v>
+      </c>
     </row>
     <row r="125" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="4"/>
-      <c r="B125" s="4"/>
-      <c r="C125" s="4"/>
-      <c r="D125" s="4"/>
-      <c r="E125" s="4"/>
-      <c r="F125" s="3"/>
+      <c r="A125" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D125" s="4">
+        <v>8</v>
+      </c>
+      <c r="E125" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>650</v>
+      </c>
     </row>
     <row r="126" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="4"/>
-      <c r="B126" s="4"/>
-      <c r="C126" s="4"/>
-      <c r="D126" s="4"/>
-      <c r="E126" s="4"/>
-      <c r="F126" s="3"/>
+      <c r="A126" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D126" s="4">
+        <v>8</v>
+      </c>
+      <c r="E126" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>651</v>
+      </c>
     </row>
     <row r="127" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="4"/>
-      <c r="B127" s="4"/>
-      <c r="C127" s="4"/>
-      <c r="D127" s="4"/>
-      <c r="E127" s="4"/>
-      <c r="F127" s="3"/>
+      <c r="A127" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D127" s="4">
+        <v>8</v>
+      </c>
+      <c r="E127" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>652</v>
+      </c>
     </row>
     <row r="128" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="4"/>
-      <c r="B128" s="4"/>
-      <c r="C128" s="4"/>
-      <c r="D128" s="4"/>
-      <c r="E128" s="4"/>
-      <c r="F128" s="3"/>
-    </row>
-    <row r="129" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="16" t="s">
+      <c r="A128" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D128" s="4">
+        <v>8</v>
+      </c>
+      <c r="E128" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D129" s="4">
+        <v>8</v>
+      </c>
+      <c r="E129" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B130" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D130" s="4">
+        <v>8</v>
+      </c>
+      <c r="E130" s="4">
+        <v>-8</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="B131" s="16"/>
-      <c r="C131" s="16"/>
-      <c r="D131" s="16"/>
-      <c r="E131" s="16"/>
-      <c r="F131" s="16"/>
-      <c r="G131" s="16"/>
-      <c r="H131" s="16"/>
-    </row>
-    <row r="132" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="2" t="s">
+      <c r="B132" s="16"/>
+      <c r="C132" s="16"/>
+      <c r="D132" s="16"/>
+      <c r="E132" s="16"/>
+      <c r="F132" s="16"/>
+      <c r="G132" s="16"/>
+      <c r="H132" s="16"/>
+    </row>
+    <row r="133" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B133" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="C132" s="2" t="s">
+      <c r="C133" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="D133" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="E132" s="2" t="s">
+      <c r="E133" s="2" t="s">
         <v>399</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="B133" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C133" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="D133" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="E133" s="3" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -11569,13 +11867,13 @@
         <v>400</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>403</v>
@@ -11586,13 +11884,13 @@
         <v>400</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>403</v>
@@ -11603,13 +11901,13 @@
         <v>400</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>403</v>
@@ -11620,13 +11918,13 @@
         <v>400</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>403</v>
@@ -11637,13 +11935,13 @@
         <v>400</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>403</v>
@@ -11651,16 +11949,16 @@
     </row>
     <row r="139" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>403</v>
@@ -11671,13 +11969,13 @@
         <v>414</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>403</v>
@@ -11688,13 +11986,13 @@
         <v>414</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>403</v>
@@ -11705,13 +12003,13 @@
         <v>414</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>403</v>
@@ -11719,16 +12017,16 @@
     </row>
     <row r="143" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>86</v>
+        <v>414</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>403</v>
@@ -11739,13 +12037,13 @@
         <v>86</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>403</v>
@@ -11756,13 +12054,13 @@
         <v>86</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>403</v>
@@ -11773,33 +12071,33 @@
         <v>86</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>239</v>
+        <v>428</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>430</v>
+        <v>403</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>431</v>
+        <v>86</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>433</v>
+        <v>239</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>403</v>
+        <v>430</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -11807,13 +12105,13 @@
         <v>431</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>403</v>
@@ -11824,13 +12122,13 @@
         <v>431</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>403</v>
@@ -11841,13 +12139,13 @@
         <v>431</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>403</v>
@@ -11855,16 +12153,16 @@
     </row>
     <row r="151" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>403</v>
@@ -11875,13 +12173,13 @@
         <v>440</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>239</v>
+        <v>442</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>403</v>
@@ -11892,13 +12190,13 @@
         <v>440</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>107</v>
+        <v>240</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>445</v>
+        <v>239</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>403</v>
@@ -11909,13 +12207,13 @@
         <v>440</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>403</v>
@@ -11926,30 +12224,30 @@
         <v>440</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>448</v>
+        <v>115</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>451</v>
+        <v>403</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>451</v>
@@ -11957,16 +12255,16 @@
     </row>
     <row r="157" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>451</v>
@@ -11977,13 +12275,13 @@
         <v>440</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>161</v>
+        <v>457</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>451</v>
@@ -11991,207 +12289,153 @@
     </row>
     <row r="159" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>451</v>
+      </c>
+    </row>
     <row r="161" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="16" t="s">
+    <row r="162" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="B162" s="16"/>
-      <c r="C162" s="16"/>
-      <c r="D162" s="16"/>
-      <c r="E162" s="16"/>
-      <c r="F162" s="16"/>
-      <c r="G162" s="16"/>
-      <c r="H162" s="16"/>
-      <c r="I162" s="16"/>
-      <c r="J162" s="16"/>
-      <c r="K162" s="16"/>
-      <c r="L162" s="16"/>
-      <c r="M162" s="16"/>
-      <c r="N162" s="16"/>
-      <c r="O162" s="16"/>
-      <c r="P162" s="16"/>
-      <c r="Q162" s="16"/>
-      <c r="R162" s="16"/>
-      <c r="S162" s="16"/>
-      <c r="T162" s="16"/>
-      <c r="U162" s="16"/>
-      <c r="V162" s="16"/>
-      <c r="W162" s="16"/>
-    </row>
-    <row r="163" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="2" t="s">
+      <c r="B163" s="16"/>
+      <c r="C163" s="16"/>
+      <c r="D163" s="16"/>
+      <c r="E163" s="16"/>
+      <c r="F163" s="16"/>
+      <c r="G163" s="16"/>
+      <c r="H163" s="16"/>
+      <c r="I163" s="16"/>
+      <c r="J163" s="16"/>
+      <c r="K163" s="16"/>
+      <c r="L163" s="16"/>
+      <c r="M163" s="16"/>
+      <c r="N163" s="16"/>
+      <c r="O163" s="16"/>
+      <c r="P163" s="16"/>
+      <c r="Q163" s="16"/>
+      <c r="R163" s="16"/>
+      <c r="S163" s="16"/>
+      <c r="T163" s="16"/>
+      <c r="U163" s="16"/>
+      <c r="V163" s="16"/>
+      <c r="W163" s="16"/>
+    </row>
+    <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="B164" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C163" s="2" t="s">
+      <c r="C164" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D163" s="2" t="s">
+      <c r="D164" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E163" s="2" t="s">
+      <c r="E164" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F163" s="2" t="s">
+      <c r="F164" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G163" s="2" t="s">
+      <c r="G164" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H163" s="2" t="s">
+      <c r="H164" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="I163" s="2" t="s">
+      <c r="I164" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="J163" s="2" t="s">
+      <c r="J164" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K163" s="2" t="s">
+      <c r="K164" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L163" s="2" t="s">
+      <c r="L164" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="M163" s="2" t="s">
+      <c r="M164" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="N163" s="2" t="s">
+      <c r="N164" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="O163" s="2" t="s">
+      <c r="O164" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="P163" s="2" t="s">
+      <c r="P164" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="Q163" s="2" t="s">
+      <c r="Q164" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="R163" s="2" t="s">
+      <c r="R164" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="S163" s="2" t="s">
+      <c r="S164" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="T163" s="2" t="s">
+      <c r="T164" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="U163" s="2" t="s">
+      <c r="U164" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="V163" s="2" t="s">
+      <c r="V164" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="W163" s="2" t="s">
+      <c r="W164" s="2" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B164" s="4">
-        <v>0</v>
-      </c>
-      <c r="C164" s="4">
-        <v>2</v>
-      </c>
-      <c r="D164" s="4">
-        <v>1</v>
-      </c>
-      <c r="E164" s="4">
-        <v>1</v>
-      </c>
-      <c r="F164" s="4">
-        <v>0</v>
-      </c>
-      <c r="G164" s="4">
-        <v>0</v>
-      </c>
-      <c r="H164" s="4">
-        <v>0</v>
-      </c>
-      <c r="I164" s="4">
-        <v>0</v>
-      </c>
-      <c r="J164" s="4">
-        <v>0</v>
-      </c>
-      <c r="K164" s="4">
-        <v>0</v>
-      </c>
-      <c r="L164" s="4">
-        <v>0</v>
-      </c>
-      <c r="M164" s="4">
-        <v>-1</v>
-      </c>
-      <c r="N164" s="4">
-        <v>0</v>
-      </c>
-      <c r="O164" s="4">
-        <v>0</v>
-      </c>
-      <c r="P164" s="4">
-        <v>-1</v>
-      </c>
-      <c r="Q164" s="4">
-        <v>-1</v>
-      </c>
-      <c r="R164" s="4">
-        <v>-2</v>
-      </c>
-      <c r="S164" s="4">
-        <v>-1</v>
-      </c>
-      <c r="T164" s="4">
-        <v>-1</v>
-      </c>
-      <c r="U164" s="4">
-        <v>0</v>
-      </c>
-      <c r="V164" s="4">
-        <v>0</v>
-      </c>
-      <c r="W164" s="4">
-        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B165" s="4">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="C165" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D165" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E165" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" s="4">
         <v>0</v>
@@ -12212,7 +12456,7 @@
         <v>0</v>
       </c>
       <c r="L165" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="M165" s="4">
         <v>-1</v>
@@ -12227,19 +12471,19 @@
         <v>-1</v>
       </c>
       <c r="Q165" s="4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R165" s="4">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S165" s="4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="T165" s="4">
         <v>-1</v>
       </c>
       <c r="U165" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V165" s="4">
         <v>0</v>
@@ -12250,10 +12494,10 @@
     </row>
     <row r="166" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="B166" s="4">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="C166" s="4">
         <v>0</v>
@@ -12283,22 +12527,22 @@
         <v>0</v>
       </c>
       <c r="L166" s="4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M166" s="4">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N166" s="4">
+        <v>0</v>
+      </c>
+      <c r="O166" s="4">
+        <v>0</v>
+      </c>
+      <c r="P166" s="4">
         <v>-1</v>
       </c>
-      <c r="O166" s="4">
-        <v>0</v>
-      </c>
-      <c r="P166" s="4">
-        <v>-2</v>
-      </c>
       <c r="Q166" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R166" s="4">
         <v>0</v>
@@ -12316,12 +12560,12 @@
         <v>0</v>
       </c>
       <c r="W166" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="B167" s="4">
         <v>0</v>
@@ -12354,22 +12598,22 @@
         <v>0</v>
       </c>
       <c r="L167" s="4">
+        <v>0</v>
+      </c>
+      <c r="M167" s="4">
+        <v>1</v>
+      </c>
+      <c r="N167" s="4">
         <v>-1</v>
       </c>
-      <c r="M167" s="4">
+      <c r="O167" s="4">
+        <v>0</v>
+      </c>
+      <c r="P167" s="4">
+        <v>-2</v>
+      </c>
+      <c r="Q167" s="4">
         <v>-1</v>
-      </c>
-      <c r="N167" s="4">
-        <v>0</v>
-      </c>
-      <c r="O167" s="4">
-        <v>0</v>
-      </c>
-      <c r="P167" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q167" s="4">
-        <v>0</v>
       </c>
       <c r="R167" s="4">
         <v>0</v>
@@ -12387,12 +12631,12 @@
         <v>0</v>
       </c>
       <c r="W167" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="B168" s="4">
         <v>0</v>
@@ -12425,10 +12669,10 @@
         <v>0</v>
       </c>
       <c r="L168" s="4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M168" s="4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N168" s="4">
         <v>0</v>
@@ -12437,33 +12681,33 @@
         <v>0</v>
       </c>
       <c r="P168" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q168" s="4">
+        <v>0</v>
+      </c>
+      <c r="R168" s="4">
+        <v>0</v>
+      </c>
+      <c r="S168" s="4">
+        <v>0</v>
+      </c>
+      <c r="T168" s="4">
+        <v>-1</v>
+      </c>
+      <c r="U168" s="4">
         <v>1</v>
       </c>
-      <c r="Q168" s="4">
+      <c r="V168" s="4">
+        <v>0</v>
+      </c>
+      <c r="W168" s="4">
         <v>2</v>
-      </c>
-      <c r="R168" s="4">
-        <v>0</v>
-      </c>
-      <c r="S168" s="4">
-        <v>2</v>
-      </c>
-      <c r="T168" s="4">
-        <v>0</v>
-      </c>
-      <c r="U168" s="4">
-        <v>0</v>
-      </c>
-      <c r="V168" s="4">
-        <v>0</v>
-      </c>
-      <c r="W168" s="4">
-        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="B169" s="4">
         <v>0</v>
@@ -12508,16 +12752,16 @@
         <v>0</v>
       </c>
       <c r="P169" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q169" s="4">
         <v>2</v>
       </c>
-      <c r="Q169" s="4">
-        <v>0</v>
-      </c>
       <c r="R169" s="4">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="S169" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T169" s="4">
         <v>0</v>
@@ -12534,7 +12778,7 @@
     </row>
     <row r="170" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="B170" s="4">
         <v>0</v>
@@ -12567,19 +12811,19 @@
         <v>0</v>
       </c>
       <c r="L170" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M170" s="4">
+        <v>0</v>
+      </c>
+      <c r="N170" s="4">
+        <v>0</v>
+      </c>
+      <c r="O170" s="4">
+        <v>0</v>
+      </c>
+      <c r="P170" s="4">
         <v>2</v>
-      </c>
-      <c r="N170" s="4">
-        <v>1</v>
-      </c>
-      <c r="O170" s="4">
-        <v>2</v>
-      </c>
-      <c r="P170" s="4">
-        <v>0</v>
       </c>
       <c r="Q170" s="4">
         <v>0</v>
@@ -12605,7 +12849,7 @@
     </row>
     <row r="171" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B171" s="4">
         <v>0</v>
@@ -12638,16 +12882,16 @@
         <v>0</v>
       </c>
       <c r="L171" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M171" s="4">
+        <v>2</v>
+      </c>
+      <c r="N171" s="4">
         <v>1</v>
       </c>
-      <c r="N171" s="4">
-        <v>0</v>
-      </c>
       <c r="O171" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P171" s="4">
         <v>0</v>
@@ -12656,13 +12900,13 @@
         <v>0</v>
       </c>
       <c r="R171" s="4">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="S171" s="4">
         <v>0</v>
       </c>
       <c r="T171" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U171" s="4">
         <v>0</v>
@@ -12676,7 +12920,7 @@
     </row>
     <row r="172" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B172" s="4">
         <v>0</v>
@@ -12712,13 +12956,13 @@
         <v>0</v>
       </c>
       <c r="M172" s="4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N172" s="4">
         <v>0</v>
       </c>
       <c r="O172" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P172" s="4">
         <v>0</v>
@@ -12733,7 +12977,7 @@
         <v>0</v>
       </c>
       <c r="T172" s="4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U172" s="4">
         <v>0</v>
@@ -12742,12 +12986,12 @@
         <v>0</v>
       </c>
       <c r="W172" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B173" s="4">
         <v>0</v>
@@ -12780,16 +13024,16 @@
         <v>0</v>
       </c>
       <c r="L173" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M173" s="4">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="N173" s="4">
         <v>0</v>
       </c>
       <c r="O173" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P173" s="4">
         <v>0</v>
@@ -12813,12 +13057,12 @@
         <v>0</v>
       </c>
       <c r="W173" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="B174" s="4">
         <v>0</v>
@@ -12827,49 +13071,49 @@
         <v>0</v>
       </c>
       <c r="D174" s="4">
+        <v>0</v>
+      </c>
+      <c r="E174" s="4">
+        <v>0</v>
+      </c>
+      <c r="F174" s="4">
+        <v>0</v>
+      </c>
+      <c r="G174" s="4">
+        <v>0</v>
+      </c>
+      <c r="H174" s="4">
+        <v>0</v>
+      </c>
+      <c r="I174" s="4">
+        <v>0</v>
+      </c>
+      <c r="J174" s="4">
+        <v>0</v>
+      </c>
+      <c r="K174" s="4">
+        <v>0</v>
+      </c>
+      <c r="L174" s="4">
         <v>1</v>
       </c>
-      <c r="E174" s="4">
-        <v>1</v>
-      </c>
-      <c r="F174" s="4">
-        <v>0</v>
-      </c>
-      <c r="G174" s="4">
-        <v>0</v>
-      </c>
-      <c r="H174" s="4">
+      <c r="M174" s="4">
+        <v>2</v>
+      </c>
+      <c r="N174" s="4">
+        <v>0</v>
+      </c>
+      <c r="O174" s="4">
+        <v>2</v>
+      </c>
+      <c r="P174" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="4">
+        <v>0</v>
+      </c>
+      <c r="R174" s="4">
         <v>-1</v>
-      </c>
-      <c r="I174" s="4">
-        <v>0</v>
-      </c>
-      <c r="J174" s="4">
-        <v>0</v>
-      </c>
-      <c r="K174" s="4">
-        <v>-1</v>
-      </c>
-      <c r="L174" s="4">
-        <v>0</v>
-      </c>
-      <c r="M174" s="4">
-        <v>0</v>
-      </c>
-      <c r="N174" s="4">
-        <v>0</v>
-      </c>
-      <c r="O174" s="4">
-        <v>0</v>
-      </c>
-      <c r="P174" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q174" s="4">
-        <v>0</v>
-      </c>
-      <c r="R174" s="4">
-        <v>0</v>
       </c>
       <c r="S174" s="4">
         <v>0</v>
@@ -12889,7 +13133,7 @@
     </row>
     <row r="175" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B175" s="4">
         <v>0</v>
@@ -12898,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="D175" s="4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E175" s="4">
         <v>1</v>
@@ -12910,16 +13154,16 @@
         <v>0</v>
       </c>
       <c r="H175" s="4">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I175" s="4">
+        <v>0</v>
+      </c>
+      <c r="J175" s="4">
+        <v>0</v>
+      </c>
+      <c r="K175" s="4">
         <v>-1</v>
-      </c>
-      <c r="J175" s="4">
-        <v>1</v>
-      </c>
-      <c r="K175" s="4">
-        <v>-2</v>
       </c>
       <c r="L175" s="4">
         <v>0</v>
@@ -12960,7 +13204,7 @@
     </row>
     <row r="176" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="B176" s="4">
         <v>0</v>
@@ -12969,10 +13213,10 @@
         <v>0</v>
       </c>
       <c r="D176" s="4">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E176" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F176" s="4">
         <v>0</v>
@@ -12981,16 +13225,16 @@
         <v>0</v>
       </c>
       <c r="H176" s="4">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I176" s="4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J176" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K176" s="4">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L176" s="4">
         <v>0</v>
@@ -13017,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="T176" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U176" s="4">
         <v>0</v>
@@ -13031,7 +13275,7 @@
     </row>
     <row r="177" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="B177" s="4">
         <v>0</v>
@@ -13040,7 +13284,7 @@
         <v>0</v>
       </c>
       <c r="D177" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E177" s="4">
         <v>0</v>
@@ -13052,43 +13296,43 @@
         <v>0</v>
       </c>
       <c r="H177" s="4">
+        <v>0</v>
+      </c>
+      <c r="I177" s="4">
+        <v>0</v>
+      </c>
+      <c r="J177" s="4">
+        <v>0</v>
+      </c>
+      <c r="K177" s="4">
+        <v>0</v>
+      </c>
+      <c r="L177" s="4">
+        <v>0</v>
+      </c>
+      <c r="M177" s="4">
+        <v>0</v>
+      </c>
+      <c r="N177" s="4">
+        <v>0</v>
+      </c>
+      <c r="O177" s="4">
+        <v>0</v>
+      </c>
+      <c r="P177" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q177" s="4">
+        <v>0</v>
+      </c>
+      <c r="R177" s="4">
+        <v>0</v>
+      </c>
+      <c r="S177" s="4">
+        <v>0</v>
+      </c>
+      <c r="T177" s="4">
         <v>-1</v>
-      </c>
-      <c r="I177" s="4">
-        <v>0</v>
-      </c>
-      <c r="J177" s="4">
-        <v>0</v>
-      </c>
-      <c r="K177" s="4">
-        <v>-1</v>
-      </c>
-      <c r="L177" s="4">
-        <v>0</v>
-      </c>
-      <c r="M177" s="4">
-        <v>0</v>
-      </c>
-      <c r="N177" s="4">
-        <v>0</v>
-      </c>
-      <c r="O177" s="4">
-        <v>0</v>
-      </c>
-      <c r="P177" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q177" s="4">
-        <v>0</v>
-      </c>
-      <c r="R177" s="4">
-        <v>0</v>
-      </c>
-      <c r="S177" s="4">
-        <v>0</v>
-      </c>
-      <c r="T177" s="4">
-        <v>0</v>
       </c>
       <c r="U177" s="4">
         <v>0</v>
@@ -13102,38 +13346,38 @@
     </row>
     <row r="178" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="B178" s="4">
+        <v>0</v>
+      </c>
+      <c r="C178" s="4">
+        <v>0</v>
+      </c>
+      <c r="D178" s="4">
+        <v>0</v>
+      </c>
+      <c r="E178" s="4">
+        <v>0</v>
+      </c>
+      <c r="F178" s="4">
+        <v>0</v>
+      </c>
+      <c r="G178" s="4">
+        <v>0</v>
+      </c>
+      <c r="H178" s="4">
         <v>-1</v>
       </c>
-      <c r="C178" s="4">
-        <v>1</v>
-      </c>
-      <c r="D178" s="4">
-        <v>2</v>
-      </c>
-      <c r="E178" s="4">
-        <v>0</v>
-      </c>
-      <c r="F178" s="4">
+      <c r="I178" s="4">
+        <v>0</v>
+      </c>
+      <c r="J178" s="4">
+        <v>0</v>
+      </c>
+      <c r="K178" s="4">
         <v>-1</v>
       </c>
-      <c r="G178" s="4">
-        <v>-2</v>
-      </c>
-      <c r="H178" s="4">
-        <v>0</v>
-      </c>
-      <c r="I178" s="4">
-        <v>0</v>
-      </c>
-      <c r="J178" s="4">
-        <v>0</v>
-      </c>
-      <c r="K178" s="4">
-        <v>0</v>
-      </c>
       <c r="L178" s="4">
         <v>0</v>
       </c>
@@ -13162,119 +13406,119 @@
         <v>0</v>
       </c>
       <c r="U178" s="4">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="V178" s="4">
         <v>0</v>
       </c>
       <c r="W178" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="B179" s="4">
+        <v>-1</v>
+      </c>
+      <c r="C179" s="4">
         <v>1</v>
       </c>
-      <c r="C179" s="4">
-        <v>0</v>
-      </c>
       <c r="D179" s="4">
+        <v>2</v>
+      </c>
+      <c r="E179" s="4">
+        <v>0</v>
+      </c>
+      <c r="F179" s="4">
+        <v>-1</v>
+      </c>
+      <c r="G179" s="4">
+        <v>-2</v>
+      </c>
+      <c r="H179" s="4">
+        <v>0</v>
+      </c>
+      <c r="I179" s="4">
+        <v>0</v>
+      </c>
+      <c r="J179" s="4">
+        <v>0</v>
+      </c>
+      <c r="K179" s="4">
+        <v>0</v>
+      </c>
+      <c r="L179" s="4">
+        <v>0</v>
+      </c>
+      <c r="M179" s="4">
+        <v>0</v>
+      </c>
+      <c r="N179" s="4">
+        <v>0</v>
+      </c>
+      <c r="O179" s="4">
+        <v>0</v>
+      </c>
+      <c r="P179" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q179" s="4">
+        <v>0</v>
+      </c>
+      <c r="R179" s="4">
+        <v>0</v>
+      </c>
+      <c r="S179" s="4">
+        <v>0</v>
+      </c>
+      <c r="T179" s="4">
+        <v>0</v>
+      </c>
+      <c r="U179" s="4">
+        <v>-2</v>
+      </c>
+      <c r="V179" s="4">
+        <v>0</v>
+      </c>
+      <c r="W179" s="4">
         <v>1</v>
-      </c>
-      <c r="E179" s="4">
-        <v>0</v>
-      </c>
-      <c r="F179" s="4">
-        <v>-2</v>
-      </c>
-      <c r="G179" s="4">
-        <v>0</v>
-      </c>
-      <c r="H179" s="4">
-        <v>0</v>
-      </c>
-      <c r="I179" s="4">
-        <v>0</v>
-      </c>
-      <c r="J179" s="4">
-        <v>0</v>
-      </c>
-      <c r="K179" s="4">
-        <v>0</v>
-      </c>
-      <c r="L179" s="4">
-        <v>0</v>
-      </c>
-      <c r="M179" s="4">
-        <v>0</v>
-      </c>
-      <c r="N179" s="4">
-        <v>0</v>
-      </c>
-      <c r="O179" s="4">
-        <v>0</v>
-      </c>
-      <c r="P179" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q179" s="4">
-        <v>0</v>
-      </c>
-      <c r="R179" s="4">
-        <v>0</v>
-      </c>
-      <c r="S179" s="4">
-        <v>0</v>
-      </c>
-      <c r="T179" s="4">
-        <v>0</v>
-      </c>
-      <c r="U179" s="4">
-        <v>0</v>
-      </c>
-      <c r="V179" s="4">
-        <v>0</v>
-      </c>
-      <c r="W179" s="4">
-        <v>0</v>
       </c>
     </row>
     <row r="180" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="B180" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C180" s="4">
         <v>0</v>
       </c>
       <c r="D180" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E180" s="4">
         <v>0</v>
       </c>
       <c r="F180" s="4">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G180" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H180" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I180" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J180" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K180" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L180" s="4">
         <v>0</v>
@@ -13315,37 +13559,37 @@
     </row>
     <row r="181" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="B181" s="4">
+        <v>2</v>
+      </c>
+      <c r="C181" s="4">
+        <v>0</v>
+      </c>
+      <c r="D181" s="4">
+        <v>0</v>
+      </c>
+      <c r="E181" s="4">
+        <v>0</v>
+      </c>
+      <c r="F181" s="4">
         <v>1</v>
       </c>
-      <c r="C181" s="4">
+      <c r="G181" s="4">
+        <v>2</v>
+      </c>
+      <c r="H181" s="4">
+        <v>2</v>
+      </c>
+      <c r="I181" s="4">
         <v>1</v>
       </c>
-      <c r="D181" s="4">
+      <c r="J181" s="4">
         <v>1</v>
       </c>
-      <c r="E181" s="4">
-        <v>0</v>
-      </c>
-      <c r="F181" s="4">
-        <v>-2</v>
-      </c>
-      <c r="G181" s="4">
-        <v>0</v>
-      </c>
-      <c r="H181" s="4">
-        <v>0</v>
-      </c>
-      <c r="I181" s="4">
-        <v>0</v>
-      </c>
-      <c r="J181" s="4">
-        <v>0</v>
-      </c>
       <c r="K181" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L181" s="4">
         <v>0</v>
@@ -13386,25 +13630,25 @@
     </row>
     <row r="182" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>81</v>
+        <v>147</v>
       </c>
       <c r="B182" s="4">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="C182" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D182" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E182" s="4">
         <v>0</v>
       </c>
       <c r="F182" s="4">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G182" s="4">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H182" s="4">
         <v>0</v>
@@ -13446,7 +13690,7 @@
         <v>0</v>
       </c>
       <c r="U182" s="4">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="V182" s="4">
         <v>0</v>
@@ -13457,16 +13701,16 @@
     </row>
     <row r="183" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
-        <v>240</v>
+        <v>81</v>
       </c>
       <c r="B183" s="4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="C183" s="4">
         <v>0</v>
       </c>
       <c r="D183" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E183" s="4">
         <v>0</v>
@@ -13475,7 +13719,7 @@
         <v>0</v>
       </c>
       <c r="G183" s="4">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H183" s="4">
         <v>0</v>
@@ -13502,7 +13746,7 @@
         <v>0</v>
       </c>
       <c r="P183" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q183" s="4">
         <v>0</v>
@@ -13514,10 +13758,10 @@
         <v>0</v>
       </c>
       <c r="T183" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U183" s="4">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="V183" s="4">
         <v>0</v>
@@ -13528,7 +13772,7 @@
     </row>
     <row r="184" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>107</v>
+        <v>240</v>
       </c>
       <c r="B184" s="4">
         <v>0</v>
@@ -13564,7 +13808,7 @@
         <v>0</v>
       </c>
       <c r="M184" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N184" s="4">
         <v>0</v>
@@ -13573,7 +13817,7 @@
         <v>0</v>
       </c>
       <c r="P184" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q184" s="4">
         <v>0</v>
@@ -13585,7 +13829,7 @@
         <v>0</v>
       </c>
       <c r="T184" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U184" s="4">
         <v>0</v>
@@ -13599,111 +13843,172 @@
     </row>
     <row r="185" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B185" s="4">
+        <v>0</v>
+      </c>
+      <c r="C185" s="4">
+        <v>0</v>
+      </c>
+      <c r="D185" s="4">
+        <v>0</v>
+      </c>
+      <c r="E185" s="4">
+        <v>0</v>
+      </c>
+      <c r="F185" s="4">
+        <v>0</v>
+      </c>
+      <c r="G185" s="4">
+        <v>0</v>
+      </c>
+      <c r="H185" s="4">
+        <v>0</v>
+      </c>
+      <c r="I185" s="4">
+        <v>0</v>
+      </c>
+      <c r="J185" s="4">
+        <v>0</v>
+      </c>
+      <c r="K185" s="4">
+        <v>0</v>
+      </c>
+      <c r="L185" s="4">
+        <v>0</v>
+      </c>
+      <c r="M185" s="4">
+        <v>1</v>
+      </c>
+      <c r="N185" s="4">
+        <v>0</v>
+      </c>
+      <c r="O185" s="4">
+        <v>0</v>
+      </c>
+      <c r="P185" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q185" s="4">
+        <v>0</v>
+      </c>
+      <c r="R185" s="4">
+        <v>0</v>
+      </c>
+      <c r="S185" s="4">
+        <v>0</v>
+      </c>
+      <c r="T185" s="4">
+        <v>0</v>
+      </c>
+      <c r="U185" s="4">
+        <v>0</v>
+      </c>
+      <c r="V185" s="4">
+        <v>0</v>
+      </c>
+      <c r="W185" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B185" s="4">
-        <v>0</v>
-      </c>
-      <c r="C185" s="4">
-        <v>0</v>
-      </c>
-      <c r="D185" s="4">
-        <v>0</v>
-      </c>
-      <c r="E185" s="4">
+      <c r="B186" s="4">
+        <v>0</v>
+      </c>
+      <c r="C186" s="4">
+        <v>0</v>
+      </c>
+      <c r="D186" s="4">
+        <v>0</v>
+      </c>
+      <c r="E186" s="4">
         <v>-2</v>
       </c>
-      <c r="F185" s="4">
-        <v>0</v>
-      </c>
-      <c r="G185" s="4">
-        <v>0</v>
-      </c>
-      <c r="H185" s="4">
-        <v>0</v>
-      </c>
-      <c r="I185" s="4">
-        <v>0</v>
-      </c>
-      <c r="J185" s="4">
+      <c r="F186" s="4">
+        <v>0</v>
+      </c>
+      <c r="G186" s="4">
+        <v>0</v>
+      </c>
+      <c r="H186" s="4">
+        <v>0</v>
+      </c>
+      <c r="I186" s="4">
+        <v>0</v>
+      </c>
+      <c r="J186" s="4">
         <v>-2</v>
       </c>
-      <c r="K185" s="4">
-        <v>0</v>
-      </c>
-      <c r="L185" s="4">
-        <v>0</v>
-      </c>
-      <c r="M185" s="4">
-        <v>0</v>
-      </c>
-      <c r="N185" s="4">
-        <v>0</v>
-      </c>
-      <c r="O185" s="4">
-        <v>0</v>
-      </c>
-      <c r="P185" s="4">
-        <v>0</v>
-      </c>
-      <c r="Q185" s="4">
-        <v>0</v>
-      </c>
-      <c r="R185" s="4">
-        <v>0</v>
-      </c>
-      <c r="S185" s="4">
-        <v>0</v>
-      </c>
-      <c r="T185" s="4">
-        <v>0</v>
-      </c>
-      <c r="U185" s="4">
-        <v>0</v>
-      </c>
-      <c r="V185" s="4">
-        <v>0</v>
-      </c>
-      <c r="W185" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="K186" s="4">
+        <v>0</v>
+      </c>
+      <c r="L186" s="4">
+        <v>0</v>
+      </c>
+      <c r="M186" s="4">
+        <v>0</v>
+      </c>
+      <c r="N186" s="4">
+        <v>0</v>
+      </c>
+      <c r="O186" s="4">
+        <v>0</v>
+      </c>
+      <c r="P186" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q186" s="4">
+        <v>0</v>
+      </c>
+      <c r="R186" s="4">
+        <v>0</v>
+      </c>
+      <c r="S186" s="4">
+        <v>0</v>
+      </c>
+      <c r="T186" s="4">
+        <v>0</v>
+      </c>
+      <c r="U186" s="4">
+        <v>0</v>
+      </c>
+      <c r="V186" s="4">
+        <v>0</v>
+      </c>
+      <c r="W186" s="4">
+        <v>0</v>
+      </c>
+    </row>
     <row r="187" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="16" t="s">
+    <row r="188" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="16" t="s">
         <v>463</v>
       </c>
-      <c r="B188" s="16"/>
-      <c r="C188" s="16"/>
-      <c r="D188" s="16"/>
-      <c r="E188" s="16"/>
-    </row>
-    <row r="189" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="2" t="s">
+      <c r="B189" s="16"/>
+      <c r="C189" s="16"/>
+      <c r="D189" s="16"/>
+      <c r="E189" s="16"/>
+    </row>
+    <row r="190" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B189" s="2" t="s">
+      <c r="B190" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="C189" s="2" t="s">
+      <c r="C190" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D189" s="2" t="s">
+      <c r="D190" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="E189" s="2" t="s">
+      <c r="E190" s="2" t="s">
         <v>466</v>
-      </c>
-    </row>
-    <row r="190" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="5"/>
-      <c r="B190" s="5"/>
-      <c r="C190" s="5"/>
-      <c r="D190" s="5"/>
-      <c r="E190" t="str">
-        <f t="shared" ref="E190:E253" si="0">A190&amp;"|"&amp;B190</f>
-        <v>|</v>
       </c>
     </row>
     <row r="191" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -13712,7 +14017,7 @@
       <c r="C191" s="5"/>
       <c r="D191" s="5"/>
       <c r="E191" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E191:E254" si="0">A191&amp;"|"&amp;B191</f>
         <v>|</v>
       </c>
     </row>
@@ -14342,7 +14647,7 @@
       <c r="C254" s="5"/>
       <c r="D254" s="5"/>
       <c r="E254" t="str">
-        <f t="shared" ref="E254:E317" si="1">A254&amp;"|"&amp;B254</f>
+        <f t="shared" si="0"/>
         <v>|</v>
       </c>
     </row>
@@ -14352,7 +14657,7 @@
       <c r="C255" s="5"/>
       <c r="D255" s="5"/>
       <c r="E255" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E255:E318" si="1">A255&amp;"|"&amp;B255</f>
         <v>|</v>
       </c>
     </row>
@@ -14982,7 +15287,7 @@
       <c r="C318" s="5"/>
       <c r="D318" s="5"/>
       <c r="E318" t="str">
-        <f t="shared" ref="E318:E381" si="2">A318&amp;"|"&amp;B318</f>
+        <f t="shared" si="1"/>
         <v>|</v>
       </c>
     </row>
@@ -14992,7 +15297,7 @@
       <c r="C319" s="5"/>
       <c r="D319" s="5"/>
       <c r="E319" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="E319:E382" si="2">A319&amp;"|"&amp;B319</f>
         <v>|</v>
       </c>
     </row>
@@ -15622,7 +15927,7 @@
       <c r="C382" s="5"/>
       <c r="D382" s="5"/>
       <c r="E382" t="str">
-        <f t="shared" ref="E382:E445" si="3">A382&amp;"|"&amp;B382</f>
+        <f t="shared" si="2"/>
         <v>|</v>
       </c>
     </row>
@@ -15632,7 +15937,7 @@
       <c r="C383" s="5"/>
       <c r="D383" s="5"/>
       <c r="E383" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E383:E446" si="3">A383&amp;"|"&amp;B383</f>
         <v>|</v>
       </c>
     </row>
@@ -16262,7 +16567,7 @@
       <c r="C446" s="5"/>
       <c r="D446" s="5"/>
       <c r="E446" t="str">
-        <f t="shared" ref="E446:E509" si="4">A446&amp;"|"&amp;B446</f>
+        <f t="shared" si="3"/>
         <v>|</v>
       </c>
     </row>
@@ -16272,7 +16577,7 @@
       <c r="C447" s="5"/>
       <c r="D447" s="5"/>
       <c r="E447" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E447:E510" si="4">A447&amp;"|"&amp;B447</f>
         <v>|</v>
       </c>
     </row>
@@ -16902,7 +17207,7 @@
       <c r="C510" s="5"/>
       <c r="D510" s="5"/>
       <c r="E510" t="str">
-        <f t="shared" ref="E510:E573" si="5">A510&amp;"|"&amp;B510</f>
+        <f t="shared" si="4"/>
         <v>|</v>
       </c>
     </row>
@@ -16912,7 +17217,7 @@
       <c r="C511" s="5"/>
       <c r="D511" s="5"/>
       <c r="E511" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="E511:E574" si="5">A511&amp;"|"&amp;B511</f>
         <v>|</v>
       </c>
     </row>
@@ -17542,7 +17847,7 @@
       <c r="C574" s="5"/>
       <c r="D574" s="5"/>
       <c r="E574" t="str">
-        <f t="shared" ref="E574:E637" si="6">A574&amp;"|"&amp;B574</f>
+        <f t="shared" si="5"/>
         <v>|</v>
       </c>
     </row>
@@ -17552,7 +17857,7 @@
       <c r="C575" s="5"/>
       <c r="D575" s="5"/>
       <c r="E575" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="E575:E638" si="6">A575&amp;"|"&amp;B575</f>
         <v>|</v>
       </c>
     </row>
@@ -18182,7 +18487,7 @@
       <c r="C638" s="5"/>
       <c r="D638" s="5"/>
       <c r="E638" t="str">
-        <f t="shared" ref="E638:E701" si="7">A638&amp;"|"&amp;B638</f>
+        <f t="shared" si="6"/>
         <v>|</v>
       </c>
     </row>
@@ -18192,7 +18497,7 @@
       <c r="C639" s="5"/>
       <c r="D639" s="5"/>
       <c r="E639" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="E639:E702" si="7">A639&amp;"|"&amp;B639</f>
         <v>|</v>
       </c>
     </row>
@@ -18822,7 +19127,7 @@
       <c r="C702" s="5"/>
       <c r="D702" s="5"/>
       <c r="E702" t="str">
-        <f t="shared" ref="E702:E765" si="8">A702&amp;"|"&amp;B702</f>
+        <f t="shared" si="7"/>
         <v>|</v>
       </c>
     </row>
@@ -18832,7 +19137,7 @@
       <c r="C703" s="5"/>
       <c r="D703" s="5"/>
       <c r="E703" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="E703:E766" si="8">A703&amp;"|"&amp;B703</f>
         <v>|</v>
       </c>
     </row>
@@ -19462,7 +19767,7 @@
       <c r="C766" s="5"/>
       <c r="D766" s="5"/>
       <c r="E766" t="str">
-        <f t="shared" ref="E766:E829" si="9">A766&amp;"|"&amp;B766</f>
+        <f t="shared" si="8"/>
         <v>|</v>
       </c>
     </row>
@@ -19472,7 +19777,7 @@
       <c r="C767" s="5"/>
       <c r="D767" s="5"/>
       <c r="E767" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="E767:E830" si="9">A767&amp;"|"&amp;B767</f>
         <v>|</v>
       </c>
     </row>
@@ -20102,7 +20407,7 @@
       <c r="C830" s="5"/>
       <c r="D830" s="5"/>
       <c r="E830" t="str">
-        <f t="shared" ref="E830:E893" si="10">A830&amp;"|"&amp;B830</f>
+        <f t="shared" si="9"/>
         <v>|</v>
       </c>
     </row>
@@ -20112,7 +20417,7 @@
       <c r="C831" s="5"/>
       <c r="D831" s="5"/>
       <c r="E831" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="E831:E894" si="10">A831&amp;"|"&amp;B831</f>
         <v>|</v>
       </c>
     </row>
@@ -20742,7 +21047,7 @@
       <c r="C894" s="5"/>
       <c r="D894" s="5"/>
       <c r="E894" t="str">
-        <f t="shared" ref="E894:E957" si="11">A894&amp;"|"&amp;B894</f>
+        <f t="shared" si="10"/>
         <v>|</v>
       </c>
     </row>
@@ -20752,7 +21057,7 @@
       <c r="C895" s="5"/>
       <c r="D895" s="5"/>
       <c r="E895" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="E895:E958" si="11">A895&amp;"|"&amp;B895</f>
         <v>|</v>
       </c>
     </row>
@@ -21382,7 +21687,7 @@
       <c r="C958" s="5"/>
       <c r="D958" s="5"/>
       <c r="E958" t="str">
-        <f t="shared" ref="E958:E1021" si="12">A958&amp;"|"&amp;B958</f>
+        <f t="shared" si="11"/>
         <v>|</v>
       </c>
     </row>
@@ -21392,7 +21697,7 @@
       <c r="C959" s="5"/>
       <c r="D959" s="5"/>
       <c r="E959" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="E959:E1022" si="12">A959&amp;"|"&amp;B959</f>
         <v>|</v>
       </c>
     </row>
@@ -22022,7 +22327,7 @@
       <c r="C1022" s="5"/>
       <c r="D1022" s="5"/>
       <c r="E1022" t="str">
-        <f t="shared" ref="E1022:E1085" si="13">A1022&amp;"|"&amp;B1022</f>
+        <f t="shared" si="12"/>
         <v>|</v>
       </c>
     </row>
@@ -22032,7 +22337,7 @@
       <c r="C1023" s="5"/>
       <c r="D1023" s="5"/>
       <c r="E1023" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="E1023:E1086" si="13">A1023&amp;"|"&amp;B1023</f>
         <v>|</v>
       </c>
     </row>
@@ -22662,7 +22967,7 @@
       <c r="C1086" s="5"/>
       <c r="D1086" s="5"/>
       <c r="E1086" t="str">
-        <f t="shared" ref="E1086:E1149" si="14">A1086&amp;"|"&amp;B1086</f>
+        <f t="shared" si="13"/>
         <v>|</v>
       </c>
     </row>
@@ -22672,7 +22977,7 @@
       <c r="C1087" s="5"/>
       <c r="D1087" s="5"/>
       <c r="E1087" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="E1087:E1150" si="14">A1087&amp;"|"&amp;B1087</f>
         <v>|</v>
       </c>
     </row>
@@ -23302,7 +23607,7 @@
       <c r="C1150" s="5"/>
       <c r="D1150" s="5"/>
       <c r="E1150" t="str">
-        <f t="shared" ref="E1150:E1189" si="15">A1150&amp;"|"&amp;B1150</f>
+        <f t="shared" si="14"/>
         <v>|</v>
       </c>
     </row>
@@ -23312,7 +23617,7 @@
       <c r="C1151" s="5"/>
       <c r="D1151" s="5"/>
       <c r="E1151" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="E1151:E1190" si="15">A1151&amp;"|"&amp;B1151</f>
         <v>|</v>
       </c>
     </row>
@@ -23696,11 +24001,21 @@
         <v>|</v>
       </c>
     </row>
+    <row r="1190" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1190" s="5"/>
+      <c r="B1190" s="5"/>
+      <c r="C1190" s="5"/>
+      <c r="D1190" s="5"/>
+      <c r="E1190" t="str">
+        <f t="shared" si="15"/>
+        <v>|</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A131:H131"/>
-    <mergeCell ref="A162:W162"/>
-    <mergeCell ref="A188:E188"/>
+    <mergeCell ref="A132:H132"/>
+    <mergeCell ref="A163:W163"/>
+    <mergeCell ref="A189:E189"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A3:N3"/>
     <mergeCell ref="A5:H5"/>
@@ -23708,7 +24023,7 @@
     <mergeCell ref="A27:H27"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid type" error="Must be &quot;Tag&quot; or &quot;Hero&quot;." sqref="B29:B128" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid type" error="Must be &quot;Tag&quot; or &quot;Hero&quot;." sqref="B29:B129" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Tag,Hero,Role,DamageType,Resource"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -23725,16 +24040,16 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>A190:B1189 A29:A62 A111:A128</xm:sqref>
+          <xm:sqref>A191:B1190 A29:A62 A111:A129</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000004000000}">
           <x14:formula1>
-            <xm:f>IF($B29="Hero",Heroes!$B$2:$B$134,IF($B29="Role",$A$19:$A$24,IF($B29="DamageType",$J$29:$J$31,IF($B29="Resource",$J$33:$J$35,$A$164:$A$185))))</xm:f>
+            <xm:f>IF($B29="Hero",Heroes!$B$2:$B$134,IF($B29="Role",$A$19:$A$24,IF($B29="DamageType",$J$29:$J$31,IF($B29="Resource",$J$33:$J$35,$A$165:$A$186))))</xm:f>
           </x14:formula1>
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>C29:C62 C111:C128</xm:sqref>
+          <xm:sqref>C29:C62 C111:C129</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -23770,18 +24085,18 @@
       <c r="J3" s="19"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>469</v>
       </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="7" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
@@ -23854,18 +24169,18 @@
       <c r="J11" s="19"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="20" t="s">
         <v>475</v>
       </c>
-      <c r="B13" s="21"/>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
     </row>
     <row r="15" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19" t="s">
@@ -23882,18 +24197,18 @@
       <c r="J15" s="19"/>
     </row>
     <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="20" t="s">
         <v>477</v>
       </c>
-      <c r="B17" s="21"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
@@ -23929,18 +24244,18 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="21" t="s">
         <v>481</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
     </row>
     <row r="24" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
@@ -23962,18 +24277,18 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="21" t="s">
         <v>484</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
     </row>
     <row r="27" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19" t="s">
@@ -23995,18 +24310,18 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="21" t="s">
         <v>487</v>
       </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
     </row>
     <row r="30" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
@@ -24028,18 +24343,18 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="21" t="s">
         <v>490</v>
       </c>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
     </row>
     <row r="33" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
@@ -24061,18 +24376,18 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="21" t="s">
         <v>493</v>
       </c>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
     </row>
     <row r="36" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19" t="s">
@@ -24094,18 +24409,18 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="21" t="s">
         <v>496</v>
       </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="21"/>
+      <c r="J38" s="21"/>
     </row>
     <row r="39" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19" t="s">
@@ -24225,18 +24540,18 @@
       <c r="J47" s="19"/>
     </row>
     <row r="49" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="20" t="s">
         <v>506</v>
       </c>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21"/>
-      <c r="J49" s="21"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
     </row>
     <row r="51" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="19" t="s">
@@ -24267,270 +24582,270 @@
       <c r="J52" s="19"/>
     </row>
     <row r="54" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="21" t="s">
+      <c r="A54" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="B54" s="21"/>
-      <c r="C54" s="21"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
-      <c r="J54" s="21"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
     </row>
     <row r="56" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="20" t="s">
+      <c r="A56" s="21" t="s">
         <v>510</v>
       </c>
-      <c r="B56" s="20"/>
-      <c r="C56" s="20"/>
-      <c r="D56" s="20"/>
-      <c r="E56" s="20"/>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="21"/>
+      <c r="G56" s="21"/>
+      <c r="H56" s="21"/>
+      <c r="I56" s="21"/>
+      <c r="J56" s="21"/>
     </row>
     <row r="57" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="20" t="s">
+      <c r="A57" s="21" t="s">
         <v>511</v>
       </c>
-      <c r="B57" s="20"/>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20"/>
-      <c r="E57" s="20"/>
-      <c r="F57" s="20"/>
-      <c r="G57" s="20"/>
-      <c r="H57" s="20"/>
-      <c r="I57" s="20"/>
-      <c r="J57" s="20"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="21"/>
+      <c r="D57" s="21"/>
+      <c r="E57" s="21"/>
+      <c r="F57" s="21"/>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="21"/>
+      <c r="J57" s="21"/>
     </row>
     <row r="58" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="20" t="s">
+      <c r="A58" s="21" t="s">
         <v>512</v>
       </c>
-      <c r="B58" s="20"/>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="20"/>
-      <c r="F58" s="20"/>
-      <c r="G58" s="20"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
-      <c r="J58" s="20"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="21"/>
+      <c r="J58" s="21"/>
     </row>
     <row r="59" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="20" t="s">
+      <c r="A59" s="21" t="s">
         <v>513</v>
       </c>
-      <c r="B59" s="20"/>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="20"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="21"/>
+      <c r="H59" s="21"/>
+      <c r="I59" s="21"/>
+      <c r="J59" s="21"/>
     </row>
     <row r="60" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="20" t="s">
+      <c r="A60" s="21" t="s">
         <v>514</v>
       </c>
-      <c r="B60" s="20"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
-      <c r="J60" s="20"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21"/>
+      <c r="H60" s="21"/>
+      <c r="I60" s="21"/>
+      <c r="J60" s="21"/>
     </row>
     <row r="61" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="20" t="s">
+      <c r="A61" s="21" t="s">
         <v>515</v>
       </c>
-      <c r="B61" s="20"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="20"/>
-      <c r="I61" s="20"/>
-      <c r="J61" s="20"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="21"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="21"/>
+      <c r="H61" s="21"/>
+      <c r="I61" s="21"/>
+      <c r="J61" s="21"/>
     </row>
     <row r="62" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="20" t="s">
+      <c r="A62" s="21" t="s">
         <v>516</v>
       </c>
-      <c r="B62" s="20"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="21"/>
     </row>
     <row r="63" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="20" t="s">
+      <c r="A63" s="21" t="s">
         <v>517</v>
       </c>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="20"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="21"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="21"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="21"/>
+      <c r="H63" s="21"/>
+      <c r="I63" s="21"/>
+      <c r="J63" s="21"/>
     </row>
     <row r="65" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="21" t="s">
+      <c r="A65" s="20" t="s">
         <v>518</v>
       </c>
-      <c r="B65" s="21"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
-      <c r="I65" s="21"/>
-      <c r="J65" s="21"/>
+      <c r="B65" s="20"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
     </row>
     <row r="67" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="20" t="s">
+      <c r="A67" s="21" t="s">
         <v>519</v>
       </c>
-      <c r="B67" s="20"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="20"/>
-      <c r="I67" s="20"/>
-      <c r="J67" s="20"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21"/>
+      <c r="H67" s="21"/>
+      <c r="I67" s="21"/>
+      <c r="J67" s="21"/>
     </row>
     <row r="68" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="20" t="s">
+      <c r="A68" s="21" t="s">
         <v>520</v>
       </c>
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
-      <c r="J68" s="20"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
     </row>
     <row r="69" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="20" t="s">
+      <c r="A69" s="21" t="s">
         <v>521</v>
       </c>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
-      <c r="J69" s="20"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
     </row>
     <row r="70" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="20" t="s">
+      <c r="A70" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
-      <c r="J70" s="20"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="21"/>
+      <c r="D70" s="21"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="21"/>
+      <c r="H70" s="21"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="21"/>
     </row>
     <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="20" t="s">
+      <c r="A71" s="21" t="s">
         <v>523</v>
       </c>
-      <c r="B71" s="20"/>
-      <c r="C71" s="20"/>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
-      <c r="J71" s="20"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="21"/>
+      <c r="H71" s="21"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="21"/>
     </row>
     <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="20" t="s">
+      <c r="A72" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="B72" s="20"/>
-      <c r="C72" s="20"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
-      <c r="J72" s="20"/>
+      <c r="B72" s="21"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="21"/>
+      <c r="H72" s="21"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="21"/>
     </row>
     <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="20" t="s">
+      <c r="A73" s="21" t="s">
         <v>525</v>
       </c>
-      <c r="B73" s="20"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
-      <c r="J73" s="20"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="21"/>
     </row>
     <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="20" t="s">
+      <c r="A74" s="21" t="s">
         <v>526</v>
       </c>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
-      <c r="J74" s="20"/>
+      <c r="B74" s="21"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="21"/>
+      <c r="H74" s="21"/>
+      <c r="I74" s="21"/>
+      <c r="J74" s="21"/>
     </row>
     <row r="76" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="21" t="s">
+      <c r="A76" s="20" t="s">
         <v>527</v>
       </c>
-      <c r="B76" s="21"/>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="20"/>
+      <c r="I76" s="20"/>
+      <c r="J76" s="20"/>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="19" t="s">
@@ -24632,66 +24947,66 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="A80:J80"/>
+    <mergeCell ref="A81:J81"/>
+    <mergeCell ref="A82:J82"/>
+    <mergeCell ref="A83:J83"/>
+    <mergeCell ref="A84:J84"/>
+    <mergeCell ref="A73:J73"/>
+    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="A78:J78"/>
+    <mergeCell ref="A79:J79"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="A69:J69"/>
+    <mergeCell ref="A70:J70"/>
+    <mergeCell ref="A71:J71"/>
+    <mergeCell ref="A72:J72"/>
+    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="A62:J62"/>
+    <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A67:J67"/>
+    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="A57:J57"/>
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A17:J17"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A7:J7"/>
     <mergeCell ref="A8:J8"/>
     <mergeCell ref="A9:J9"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A20:J20"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A39:J39"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="A42:J42"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A44:J44"/>
-    <mergeCell ref="A45:J45"/>
-    <mergeCell ref="A46:J46"/>
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A49:J49"/>
-    <mergeCell ref="A51:J51"/>
-    <mergeCell ref="A52:J52"/>
-    <mergeCell ref="A54:J54"/>
-    <mergeCell ref="A56:J56"/>
-    <mergeCell ref="A57:J57"/>
-    <mergeCell ref="A58:J58"/>
-    <mergeCell ref="A59:J59"/>
-    <mergeCell ref="A60:J60"/>
-    <mergeCell ref="A61:J61"/>
-    <mergeCell ref="A62:J62"/>
-    <mergeCell ref="A63:J63"/>
-    <mergeCell ref="A65:J65"/>
-    <mergeCell ref="A67:J67"/>
-    <mergeCell ref="A68:J68"/>
-    <mergeCell ref="A69:J69"/>
-    <mergeCell ref="A70:J70"/>
-    <mergeCell ref="A71:J71"/>
-    <mergeCell ref="A72:J72"/>
-    <mergeCell ref="A73:J73"/>
-    <mergeCell ref="A74:J74"/>
-    <mergeCell ref="A76:J76"/>
-    <mergeCell ref="A78:J78"/>
-    <mergeCell ref="A79:J79"/>
-    <mergeCell ref="A80:J80"/>
-    <mergeCell ref="A81:J81"/>
-    <mergeCell ref="A82:J82"/>
-    <mergeCell ref="A83:J83"/>
-    <mergeCell ref="A84:J84"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -24993,7 +25308,7 @@
         <v>557</v>
       </c>
       <c r="C12" s="11">
-        <f>IF(OR($B$3="",$D$3=""),0,MAX(IF($H$8&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH($H$8,'Data-Input'!$A$164:$A$185,0),MATCH($K$7,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND($H$8&lt;&gt;"",$K$8&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH($H$8,'Data-Input'!$A$164:$A$185,0),MATCH($K$8,'Data-Input'!$B$163:$W$163,0)),0),0),IF($H$9&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH($H$9,'Data-Input'!$A$164:$A$185,0),MATCH($K$7,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND($H$9&lt;&gt;"",$K$8&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH($H$9,'Data-Input'!$A$164:$A$185,0),MATCH($K$8,'Data-Input'!$B$163:$W$163,0)),0),0))*$N$6)</f>
+        <f>IF(OR($B$3="",$D$3=""),0,MAX(IF($H$8&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH($H$8,'Data-Input'!$A$165:$A$186,0),MATCH($K$7,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND($H$8&lt;&gt;"",$K$8&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH($H$8,'Data-Input'!$A$165:$A$186,0),MATCH($K$8,'Data-Input'!$B$164:$W$164,0)),0),0),IF($H$9&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH($H$9,'Data-Input'!$A$165:$A$186,0),MATCH($K$7,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND($H$9&lt;&gt;"",$K$8&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH($H$9,'Data-Input'!$A$165:$A$186,0),MATCH($K$8,'Data-Input'!$B$164:$W$164,0)),0),0))*$N$6)</f>
         <v>0</v>
       </c>
       <c r="G12" t="s">
@@ -25023,7 +25338,7 @@
         <v>560</v>
       </c>
       <c r="C13">
-        <f>IF(OR($B$3="",$D$3=""),0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=$B$3)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$7)+('Data-Input'!$C$29:$C$128=$K$8))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=$B$3)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$D$3)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=$B$3)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$K$3)+('Data-Input'!$C$29:$C$128=$K$4))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=$B$3)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$K$9)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=$B$3)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$K$11)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF(OR($B$3="",$D$3=""),0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=$B$3)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$7)+('Data-Input'!$C$29:$C$129=$K$8))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=$B$3)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$D$3)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=$B$3)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$K$3)+('Data-Input'!$C$29:$C$129=$K$4))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=$B$3)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$K$9)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=$B$3)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$K$11)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
     </row>
@@ -25059,7 +25374,7 @@
         <v>564</v>
       </c>
       <c r="C17" s="3">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH($B$3&amp;"|"&amp;$D$3,'Data-Input'!$E$190:$E$1189,0)),"None")</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH($B$3&amp;"|"&amp;$D$3,'Data-Input'!$E$191:$E$1190,0)),"None")</f>
         <v>0</v>
       </c>
     </row>
@@ -25140,11 +25455,11 @@
     <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" t="str">
         <f>IFERROR(INDEX(LookupCalc!$A$2:$A$134,MATCH(LARGE(LookupCalc!$T$2:$T$134,ROW()-2),LookupCalc!$T$2:$T$134,0)),"")</f>
-        <v>Harley</v>
+        <v>Hilda</v>
       </c>
       <c r="C4">
         <f>IFERROR(ROUND(LARGE(LookupCalc!$T$2:$T$134,ROW()-2),2),"")</f>
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -25160,11 +25475,11 @@
     <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" t="str">
         <f>IFERROR(INDEX(LookupCalc!$A$2:$A$134,MATCH(LARGE(LookupCalc!$T$2:$T$134,ROW()-2),LookupCalc!$T$2:$T$134,0)),"")</f>
-        <v>Hilda</v>
+        <v>Saber</v>
       </c>
       <c r="C6">
         <f>IFERROR(ROUND(LARGE(LookupCalc!$T$2:$T$134,ROW()-2),2),"")</f>
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -25194,31 +25509,31 @@
     <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" t="str">
         <f>IFERROR(INDEX(LookupCalc!$A$2:$A$134,MATCH(LARGE(LookupCalc!$V$2:$V$134,ROW()-10),LookupCalc!$V$2:$V$134,0)),"")</f>
-        <v>Harley</v>
+        <v>Saber</v>
       </c>
       <c r="C11">
         <f>IFERROR(ROUND(LARGE(LookupCalc!$V$2:$V$134,ROW()-10),2),"")</f>
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" t="str">
         <f>IFERROR(INDEX(LookupCalc!$A$2:$A$134,MATCH(LARGE(LookupCalc!$V$2:$V$134,ROW()-10),LookupCalc!$V$2:$V$134,0)),"")</f>
-        <v>Julian</v>
+        <v>Harley</v>
       </c>
       <c r="C12">
         <f>IFERROR(ROUND(LARGE(LookupCalc!$V$2:$V$134,ROW()-10),2),"")</f>
-        <v>14.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" t="str">
         <f>IFERROR(INDEX(LookupCalc!$A$2:$A$134,MATCH(LARGE(LookupCalc!$V$2:$V$134,ROW()-10),LookupCalc!$V$2:$V$134,0)),"")</f>
-        <v>Saber</v>
+        <v>Julian</v>
       </c>
       <c r="C13">
         <f>IFERROR(ROUND(LARGE(LookupCalc!$V$2:$V$134,ROW()-10),2),"")</f>
-        <v>14</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -25445,7 +25760,7 @@
         <v>2.5</v>
       </c>
       <c r="R2">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A2&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q2)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A2&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q2)</f>
         <v>2.5</v>
       </c>
       <c r="S2">
@@ -25473,11 +25788,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y2">
-        <f>IF($A$1="",0,MAX(IF(W2&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W2,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W2&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W2,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X2&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X2,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X2&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X2,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W2&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W2,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W2&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W2,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X2&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X2,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X2&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X2,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z2">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A2)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A2)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A2)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A2)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A2)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A2)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A2)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A2)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A2)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A2)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE2" t="str">
@@ -25563,7 +25878,7 @@
         <v>-1.5</v>
       </c>
       <c r="R3">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A3&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q3)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A3&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q3)</f>
         <v>-1.5</v>
       </c>
       <c r="S3">
@@ -25591,11 +25906,11 @@
         <v>Execute</v>
       </c>
       <c r="Y3">
-        <f>IF($A$1="",0,MAX(IF(W3&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W3,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W3&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W3,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X3&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X3,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X3&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X3,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W3&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W3,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W3&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W3,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X3&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X3,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X3&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X3,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A3)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A3)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A3)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A3)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A3)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A3)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A3)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A3)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A3)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A3)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE3" t="str">
@@ -25678,19 +25993,19 @@
       </c>
       <c r="Q4">
         <f t="shared" si="6"/>
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="R4">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A4&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q4)</f>
-        <v>14</v>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A4&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q4)</f>
+        <v>30</v>
       </c>
       <c r="S4">
         <f t="shared" si="7"/>
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="T4">
         <f t="shared" si="8"/>
-        <v>14.000000399999999</v>
+        <v>30.000000400000001</v>
       </c>
       <c r="U4" t="str">
         <f>Heroes!$M4</f>
@@ -25698,7 +26013,7 @@
       </c>
       <c r="V4">
         <f t="shared" si="9"/>
-        <v>14.000000399999999</v>
+        <v>30.000000400000001</v>
       </c>
       <c r="W4" t="str">
         <f>Heroes!$I4</f>
@@ -25709,12 +26024,12 @@
         <v>Targeted CC</v>
       </c>
       <c r="Y4">
-        <f>IF($A$1="",0,MAX(IF(W4&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W4,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W4&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W4,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X4&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X4,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X4&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X4,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W4&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W4,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W4&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W4,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X4&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X4,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X4&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X4,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z4">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A4)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A4)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A4)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A4)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A4)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
-        <v>20</v>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A4)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A4)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A4)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A4)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A4)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
+        <v>36</v>
       </c>
       <c r="AE4" t="str">
         <f>Heroes!$R4</f>
@@ -25799,7 +26114,7 @@
         <v>8</v>
       </c>
       <c r="R5">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A5&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q5)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A5&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q5)</f>
         <v>8</v>
       </c>
       <c r="S5">
@@ -25827,11 +26142,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y5">
-        <f>IF($A$1="",0,MAX(IF(W5&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W5,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W5&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W5,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X5&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X5,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X5&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X5,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W5&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W5,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W5&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W5,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X5&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X5,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X5&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X5,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z5">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A5)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A5)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A5)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A5)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A5)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A5)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A5)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A5)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A5)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A5)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE5" t="str">
@@ -25917,7 +26232,7 @@
         <v>4</v>
       </c>
       <c r="R6">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A6&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q6)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A6&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q6)</f>
         <v>4</v>
       </c>
       <c r="S6">
@@ -25945,11 +26260,11 @@
         <v>Soft CC</v>
       </c>
       <c r="Y6">
-        <f>IF($A$1="",0,MAX(IF(W6&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W6,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W6&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W6,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X6&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X6,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X6&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X6,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W6&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W6,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W6&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W6,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X6&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X6,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X6&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X6,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z6">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A6)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A6)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A6)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A6)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A6)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A6)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A6)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A6)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A6)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A6)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE6" t="str">
@@ -26035,7 +26350,7 @@
         <v>3.5</v>
       </c>
       <c r="R7">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A7&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q7)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A7&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q7)</f>
         <v>3.5</v>
       </c>
       <c r="S7">
@@ -26063,11 +26378,11 @@
         <v>Hard CC</v>
       </c>
       <c r="Y7">
-        <f>IF($A$1="",0,MAX(IF(W7&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W7,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W7&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W7,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X7&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X7,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X7&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X7,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W7&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W7,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W7&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W7,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X7&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X7,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X7&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X7,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z7">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A7)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A7)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A7)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A7)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A7)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A7)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A7)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A7)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A7)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A7)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE7" t="str">
@@ -26153,7 +26468,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A8&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q8)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A8&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q8)</f>
         <v>-1</v>
       </c>
       <c r="S8">
@@ -26181,11 +26496,11 @@
         <v>DPS</v>
       </c>
       <c r="Y8">
-        <f>IF($A$1="",0,MAX(IF(W8&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W8,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W8&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W8,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X8&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X8,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X8&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X8,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W8&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W8,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W8&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W8,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X8&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X8,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X8&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X8,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A8)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A8)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A8)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A8)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A8)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A8)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A8)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A8)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A8)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A8)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE8" t="str">
@@ -26271,7 +26586,7 @@
         <v>-3</v>
       </c>
       <c r="R9">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A9&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q9)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A9&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q9)</f>
         <v>-3</v>
       </c>
       <c r="S9">
@@ -26299,11 +26614,11 @@
         <v>Execute</v>
       </c>
       <c r="Y9">
-        <f>IF($A$1="",0,MAX(IF(W9&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W9,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W9&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W9,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X9&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X9,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X9&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X9,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W9&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W9,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W9&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W9,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X9&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X9,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X9&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X9,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z9">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A9)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A9)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A9)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A9)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A9)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A9)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A9)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A9)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A9)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A9)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE9" t="str">
@@ -26389,7 +26704,7 @@
         <v>9</v>
       </c>
       <c r="R10">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A10&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q10)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A10&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q10)</f>
         <v>9</v>
       </c>
       <c r="S10">
@@ -26417,11 +26732,11 @@
         <v>Shield</v>
       </c>
       <c r="Y10">
-        <f>IF($A$1="",0,MAX(IF(W10&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W10,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W10&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W10,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X10&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X10,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X10&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X10,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W10&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W10,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W10&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W10,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X10&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X10,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X10&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X10,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z10">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A10)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A10)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A10)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A10)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A10)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A10)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A10)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A10)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A10)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A10)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE10" t="str">
@@ -26507,7 +26822,7 @@
         <v>3.5</v>
       </c>
       <c r="R11">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A11&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q11)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A11&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q11)</f>
         <v>3.5</v>
       </c>
       <c r="S11">
@@ -26535,11 +26850,11 @@
         <v>Hard CC</v>
       </c>
       <c r="Y11">
-        <f>IF($A$1="",0,MAX(IF(W11&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W11,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W11&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W11,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X11&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X11,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X11&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X11,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W11&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W11,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W11&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W11,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X11&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X11,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X11&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X11,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z11">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A11)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A11)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A11)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A11)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A11)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A11)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A11)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A11)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A11)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A11)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE11" t="str">
@@ -26625,7 +26940,7 @@
         <v>8</v>
       </c>
       <c r="R12">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A12&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q12)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A12&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q12)</f>
         <v>8</v>
       </c>
       <c r="S12">
@@ -26653,11 +26968,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y12">
-        <f>IF($A$1="",0,MAX(IF(W12&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W12,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W12&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W12,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X12&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X12,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X12&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X12,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W12&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W12,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W12&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W12,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X12&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X12,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X12&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X12,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z12">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A12)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A12)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A12)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A12)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A12)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A12)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A12)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A12)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A12)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A12)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE12" t="str">
@@ -26743,7 +27058,7 @@
         <v>1</v>
       </c>
       <c r="R13">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A13&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q13)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A13&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q13)</f>
         <v>1</v>
       </c>
       <c r="S13">
@@ -26771,11 +27086,11 @@
         <v>Burst</v>
       </c>
       <c r="Y13">
-        <f>IF($A$1="",0,MAX(IF(W13&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W13,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W13&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W13,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X13&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X13,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X13&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X13,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W13&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W13,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W13&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W13,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X13&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X13,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X13&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X13,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z13">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A13)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A13)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A13)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A13)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A13)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A13)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A13)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A13)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A13)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A13)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE13" t="str">
@@ -26861,7 +27176,7 @@
         <v>-0.5</v>
       </c>
       <c r="R14">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A14&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q14)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A14&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q14)</f>
         <v>-0.5</v>
       </c>
       <c r="S14">
@@ -26889,11 +27204,11 @@
         <v>Poke</v>
       </c>
       <c r="Y14">
-        <f>IF($A$1="",0,MAX(IF(W14&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W14,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W14&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W14,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X14&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X14,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X14&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X14,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W14&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W14,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W14&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W14,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X14&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X14,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X14&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X14,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z14">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A14)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A14)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A14)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A14)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A14)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A14)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A14)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A14)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A14)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A14)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE14" t="str">
@@ -26979,7 +27294,7 @@
         <v>-2.5</v>
       </c>
       <c r="R15">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A15&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q15)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A15&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q15)</f>
         <v>-2.5</v>
       </c>
       <c r="S15">
@@ -27007,11 +27322,11 @@
         <v>Soft CC</v>
       </c>
       <c r="Y15">
-        <f>IF($A$1="",0,MAX(IF(W15&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W15,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W15&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W15,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X15&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X15,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X15&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X15,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W15&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W15,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W15&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W15,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X15&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X15,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X15&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X15,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z15">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A15)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A15)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A15)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A15)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A15)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A15)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A15)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A15)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A15)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A15)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE15" t="str">
@@ -27097,7 +27412,7 @@
         <v>4</v>
       </c>
       <c r="R16">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A16&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q16)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A16&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q16)</f>
         <v>4</v>
       </c>
       <c r="S16">
@@ -27125,11 +27440,11 @@
         <v>Targeted CC</v>
       </c>
       <c r="Y16">
-        <f>IF($A$1="",0,MAX(IF(W16&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W16,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W16&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W16,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X16&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X16,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X16&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X16,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W16&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W16,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W16&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W16,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X16&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X16,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X16&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X16,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z16">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A16)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A16)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A16)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A16)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A16)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A16)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A16)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A16)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A16)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A16)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE16" t="str">
@@ -27215,7 +27530,7 @@
         <v>1.5</v>
       </c>
       <c r="R17">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A17&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q17)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A17&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q17)</f>
         <v>1.5</v>
       </c>
       <c r="S17">
@@ -27243,11 +27558,11 @@
         <v>Mobility</v>
       </c>
       <c r="Y17">
-        <f>IF($A$1="",0,MAX(IF(W17&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W17,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W17&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W17,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X17&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X17,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X17&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X17,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W17&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W17,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W17&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W17,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X17&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X17,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X17&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X17,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z17">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A17)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A17)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A17)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A17)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A17)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A17)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A17)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A17)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A17)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A17)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE17" t="str">
@@ -27333,7 +27648,7 @@
         <v>-11</v>
       </c>
       <c r="R18">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A18&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q18)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A18&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q18)</f>
         <v>-11</v>
       </c>
       <c r="S18">
@@ -27361,11 +27676,11 @@
         <v>Burst</v>
       </c>
       <c r="Y18">
-        <f>IF($A$1="",0,MAX(IF(W18&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W18,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W18&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W18,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X18&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X18,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X18&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X18,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W18&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W18,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W18&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W18,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X18&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X18,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X18&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X18,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z18">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A18)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A18)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A18)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A18)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A18)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A18)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A18)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A18)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A18)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A18)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE18" t="str">
@@ -27451,7 +27766,7 @@
         <v>1.5</v>
       </c>
       <c r="R19">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A19&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q19)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A19&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q19)</f>
         <v>1.5</v>
       </c>
       <c r="S19">
@@ -27479,11 +27794,11 @@
         <v>Poke</v>
       </c>
       <c r="Y19">
-        <f>IF($A$1="",0,MAX(IF(W19&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W19,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W19&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W19,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X19&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X19,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X19&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X19,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W19&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W19,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W19&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W19,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X19&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X19,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X19&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X19,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z19">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A19)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A19)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A19)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A19)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A19)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A19)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A19)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A19)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A19)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A19)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE19" t="str">
@@ -27569,7 +27884,7 @@
         <v>5.5</v>
       </c>
       <c r="R20">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A20&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q20)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A20&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q20)</f>
         <v>5.5</v>
       </c>
       <c r="S20">
@@ -27597,11 +27912,11 @@
         <v>Healing</v>
       </c>
       <c r="Y20">
-        <f>IF($A$1="",0,MAX(IF(W20&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W20,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W20&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W20,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X20&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X20,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X20&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X20,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W20&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W20,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W20&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W20,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X20&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X20,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X20&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X20,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z20">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A20)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A20)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A20)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A20)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A20)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A20)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A20)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A20)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A20)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A20)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE20" t="str">
@@ -27687,7 +28002,7 @@
         <v>11</v>
       </c>
       <c r="R21">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A21&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q21)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A21&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q21)</f>
         <v>11</v>
       </c>
       <c r="S21">
@@ -27715,11 +28030,11 @@
         <v>AoE CC</v>
       </c>
       <c r="Y21">
-        <f>IF($A$1="",0,MAX(IF(W21&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W21,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W21&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W21,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X21&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X21,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X21&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X21,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W21&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W21,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W21&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W21,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X21&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X21,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X21&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X21,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z21">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A21)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A21)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A21)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A21)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A21)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A21)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A21)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A21)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A21)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A21)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE21" t="str">
@@ -27805,7 +28120,7 @@
         <v>1</v>
       </c>
       <c r="R22">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A22&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q22)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A22&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q22)</f>
         <v>1</v>
       </c>
       <c r="S22">
@@ -27833,11 +28148,11 @@
         <v>I-Frame</v>
       </c>
       <c r="Y22">
-        <f>IF($A$1="",0,MAX(IF(W22&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W22,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W22&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W22,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X22&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X22,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X22&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X22,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W22&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W22,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W22&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W22,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X22&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X22,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X22&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X22,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>10</v>
       </c>
       <c r="Z22">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A22)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A22)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A22)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A22)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A22)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A22)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A22)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A22)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A22)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A22)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE22" t="str">
@@ -27923,7 +28238,7 @@
         <v>6</v>
       </c>
       <c r="R23">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A23&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q23)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A23&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q23)</f>
         <v>6</v>
       </c>
       <c r="S23">
@@ -27951,11 +28266,11 @@
         <v>DPS</v>
       </c>
       <c r="Y23">
-        <f>IF($A$1="",0,MAX(IF(W23&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W23,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W23&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W23,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X23&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X23,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X23&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X23,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W23&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W23,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W23&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W23,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X23&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X23,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X23&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X23,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z23">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A23)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A23)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A23)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A23)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A23)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A23)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A23)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A23)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A23)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A23)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE23" t="str">
@@ -28041,7 +28356,7 @@
         <v>3.5</v>
       </c>
       <c r="R24">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A24&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q24)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A24&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q24)</f>
         <v>3.5</v>
       </c>
       <c r="S24">
@@ -28069,11 +28384,11 @@
         <v>Poke</v>
       </c>
       <c r="Y24">
-        <f>IF($A$1="",0,MAX(IF(W24&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W24,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W24&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W24,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X24&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X24,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X24&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X24,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W24&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W24,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W24&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W24,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X24&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X24,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X24&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X24,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z24">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A24)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A24)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A24)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A24)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A24)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A24)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A24)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A24)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A24)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A24)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE24" t="str">
@@ -28159,7 +28474,7 @@
         <v>-6</v>
       </c>
       <c r="R25">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A25&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q25)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A25&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q25)</f>
         <v>-6</v>
       </c>
       <c r="S25">
@@ -28187,11 +28502,11 @@
         <v>Vision</v>
       </c>
       <c r="Y25">
-        <f>IF($A$1="",0,MAX(IF(W25&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W25,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W25&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W25,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X25&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X25,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X25&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X25,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W25&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W25,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W25&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W25,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X25&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X25,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X25&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X25,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z25">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A25)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A25)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A25)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A25)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A25)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A25)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A25)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A25)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A25)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A25)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE25" t="str">
@@ -28277,7 +28592,7 @@
         <v>2.5</v>
       </c>
       <c r="R26">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A26&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q26)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A26&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q26)</f>
         <v>2.5</v>
       </c>
       <c r="S26">
@@ -28305,11 +28620,11 @@
         <v>Burst</v>
       </c>
       <c r="Y26">
-        <f>IF($A$1="",0,MAX(IF(W26&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W26,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W26&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W26,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X26&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X26,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X26&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X26,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W26&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W26,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W26&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W26,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X26&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X26,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X26&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X26,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z26">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A26)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A26)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A26)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A26)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A26)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A26)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A26)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A26)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A26)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A26)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE26" t="str">
@@ -28395,7 +28710,7 @@
         <v>-4.5</v>
       </c>
       <c r="R27">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A27&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q27)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A27&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q27)</f>
         <v>-4.5</v>
       </c>
       <c r="S27">
@@ -28423,11 +28738,11 @@
         <v>Dash/Blink</v>
       </c>
       <c r="Y27">
-        <f>IF($A$1="",0,MAX(IF(W27&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W27,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W27&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W27,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X27&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X27,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X27&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X27,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W27&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W27,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W27&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W27,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X27&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X27,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X27&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X27,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z27">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A27)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A27)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A27)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A27)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A27)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A27)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A27)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A27)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A27)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A27)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE27" t="str">
@@ -28513,7 +28828,7 @@
         <v>-4</v>
       </c>
       <c r="R28">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A28&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q28)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A28&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q28)</f>
         <v>-4</v>
       </c>
       <c r="S28">
@@ -28541,11 +28856,11 @@
         <v>DPS</v>
       </c>
       <c r="Y28">
-        <f>IF($A$1="",0,MAX(IF(W28&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W28,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W28&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W28,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X28&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X28,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X28&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X28,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W28&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W28,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W28&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W28,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X28&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X28,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X28&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X28,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z28">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A28)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A28)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A28)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A28)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A28)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A28)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A28)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A28)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A28)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A28)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE28" t="str">
@@ -28631,7 +28946,7 @@
         <v>1.5</v>
       </c>
       <c r="R29">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A29&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q29)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A29&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q29)</f>
         <v>1.5</v>
       </c>
       <c r="S29">
@@ -28659,11 +28974,11 @@
         <v>True Damage</v>
       </c>
       <c r="Y29">
-        <f>IF($A$1="",0,MAX(IF(W29&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W29,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W29&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W29,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X29&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X29,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X29&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X29,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W29&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W29,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W29&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W29,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X29&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X29,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X29&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X29,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z29">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A29)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A29)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A29)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A29)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A29)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A29)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A29)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A29)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A29)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A29)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE29" t="str">
@@ -28749,7 +29064,7 @@
         <v>4.5</v>
       </c>
       <c r="R30">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A30&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q30)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A30&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q30)</f>
         <v>4.5</v>
       </c>
       <c r="S30">
@@ -28777,11 +29092,11 @@
         <v>AoE CC</v>
       </c>
       <c r="Y30">
-        <f>IF($A$1="",0,MAX(IF(W30&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W30,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W30&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W30,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X30&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X30,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X30&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X30,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W30&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W30,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W30&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W30,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X30&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X30,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X30&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X30,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z30">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A30)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A30)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A30)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A30)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A30)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A30)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A30)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A30)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A30)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A30)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE30" t="str">
@@ -28867,7 +29182,7 @@
         <v>-0.5</v>
       </c>
       <c r="R31">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A31&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q31)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A31&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q31)</f>
         <v>-0.5</v>
       </c>
       <c r="S31">
@@ -28895,11 +29210,11 @@
         <v>DPS</v>
       </c>
       <c r="Y31">
-        <f>IF($A$1="",0,MAX(IF(W31&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W31,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W31&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W31,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X31&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X31,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X31&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X31,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W31&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W31,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W31&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W31,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X31&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X31,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X31&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X31,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z31">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A31)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A31)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A31)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A31)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A31)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A31)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A31)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A31)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A31)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A31)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE31" t="str">
@@ -28985,7 +29300,7 @@
         <v>3</v>
       </c>
       <c r="R32">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A32&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q32)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A32&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q32)</f>
         <v>3</v>
       </c>
       <c r="S32">
@@ -29013,11 +29328,11 @@
         <v>Hard CC</v>
       </c>
       <c r="Y32">
-        <f>IF($A$1="",0,MAX(IF(W32&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W32,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W32&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W32,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X32&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X32,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X32&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X32,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W32&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W32,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W32&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W32,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X32&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X32,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X32&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X32,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z32">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A32)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A32)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A32)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A32)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A32)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A32)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A32)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A32)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A32)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A32)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE32" t="str">
@@ -29103,7 +29418,7 @@
         <v>9</v>
       </c>
       <c r="R33">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A33&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q33)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A33&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q33)</f>
         <v>9</v>
       </c>
       <c r="S33">
@@ -29131,11 +29446,11 @@
         <v>AoE CC</v>
       </c>
       <c r="Y33">
-        <f>IF($A$1="",0,MAX(IF(W33&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W33,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W33&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W33,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X33&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X33,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X33&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X33,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W33&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W33,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W33&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W33,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X33&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X33,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X33&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X33,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z33">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A33)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A33)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A33)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A33)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A33)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A33)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A33)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A33)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A33)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A33)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE33" t="str">
@@ -29221,7 +29536,7 @@
         <v>4.5</v>
       </c>
       <c r="R34">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A34&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q34)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A34&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q34)</f>
         <v>4.5</v>
       </c>
       <c r="S34">
@@ -29249,11 +29564,11 @@
         <v>Targeted CC</v>
       </c>
       <c r="Y34">
-        <f>IF($A$1="",0,MAX(IF(W34&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W34,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W34&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W34,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X34&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X34,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X34&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X34,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W34&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W34,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W34&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W34,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X34&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X34,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X34&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X34,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z34">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A34)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A34)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A34)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A34)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A34)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A34)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A34)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A34)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A34)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A34)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE34" t="str">
@@ -29336,19 +29651,19 @@
       </c>
       <c r="Q35">
         <f t="shared" si="18"/>
-        <v>-5.5</v>
+        <v>10.5</v>
       </c>
       <c r="R35">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A35&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q35)</f>
-        <v>-5.5</v>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A35&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q35)</f>
+        <v>10.5</v>
       </c>
       <c r="S35">
         <f t="shared" si="19"/>
-        <v>-5.5</v>
+        <v>10.5</v>
       </c>
       <c r="T35">
         <f t="shared" si="20"/>
-        <v>-5.4999965</v>
+        <v>10.5000035</v>
       </c>
       <c r="U35" t="str">
         <f>Heroes!$M35</f>
@@ -29367,12 +29682,12 @@
         <v>Sustain</v>
       </c>
       <c r="Y35">
-        <f>IF($A$1="",0,MAX(IF(W35&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W35,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W35&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W35,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X35&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X35,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X35&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X35,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W35&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W35,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W35&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W35,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X35&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X35,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X35&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X35,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z35">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A35)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A35)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A35)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A35)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A35)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
-        <v>0</v>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A35)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A35)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A35)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A35)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A35)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
+        <v>16</v>
       </c>
       <c r="AE35" t="str">
         <f>Heroes!$R35</f>
@@ -29454,19 +29769,19 @@
       </c>
       <c r="Q36">
         <f t="shared" si="18"/>
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="R36">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A36&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q36)</f>
-        <v>27</v>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A36&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q36)</f>
+        <v>39</v>
       </c>
       <c r="S36">
         <f t="shared" si="19"/>
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="T36">
         <f t="shared" si="20"/>
-        <v>27.000003599999999</v>
+        <v>39.000003599999999</v>
       </c>
       <c r="U36" t="str">
         <f>Heroes!$M36</f>
@@ -29485,12 +29800,12 @@
         <v>Burst</v>
       </c>
       <c r="Y36">
-        <f>IF($A$1="",0,MAX(IF(W36&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W36,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W36&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W36,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X36&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X36,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X36&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X36,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W36&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W36,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W36&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W36,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X36&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X36,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X36&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X36,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z36">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A36)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A36)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A36)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A36)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A36)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
-        <v>28</v>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A36)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A36)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A36)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A36)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A36)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
+        <v>40</v>
       </c>
       <c r="AE36" t="str">
         <f>Heroes!$R36</f>
@@ -29575,7 +29890,7 @@
         <v>4.5</v>
       </c>
       <c r="R37">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A37&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q37)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A37&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q37)</f>
         <v>4.5</v>
       </c>
       <c r="S37">
@@ -29603,11 +29918,11 @@
         <v>Burst</v>
       </c>
       <c r="Y37">
-        <f>IF($A$1="",0,MAX(IF(W37&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W37,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W37&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W37,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X37&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X37,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X37&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X37,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W37&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W37,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W37&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W37,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X37&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X37,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X37&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X37,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z37">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A37)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A37)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A37)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A37)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A37)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A37)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A37)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A37)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A37)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A37)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE37" t="str">
@@ -29693,7 +30008,7 @@
         <v>5</v>
       </c>
       <c r="R38">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A38&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q38)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A38&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q38)</f>
         <v>5</v>
       </c>
       <c r="S38">
@@ -29721,11 +30036,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y38">
-        <f>IF($A$1="",0,MAX(IF(W38&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W38,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W38&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W38,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X38&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X38,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X38&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X38,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W38&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W38,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W38&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W38,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X38&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X38,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X38&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X38,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z38">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A38)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A38)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A38)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A38)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A38)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A38)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A38)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A38)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A38)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A38)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE38" t="str">
@@ -29811,7 +30126,7 @@
         <v>3</v>
       </c>
       <c r="R39">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A39&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q39)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A39&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q39)</f>
         <v>3</v>
       </c>
       <c r="S39">
@@ -29839,11 +30154,11 @@
         <v>AoE CC</v>
       </c>
       <c r="Y39">
-        <f>IF($A$1="",0,MAX(IF(W39&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W39,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W39&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W39,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X39&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X39,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X39&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X39,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W39&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W39,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W39&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W39,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X39&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X39,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X39&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X39,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z39">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A39)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A39)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A39)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A39)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A39)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A39)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A39)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A39)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A39)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A39)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE39" t="str">
@@ -29929,7 +30244,7 @@
         <v>-1.5</v>
       </c>
       <c r="R40">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A40&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q40)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A40&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q40)</f>
         <v>-1.5</v>
       </c>
       <c r="S40">
@@ -29957,11 +30272,11 @@
         <v>Mobility</v>
       </c>
       <c r="Y40">
-        <f>IF($A$1="",0,MAX(IF(W40&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W40,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W40&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W40,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X40&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X40,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X40&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X40,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W40&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W40,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W40&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W40,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X40&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X40,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X40&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X40,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z40">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A40)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A40)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A40)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A40)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A40)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A40)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A40)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A40)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A40)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A40)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE40" t="str">
@@ -30047,7 +30362,7 @@
         <v>1.5</v>
       </c>
       <c r="R41">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A41&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q41)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A41&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q41)</f>
         <v>1.5</v>
       </c>
       <c r="S41">
@@ -30075,11 +30390,11 @@
         <v>DPS</v>
       </c>
       <c r="Y41">
-        <f>IF($A$1="",0,MAX(IF(W41&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W41,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W41&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W41,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X41&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X41,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X41&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X41,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W41&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W41,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W41&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W41,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X41&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X41,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X41&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X41,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z41">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A41)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A41)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A41)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A41)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A41)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A41)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A41)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A41)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A41)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A41)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE41" t="str">
@@ -30165,7 +30480,7 @@
         <v>41</v>
       </c>
       <c r="R42">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A42&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q42)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A42&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q42)</f>
         <v>41</v>
       </c>
       <c r="S42">
@@ -30193,11 +30508,11 @@
         <v>Damage Reduction</v>
       </c>
       <c r="Y42">
-        <f>IF($A$1="",0,MAX(IF(W42&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W42,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W42&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W42,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X42&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X42,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X42&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X42,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W42&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W42,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W42&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W42,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X42&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X42,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X42&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X42,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z42">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A42)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A42)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A42)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A42)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A42)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A42)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A42)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A42)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A42)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A42)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>24</v>
       </c>
       <c r="AE42" t="str">
@@ -30280,19 +30595,19 @@
       </c>
       <c r="Q43">
         <f t="shared" si="18"/>
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="R43">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A43&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q43)</f>
-        <v>38</v>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A43&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q43)</f>
+        <v>24</v>
       </c>
       <c r="S43">
         <f t="shared" si="19"/>
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="T43">
         <f t="shared" si="20"/>
-        <v>38.000004300000001</v>
+        <v>24.000004300000001</v>
       </c>
       <c r="U43" t="str">
         <f>Heroes!$M43</f>
@@ -30300,7 +30615,7 @@
       </c>
       <c r="V43">
         <f t="shared" si="21"/>
-        <v>38.000004300000001</v>
+        <v>24.000004300000001</v>
       </c>
       <c r="W43" t="str">
         <f>Heroes!$I43</f>
@@ -30311,12 +30626,12 @@
         <v>Poke</v>
       </c>
       <c r="Y43">
-        <f>IF($A$1="",0,MAX(IF(W43&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W43,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W43&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W43,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X43&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X43,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X43&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X43,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W43&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W43,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W43&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W43,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X43&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X43,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X43&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X43,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z43">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A43)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A43)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A43)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A43)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A43)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
-        <v>40</v>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A43)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A43)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A43)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A43)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A43)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
+        <v>26</v>
       </c>
       <c r="AE43" t="str">
         <f>Heroes!$R43</f>
@@ -30401,7 +30716,7 @@
         <v>1.5</v>
       </c>
       <c r="R44">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A44&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q44)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A44&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q44)</f>
         <v>1.5</v>
       </c>
       <c r="S44">
@@ -30429,11 +30744,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y44">
-        <f>IF($A$1="",0,MAX(IF(W44&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W44,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W44&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W44,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X44&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X44,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X44&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X44,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W44&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W44,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W44&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W44,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X44&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X44,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X44&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X44,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z44">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A44)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A44)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A44)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A44)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A44)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A44)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A44)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A44)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A44)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A44)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE44" t="str">
@@ -30519,7 +30834,7 @@
         <v>4</v>
       </c>
       <c r="R45">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A45&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q45)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A45&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q45)</f>
         <v>4</v>
       </c>
       <c r="S45">
@@ -30547,11 +30862,11 @@
         <v>Burst</v>
       </c>
       <c r="Y45">
-        <f>IF($A$1="",0,MAX(IF(W45&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W45,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W45&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W45,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X45&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X45,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X45&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X45,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W45&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W45,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W45&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W45,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X45&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X45,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X45&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X45,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z45">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A45)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A45)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A45)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A45)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A45)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A45)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A45)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A45)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A45)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A45)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE45" t="str">
@@ -30637,7 +30952,7 @@
         <v>17</v>
       </c>
       <c r="R46">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A46&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q46)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A46&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q46)</f>
         <v>17</v>
       </c>
       <c r="S46">
@@ -30665,11 +30980,11 @@
         <v>DPS</v>
       </c>
       <c r="Y46">
-        <f>IF($A$1="",0,MAX(IF(W46&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W46,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W46&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W46,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X46&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X46,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X46&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X46,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W46&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W46,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W46&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W46,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X46&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X46,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X46&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X46,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>10</v>
       </c>
       <c r="Z46">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A46)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A46)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A46)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A46)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A46)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A46)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A46)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A46)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A46)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A46)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE46" t="str">
@@ -30755,7 +31070,7 @@
         <v>4.5</v>
       </c>
       <c r="R47">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A47&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q47)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A47&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q47)</f>
         <v>4.5</v>
       </c>
       <c r="S47">
@@ -30783,11 +31098,11 @@
         <v>Burst</v>
       </c>
       <c r="Y47">
-        <f>IF($A$1="",0,MAX(IF(W47&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W47,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W47&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W47,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X47&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X47,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X47&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X47,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W47&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W47,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W47&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W47,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X47&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X47,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X47&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X47,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z47">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A47)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A47)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A47)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A47)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A47)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A47)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A47)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A47)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A47)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A47)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE47" t="str">
@@ -30873,7 +31188,7 @@
         <v>1</v>
       </c>
       <c r="R48">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A48&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q48)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A48&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q48)</f>
         <v>1</v>
       </c>
       <c r="S48">
@@ -30901,11 +31216,11 @@
         <v>Dash/Blink</v>
       </c>
       <c r="Y48">
-        <f>IF($A$1="",0,MAX(IF(W48&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W48,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W48&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W48,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X48&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X48,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X48&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X48,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W48&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W48,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W48&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W48,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X48&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X48,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X48&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X48,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>10</v>
       </c>
       <c r="Z48">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A48)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A48)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A48)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A48)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A48)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A48)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A48)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A48)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A48)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A48)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE48" t="str">
@@ -30991,7 +31306,7 @@
         <v>1</v>
       </c>
       <c r="R49">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A49&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q49)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A49&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q49)</f>
         <v>1</v>
       </c>
       <c r="S49">
@@ -31019,11 +31334,11 @@
         <v>Shield</v>
       </c>
       <c r="Y49">
-        <f>IF($A$1="",0,MAX(IF(W49&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W49,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W49&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W49,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X49&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X49,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X49&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X49,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W49&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W49,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W49&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W49,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X49&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X49,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X49&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X49,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z49">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A49)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A49)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A49)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A49)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A49)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A49)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A49)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A49)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A49)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A49)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE49" t="str">
@@ -31109,7 +31424,7 @@
         <v>32</v>
       </c>
       <c r="R50">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A50&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q50)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A50&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q50)</f>
         <v>32</v>
       </c>
       <c r="S50">
@@ -31137,11 +31452,11 @@
         <v>Soft CC</v>
       </c>
       <c r="Y50">
-        <f>IF($A$1="",0,MAX(IF(W50&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W50,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W50&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W50,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X50&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X50,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X50&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X50,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W50&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W50,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W50&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W50,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X50&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X50,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X50&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X50,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z50">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A50)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A50)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A50)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A50)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A50)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A50)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A50)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A50)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A50)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A50)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>24</v>
       </c>
       <c r="AE50" t="str">
@@ -31224,19 +31539,19 @@
       </c>
       <c r="Q51">
         <f t="shared" si="18"/>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="R51">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A51&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q51)</f>
-        <v>19</v>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A51&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q51)</f>
+        <v>15</v>
       </c>
       <c r="S51">
         <f t="shared" si="19"/>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T51">
         <f t="shared" si="20"/>
-        <v>19.000005099999999</v>
+        <v>15.000005099999999</v>
       </c>
       <c r="U51" t="str">
         <f>Heroes!$M51</f>
@@ -31255,12 +31570,12 @@
         <v>DPS</v>
       </c>
       <c r="Y51">
-        <f>IF($A$1="",0,MAX(IF(W51&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W51,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W51&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W51,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X51&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X51,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X51&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X51,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W51&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W51,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W51&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W51,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X51&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X51,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X51&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X51,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z51">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A51)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A51)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A51)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A51)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A51)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
-        <v>16</v>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A51)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A51)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A51)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A51)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A51)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
+        <v>12</v>
       </c>
       <c r="AE51" t="str">
         <f>Heroes!$R51</f>
@@ -31345,7 +31660,7 @@
         <v>-7</v>
       </c>
       <c r="R52">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A52&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q52)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A52&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q52)</f>
         <v>-7</v>
       </c>
       <c r="S52">
@@ -31373,11 +31688,11 @@
         <v>Soft CC</v>
       </c>
       <c r="Y52">
-        <f>IF($A$1="",0,MAX(IF(W52&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W52,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W52&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W52,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X52&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X52,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X52&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X52,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W52&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W52,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W52&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W52,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X52&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X52,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X52&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X52,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z52">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A52)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A52)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A52)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A52)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A52)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A52)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A52)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A52)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A52)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A52)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE52" t="str">
@@ -31463,7 +31778,7 @@
         <v>3</v>
       </c>
       <c r="R53">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A53&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q53)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A53&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q53)</f>
         <v>3</v>
       </c>
       <c r="S53">
@@ -31491,11 +31806,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y53">
-        <f>IF($A$1="",0,MAX(IF(W53&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W53,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W53&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W53,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X53&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X53,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X53&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X53,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W53&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W53,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W53&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W53,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X53&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X53,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X53&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X53,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z53">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A53)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A53)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A53)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A53)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A53)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A53)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A53)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A53)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A53)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A53)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE53" t="str">
@@ -31581,7 +31896,7 @@
         <v>-1.5</v>
       </c>
       <c r="R54">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A54&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q54)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A54&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q54)</f>
         <v>-1.5</v>
       </c>
       <c r="S54">
@@ -31609,11 +31924,11 @@
         <v>True Damage</v>
       </c>
       <c r="Y54">
-        <f>IF($A$1="",0,MAX(IF(W54&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W54,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W54&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W54,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X54&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X54,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X54&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X54,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W54&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W54,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W54&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W54,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X54&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X54,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X54&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X54,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z54">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A54)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A54)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A54)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A54)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A54)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A54)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A54)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A54)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A54)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A54)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE54" t="str">
@@ -31699,7 +32014,7 @@
         <v>-2.5</v>
       </c>
       <c r="R55">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A55&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q55)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A55&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q55)</f>
         <v>-2.5</v>
       </c>
       <c r="S55">
@@ -31727,11 +32042,11 @@
         <v>Burst</v>
       </c>
       <c r="Y55">
-        <f>IF($A$1="",0,MAX(IF(W55&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W55,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W55&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W55,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X55&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X55,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X55&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X55,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W55&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W55,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W55&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W55,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X55&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X55,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X55&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X55,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z55">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A55)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A55)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A55)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A55)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A55)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A55)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A55)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A55)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A55)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A55)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE55" t="str">
@@ -31817,7 +32132,7 @@
         <v>4.5</v>
       </c>
       <c r="R56">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A56&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q56)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A56&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q56)</f>
         <v>4.5</v>
       </c>
       <c r="S56">
@@ -31845,11 +32160,11 @@
         <v>Healing</v>
       </c>
       <c r="Y56">
-        <f>IF($A$1="",0,MAX(IF(W56&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W56,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W56&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W56,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X56&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X56,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X56&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X56,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W56&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W56,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W56&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W56,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X56&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X56,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X56&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X56,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z56">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A56)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A56)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A56)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A56)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A56)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A56)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A56)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A56)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A56)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A56)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE56" t="str">
@@ -31935,7 +32250,7 @@
         <v>-2</v>
       </c>
       <c r="R57">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A57&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q57)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A57&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q57)</f>
         <v>-2</v>
       </c>
       <c r="S57">
@@ -31963,11 +32278,11 @@
         <v>Dash/Blink</v>
       </c>
       <c r="Y57">
-        <f>IF($A$1="",0,MAX(IF(W57&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W57,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W57&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W57,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X57&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X57,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X57&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X57,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W57&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W57,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W57&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W57,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X57&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X57,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X57&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X57,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z57">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A57)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A57)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A57)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A57)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A57)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A57)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A57)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A57)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A57)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A57)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE57" t="str">
@@ -32053,7 +32368,7 @@
         <v>3</v>
       </c>
       <c r="R58">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A58&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q58)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A58&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q58)</f>
         <v>3</v>
       </c>
       <c r="S58">
@@ -32081,11 +32396,11 @@
         <v>Hard CC</v>
       </c>
       <c r="Y58">
-        <f>IF($A$1="",0,MAX(IF(W58&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W58,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W58&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W58,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X58&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X58,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X58&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X58,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W58&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W58,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W58&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W58,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X58&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X58,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X58&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X58,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z58">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A58)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A58)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A58)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A58)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A58)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A58)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A58)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A58)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A58)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A58)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE58" t="str">
@@ -32171,7 +32486,7 @@
         <v>7</v>
       </c>
       <c r="R59">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A59&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q59)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A59&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q59)</f>
         <v>7</v>
       </c>
       <c r="S59">
@@ -32199,11 +32514,11 @@
         <v>Execute</v>
       </c>
       <c r="Y59">
-        <f>IF($A$1="",0,MAX(IF(W59&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W59,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W59&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W59,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X59&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X59,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X59&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X59,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W59&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W59,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W59&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W59,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X59&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X59,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X59&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X59,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>10</v>
       </c>
       <c r="Z59">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A59)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A59)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A59)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A59)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A59)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A59)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A59)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A59)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A59)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A59)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE59" t="str">
@@ -32289,7 +32604,7 @@
         <v>11</v>
       </c>
       <c r="R60">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A60&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q60)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A60&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q60)</f>
         <v>11</v>
       </c>
       <c r="S60">
@@ -32317,11 +32632,11 @@
         <v>Healing</v>
       </c>
       <c r="Y60">
-        <f>IF($A$1="",0,MAX(IF(W60&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W60,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W60&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W60,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X60&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X60,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X60&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X60,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W60&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W60,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W60&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W60,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X60&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X60,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X60&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X60,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z60">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A60)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A60)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A60)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A60)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A60)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A60)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A60)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A60)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A60)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A60)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE60" t="str">
@@ -32407,7 +32722,7 @@
         <v>9.5</v>
       </c>
       <c r="R61">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A61&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q61)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A61&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q61)</f>
         <v>9.5</v>
       </c>
       <c r="S61">
@@ -32435,11 +32750,11 @@
         <v>AoE CC</v>
       </c>
       <c r="Y61">
-        <f>IF($A$1="",0,MAX(IF(W61&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W61,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W61&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W61,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X61&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X61,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X61&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X61,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W61&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W61,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W61&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W61,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X61&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X61,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X61&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X61,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z61">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A61)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A61)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A61)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A61)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A61)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A61)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A61)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A61)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A61)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A61)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE61" t="str">
@@ -32525,7 +32840,7 @@
         <v>1</v>
       </c>
       <c r="R62">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A62&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q62)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A62&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q62)</f>
         <v>1</v>
       </c>
       <c r="S62">
@@ -32553,11 +32868,11 @@
         <v>DPS</v>
       </c>
       <c r="Y62">
-        <f>IF($A$1="",0,MAX(IF(W62&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W62,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W62&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W62,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X62&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X62,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X62&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X62,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W62&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W62,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W62&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W62,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X62&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X62,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X62&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X62,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z62">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A62)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A62)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A62)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A62)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A62)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A62)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A62)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A62)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A62)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A62)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE62" t="str">
@@ -32643,7 +32958,7 @@
         <v>4</v>
       </c>
       <c r="R63">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A63&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q63)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A63&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q63)</f>
         <v>4</v>
       </c>
       <c r="S63">
@@ -32671,11 +32986,11 @@
         <v>Burst</v>
       </c>
       <c r="Y63">
-        <f>IF($A$1="",0,MAX(IF(W63&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W63,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W63&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W63,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X63&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X63,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X63&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X63,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W63&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W63,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W63&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W63,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X63&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X63,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X63&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X63,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z63">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A63)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A63)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A63)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A63)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A63)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A63)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A63)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A63)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A63)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A63)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE63" t="str">
@@ -32761,7 +33076,7 @@
         <v>1.5</v>
       </c>
       <c r="R64">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A64&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q64)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A64&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q64)</f>
         <v>1.5</v>
       </c>
       <c r="S64">
@@ -32789,11 +33104,11 @@
         <v>Burst</v>
       </c>
       <c r="Y64">
-        <f>IF($A$1="",0,MAX(IF(W64&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W64,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W64&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W64,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X64&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X64,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X64&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X64,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W64&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W64,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W64&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W64,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X64&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X64,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X64&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X64,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z64">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A64)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A64)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A64)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A64)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A64)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A64)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A64)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A64)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A64)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A64)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE64" t="str">
@@ -32879,7 +33194,7 @@
         <v>6</v>
       </c>
       <c r="R65">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A65&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q65)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A65&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q65)</f>
         <v>6</v>
       </c>
       <c r="S65">
@@ -32907,11 +33222,11 @@
         <v>Burst</v>
       </c>
       <c r="Y65">
-        <f>IF($A$1="",0,MAX(IF(W65&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W65,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W65&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W65,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X65&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X65,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X65&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X65,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W65&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W65,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W65&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W65,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X65&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X65,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X65&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X65,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z65">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A65)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A65)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A65)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A65)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A65)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A65)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A65)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A65)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A65)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A65)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE65" t="str">
@@ -32997,7 +33312,7 @@
         <v>0.5</v>
       </c>
       <c r="R66">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A66&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q66)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A66&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q66)</f>
         <v>0.5</v>
       </c>
       <c r="S66">
@@ -33025,11 +33340,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y66">
-        <f>IF($A$1="",0,MAX(IF(W66&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W66,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W66&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W66,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X66&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X66,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X66&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X66,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W66&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W66,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W66&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W66,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X66&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X66,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X66&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X66,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z66">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A66)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A66)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A66)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A66)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A66)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A66)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A66)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A66)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A66)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A66)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE66" t="str">
@@ -33115,7 +33430,7 @@
         <v>4.5</v>
       </c>
       <c r="R67">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A67&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q67)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A67&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q67)</f>
         <v>4.5</v>
       </c>
       <c r="S67">
@@ -33143,11 +33458,11 @@
         <v>Hard CC</v>
       </c>
       <c r="Y67">
-        <f>IF($A$1="",0,MAX(IF(W67&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W67,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W67&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W67,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X67&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X67,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X67&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X67,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W67&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W67,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W67&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W67,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X67&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X67,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X67&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X67,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z67">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A67)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A67)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A67)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A67)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A67)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A67)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A67)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A67)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A67)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A67)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE67" t="str">
@@ -33233,7 +33548,7 @@
         <v>5</v>
       </c>
       <c r="R68">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A68&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q68)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A68&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q68)</f>
         <v>5</v>
       </c>
       <c r="S68">
@@ -33261,11 +33576,11 @@
         <v>DPS</v>
       </c>
       <c r="Y68">
-        <f>IF($A$1="",0,MAX(IF(W68&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W68,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W68&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W68,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X68&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X68,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X68&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X68,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W68&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W68,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W68&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W68,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X68&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X68,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X68&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X68,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z68">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A68)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A68)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A68)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A68)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A68)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A68)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A68)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A68)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A68)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A68)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE68" t="str">
@@ -33351,7 +33666,7 @@
         <v>17.5</v>
       </c>
       <c r="R69">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A69&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q69)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A69&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q69)</f>
         <v>17.5</v>
       </c>
       <c r="S69">
@@ -33379,11 +33694,11 @@
         <v>I-Frame</v>
       </c>
       <c r="Y69">
-        <f>IF($A$1="",0,MAX(IF(W69&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W69,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W69&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W69,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X69&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X69,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X69&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X69,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W69&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W69,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W69&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W69,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X69&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X69,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X69&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X69,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>10</v>
       </c>
       <c r="Z69">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A69)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A69)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A69)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A69)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A69)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A69)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A69)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A69)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A69)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A69)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE69" t="str">
@@ -33469,7 +33784,7 @@
         <v>-4</v>
       </c>
       <c r="R70">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A70&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q70)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A70&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q70)</f>
         <v>-4</v>
       </c>
       <c r="S70">
@@ -33497,11 +33812,11 @@
         <v>Vision</v>
       </c>
       <c r="Y70">
-        <f>IF($A$1="",0,MAX(IF(W70&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W70,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W70&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W70,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X70&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X70,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X70&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X70,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W70&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W70,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W70&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W70,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X70&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X70,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X70&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X70,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z70">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A70)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A70)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A70)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A70)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A70)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A70)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A70)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A70)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A70)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A70)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE70" t="str">
@@ -33587,7 +33902,7 @@
         <v>16</v>
       </c>
       <c r="R71">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A71&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q71)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A71&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q71)</f>
         <v>16</v>
       </c>
       <c r="S71">
@@ -33615,11 +33930,11 @@
         <v>AoE CC</v>
       </c>
       <c r="Y71">
-        <f>IF($A$1="",0,MAX(IF(W71&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W71,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W71&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W71,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X71&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X71,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X71&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X71,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W71&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W71,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W71&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W71,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X71&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X71,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X71&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X71,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z71">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A71)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A71)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A71)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A71)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A71)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A71)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A71)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A71)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A71)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A71)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE71" t="str">
@@ -33705,7 +34020,7 @@
         <v>-3.5</v>
       </c>
       <c r="R72">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A72&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q72)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A72&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q72)</f>
         <v>-3.5</v>
       </c>
       <c r="S72">
@@ -33733,11 +34048,11 @@
         <v>Poke</v>
       </c>
       <c r="Y72">
-        <f>IF($A$1="",0,MAX(IF(W72&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W72,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W72&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W72,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X72&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X72,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X72&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X72,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W72&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W72,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W72&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W72,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X72&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X72,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X72&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X72,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z72">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A72)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A72)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A72)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A72)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A72)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A72)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A72)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A72)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A72)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A72)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE72" t="str">
@@ -33823,7 +34138,7 @@
         <v>-1</v>
       </c>
       <c r="R73">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A73&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q73)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A73&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q73)</f>
         <v>-1</v>
       </c>
       <c r="S73">
@@ -33851,11 +34166,11 @@
         <v>DPS</v>
       </c>
       <c r="Y73">
-        <f>IF($A$1="",0,MAX(IF(W73&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W73,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W73&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W73,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X73&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X73,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X73&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X73,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W73&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W73,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W73&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W73,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X73&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X73,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X73&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X73,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z73">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A73)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A73)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A73)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A73)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A73)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A73)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A73)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A73)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A73)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A73)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE73" t="str">
@@ -33941,7 +34256,7 @@
         <v>4</v>
       </c>
       <c r="R74">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A74&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q74)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A74&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q74)</f>
         <v>4</v>
       </c>
       <c r="S74">
@@ -33969,11 +34284,11 @@
         <v>Dash/Blink</v>
       </c>
       <c r="Y74">
-        <f>IF($A$1="",0,MAX(IF(W74&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W74,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W74&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W74,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X74&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X74,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X74&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X74,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W74&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W74,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W74&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W74,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X74&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X74,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X74&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X74,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z74">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A74)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A74)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A74)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A74)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A74)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A74)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A74)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A74)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A74)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A74)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE74" t="str">
@@ -34059,7 +34374,7 @@
         <v>2</v>
       </c>
       <c r="R75">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A75&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q75)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A75&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q75)</f>
         <v>2</v>
       </c>
       <c r="S75">
@@ -34087,11 +34402,11 @@
         <v>AoE CC</v>
       </c>
       <c r="Y75">
-        <f>IF($A$1="",0,MAX(IF(W75&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W75,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W75&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W75,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X75&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X75,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X75&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X75,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W75&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W75,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W75&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W75,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X75&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X75,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X75&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X75,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z75">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A75)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A75)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A75)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A75)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A75)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A75)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A75)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A75)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A75)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A75)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE75" t="str">
@@ -34177,7 +34492,7 @@
         <v>11</v>
       </c>
       <c r="R76">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A76&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q76)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A76&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q76)</f>
         <v>11</v>
       </c>
       <c r="S76">
@@ -34205,11 +34520,11 @@
         <v>I-Frame</v>
       </c>
       <c r="Y76">
-        <f>IF($A$1="",0,MAX(IF(W76&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W76,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W76&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W76,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X76&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X76,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X76&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X76,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W76&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W76,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W76&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W76,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X76&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X76,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X76&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X76,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>10</v>
       </c>
       <c r="Z76">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A76)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A76)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A76)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A76)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A76)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A76)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A76)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A76)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A76)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A76)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE76" t="str">
@@ -34295,7 +34610,7 @@
         <v>0.5</v>
       </c>
       <c r="R77">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A77&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q77)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A77&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q77)</f>
         <v>0.5</v>
       </c>
       <c r="S77">
@@ -34323,11 +34638,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y77">
-        <f>IF($A$1="",0,MAX(IF(W77&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W77,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W77&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W77,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X77&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X77,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X77&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X77,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W77&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W77,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W77&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W77,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X77&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X77,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X77&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X77,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z77">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A77)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A77)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A77)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A77)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A77)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A77)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A77)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A77)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A77)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A77)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE77" t="str">
@@ -34413,7 +34728,7 @@
         <v>-1</v>
       </c>
       <c r="R78">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A78&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q78)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A78&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q78)</f>
         <v>-1</v>
       </c>
       <c r="S78">
@@ -34441,11 +34756,11 @@
         <v>Burst</v>
       </c>
       <c r="Y78">
-        <f>IF($A$1="",0,MAX(IF(W78&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W78,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W78&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W78,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X78&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X78,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X78&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X78,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W78&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W78,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W78&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W78,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X78&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X78,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X78&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X78,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z78">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A78)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A78)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A78)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A78)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A78)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A78)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A78)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A78)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A78)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A78)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE78" t="str">
@@ -34531,7 +34846,7 @@
         <v>16</v>
       </c>
       <c r="R79">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A79&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q79)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A79&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q79)</f>
         <v>16</v>
       </c>
       <c r="S79">
@@ -34559,11 +34874,11 @@
         <v>Damage Reduction</v>
       </c>
       <c r="Y79">
-        <f>IF($A$1="",0,MAX(IF(W79&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W79,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W79&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W79,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X79&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X79,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X79&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X79,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W79&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W79,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W79&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W79,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X79&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X79,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X79&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X79,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z79">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A79)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A79)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A79)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A79)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A79)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A79)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A79)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A79)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A79)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A79)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE79" t="str">
@@ -34649,7 +34964,7 @@
         <v>-2</v>
       </c>
       <c r="R80">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A80&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q80)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A80&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q80)</f>
         <v>-2</v>
       </c>
       <c r="S80">
@@ -34677,11 +34992,11 @@
         <v>Dash/Blink</v>
       </c>
       <c r="Y80">
-        <f>IF($A$1="",0,MAX(IF(W80&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W80,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W80&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W80,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X80&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X80,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X80&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X80,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W80&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W80,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W80&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W80,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X80&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X80,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X80&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X80,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z80">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A80)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A80)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A80)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A80)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A80)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A80)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A80)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A80)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A80)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A80)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE80" t="str">
@@ -34767,7 +35082,7 @@
         <v>7</v>
       </c>
       <c r="R81">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A81&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q81)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A81&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q81)</f>
         <v>7</v>
       </c>
       <c r="S81">
@@ -34795,11 +35110,11 @@
         <v>Burst</v>
       </c>
       <c r="Y81">
-        <f>IF($A$1="",0,MAX(IF(W81&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W81,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W81&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W81,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X81&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X81,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X81&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X81,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W81&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W81,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W81&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W81,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X81&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X81,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X81&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X81,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z81">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A81)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A81)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A81)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A81)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A81)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A81)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A81)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A81)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A81)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A81)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE81" t="str">
@@ -34885,7 +35200,7 @@
         <v>7.5</v>
       </c>
       <c r="R82">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A82&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q82)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A82&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q82)</f>
         <v>7.5</v>
       </c>
       <c r="S82">
@@ -34913,11 +35228,11 @@
         <v>Sustain</v>
       </c>
       <c r="Y82">
-        <f>IF($A$1="",0,MAX(IF(W82&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W82,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W82&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W82,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X82&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X82,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X82&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X82,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W82&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W82,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W82&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W82,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X82&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X82,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X82&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X82,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z82">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A82)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A82)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A82)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A82)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A82)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A82)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A82)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A82)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A82)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A82)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE82" t="str">
@@ -35003,7 +35318,7 @@
         <v>9.5</v>
       </c>
       <c r="R83">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A83&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q83)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A83&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q83)</f>
         <v>9.5</v>
       </c>
       <c r="S83">
@@ -35031,11 +35346,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y83">
-        <f>IF($A$1="",0,MAX(IF(W83&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W83,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W83&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W83,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X83&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X83,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X83&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X83,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W83&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W83,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W83&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W83,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X83&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X83,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X83&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X83,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z83">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A83)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A83)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A83)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A83)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A83)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A83)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A83)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A83)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A83)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A83)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE83" t="str">
@@ -35121,7 +35436,7 @@
         <v>-2</v>
       </c>
       <c r="R84">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A84&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q84)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A84&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q84)</f>
         <v>-2</v>
       </c>
       <c r="S84">
@@ -35149,11 +35464,11 @@
         <v>Sustain</v>
       </c>
       <c r="Y84">
-        <f>IF($A$1="",0,MAX(IF(W84&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W84,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W84&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W84,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X84&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X84,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X84&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X84,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W84&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W84,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W84&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W84,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X84&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X84,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X84&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X84,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z84">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A84)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A84)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A84)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A84)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A84)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A84)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A84)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A84)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A84)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A84)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE84" t="str">
@@ -35239,7 +35554,7 @@
         <v>-7.5</v>
       </c>
       <c r="R85">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A85&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q85)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A85&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q85)</f>
         <v>-7.5</v>
       </c>
       <c r="S85">
@@ -35267,11 +35582,11 @@
         <v>Burst</v>
       </c>
       <c r="Y85">
-        <f>IF($A$1="",0,MAX(IF(W85&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W85,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W85&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W85,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X85&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X85,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X85&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X85,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W85&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W85,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W85&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W85,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X85&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X85,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X85&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X85,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z85">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A85)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A85)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A85)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A85)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A85)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A85)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A85)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A85)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A85)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A85)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE85" t="str">
@@ -35357,7 +35672,7 @@
         <v>-0.5</v>
       </c>
       <c r="R86">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A86&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q86)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A86&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q86)</f>
         <v>-0.5</v>
       </c>
       <c r="S86">
@@ -35385,11 +35700,11 @@
         <v>Sustain</v>
       </c>
       <c r="Y86">
-        <f>IF($A$1="",0,MAX(IF(W86&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W86,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W86&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W86,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X86&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X86,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X86&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X86,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W86&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W86,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W86&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W86,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X86&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X86,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X86&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X86,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z86">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A86)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A86)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A86)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A86)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A86)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A86)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A86)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A86)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A86)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A86)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE86" t="str">
@@ -35475,7 +35790,7 @@
         <v>2</v>
       </c>
       <c r="R87">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A87&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q87)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A87&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q87)</f>
         <v>2</v>
       </c>
       <c r="S87">
@@ -35503,11 +35818,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y87">
-        <f>IF($A$1="",0,MAX(IF(W87&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W87,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W87&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W87,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X87&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X87,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X87&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X87,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W87&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W87,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W87&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W87,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X87&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X87,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X87&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X87,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z87">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A87)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A87)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A87)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A87)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A87)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A87)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A87)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A87)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A87)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A87)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE87" t="str">
@@ -35593,7 +35908,7 @@
         <v>10.5</v>
       </c>
       <c r="R88">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A88&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q88)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A88&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q88)</f>
         <v>10.5</v>
       </c>
       <c r="S88">
@@ -35621,11 +35936,11 @@
         <v>Mobility</v>
       </c>
       <c r="Y88">
-        <f>IF($A$1="",0,MAX(IF(W88&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W88,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W88&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W88,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X88&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X88,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X88&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X88,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W88&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W88,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W88&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W88,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X88&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X88,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X88&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X88,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z88">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A88)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A88)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A88)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A88)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A88)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A88)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A88)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A88)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A88)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A88)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE88" t="str">
@@ -35708,19 +36023,19 @@
       </c>
       <c r="Q89">
         <f t="shared" si="30"/>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="R89">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A89&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q89)</f>
-        <v>19</v>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A89&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q89)</f>
+        <v>23</v>
       </c>
       <c r="S89">
         <f t="shared" si="31"/>
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="T89">
         <f t="shared" si="32"/>
-        <v>19.000008900000001</v>
+        <v>23.000008900000001</v>
       </c>
       <c r="U89" t="str">
         <f>Heroes!$M89</f>
@@ -35739,12 +36054,12 @@
         <v>Sustain</v>
       </c>
       <c r="Y89">
-        <f>IF($A$1="",0,MAX(IF(W89&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W89,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W89&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W89,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X89&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X89,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X89&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X89,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W89&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W89,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W89&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W89,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X89&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X89,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X89&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X89,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z89">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A89)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A89)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A89)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A89)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A89)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
-        <v>16</v>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A89)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A89)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A89)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A89)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A89)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
+        <v>20</v>
       </c>
       <c r="AE89" t="str">
         <f>Heroes!$R89</f>
@@ -35829,7 +36144,7 @@
         <v>8.5</v>
       </c>
       <c r="R90">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A90&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q90)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A90&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q90)</f>
         <v>8.5</v>
       </c>
       <c r="S90">
@@ -35857,11 +36172,11 @@
         <v>High Mobility</v>
       </c>
       <c r="Y90">
-        <f>IF($A$1="",0,MAX(IF(W90&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W90,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W90&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W90,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X90&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X90,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X90&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X90,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W90&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W90,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W90&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W90,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X90&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X90,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X90&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X90,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>10</v>
       </c>
       <c r="Z90">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A90)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A90)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A90)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A90)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A90)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A90)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A90)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A90)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A90)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A90)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE90" t="str">
@@ -35947,7 +36262,7 @@
         <v>6.5</v>
       </c>
       <c r="R91">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A91&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q91)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A91&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q91)</f>
         <v>6.5</v>
       </c>
       <c r="S91">
@@ -35975,11 +36290,11 @@
         <v>Sustain</v>
       </c>
       <c r="Y91">
-        <f>IF($A$1="",0,MAX(IF(W91&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W91,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W91&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W91,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X91&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X91,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X91&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X91,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W91&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W91,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W91&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W91,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X91&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X91,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X91&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X91,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z91">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A91)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A91)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A91)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A91)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A91)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A91)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A91)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A91)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A91)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A91)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE91" t="str">
@@ -36065,7 +36380,7 @@
         <v>9.5</v>
       </c>
       <c r="R92">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A92&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q92)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A92&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q92)</f>
         <v>9.5</v>
       </c>
       <c r="S92">
@@ -36093,11 +36408,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y92">
-        <f>IF($A$1="",0,MAX(IF(W92&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W92,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W92&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W92,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X92&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X92,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X92&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X92,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W92&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W92,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W92&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W92,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X92&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X92,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X92&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X92,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z92">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A92)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A92)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A92)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A92)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A92)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A92)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A92)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A92)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A92)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A92)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE92" t="str">
@@ -36183,7 +36498,7 @@
         <v>8</v>
       </c>
       <c r="R93">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A93&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q93)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A93&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q93)</f>
         <v>8</v>
       </c>
       <c r="S93">
@@ -36211,11 +36526,11 @@
         <v>Sustain</v>
       </c>
       <c r="Y93">
-        <f>IF($A$1="",0,MAX(IF(W93&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W93,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W93&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W93,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X93&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X93,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X93&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X93,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W93&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W93,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W93&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W93,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X93&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X93,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X93&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X93,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z93">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A93)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A93)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A93)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A93)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A93)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A93)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A93)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A93)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A93)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A93)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE93" t="str">
@@ -36301,7 +36616,7 @@
         <v>8</v>
       </c>
       <c r="R94">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A94&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q94)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A94&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q94)</f>
         <v>8</v>
       </c>
       <c r="S94">
@@ -36329,11 +36644,11 @@
         <v>Hard CC</v>
       </c>
       <c r="Y94">
-        <f>IF($A$1="",0,MAX(IF(W94&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W94,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W94&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W94,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X94&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X94,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X94&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X94,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W94&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W94,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W94&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W94,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X94&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X94,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X94&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X94,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z94">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A94)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A94)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A94)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A94)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A94)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A94)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A94)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A94)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A94)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A94)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE94" t="str">
@@ -36419,7 +36734,7 @@
         <v>5</v>
       </c>
       <c r="R95">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A95&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q95)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A95&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q95)</f>
         <v>5</v>
       </c>
       <c r="S95">
@@ -36447,11 +36762,11 @@
         <v>Hard CC</v>
       </c>
       <c r="Y95">
-        <f>IF($A$1="",0,MAX(IF(W95&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W95,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W95&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W95,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X95&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X95,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X95&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X95,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W95&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W95,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W95&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W95,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X95&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X95,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X95&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X95,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z95">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A95)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A95)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A95)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A95)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A95)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A95)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A95)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A95)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A95)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A95)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE95" t="str">
@@ -36537,7 +36852,7 @@
         <v>1.5</v>
       </c>
       <c r="R96">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A96&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q96)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A96&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q96)</f>
         <v>1.5</v>
       </c>
       <c r="S96">
@@ -36565,11 +36880,11 @@
         <v>Global Dive</v>
       </c>
       <c r="Y96">
-        <f>IF($A$1="",0,MAX(IF(W96&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W96,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W96&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W96,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X96&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X96,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X96&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X96,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W96&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W96,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W96&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W96,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X96&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X96,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X96&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X96,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z96">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A96)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A96)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A96)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A96)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A96)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A96)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A96)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A96)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A96)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A96)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE96" t="str">
@@ -36655,7 +36970,7 @@
         <v>3</v>
       </c>
       <c r="R97">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A97&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q97)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A97&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q97)</f>
         <v>3</v>
       </c>
       <c r="S97">
@@ -36683,11 +36998,11 @@
         <v>Global Dive</v>
       </c>
       <c r="Y97">
-        <f>IF($A$1="",0,MAX(IF(W97&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W97,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W97&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W97,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X97&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X97,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X97&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X97,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W97&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W97,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W97&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W97,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X97&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X97,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X97&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X97,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z97">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A97)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A97)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A97)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A97)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A97)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A97)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A97)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A97)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A97)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A97)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE97" t="str">
@@ -36773,7 +37088,7 @@
         <v>6.5</v>
       </c>
       <c r="R98">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A98&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q98)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A98&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q98)</f>
         <v>6.5</v>
       </c>
       <c r="S98">
@@ -36801,11 +37116,11 @@
         <v>Dash/Blink</v>
       </c>
       <c r="Y98">
-        <f>IF($A$1="",0,MAX(IF(W98&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W98,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W98&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W98,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X98&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X98,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X98&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X98,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W98&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W98,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W98&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W98,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X98&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X98,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X98&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X98,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>10</v>
       </c>
       <c r="Z98">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A98)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A98)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A98)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A98)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A98)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A98)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A98)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A98)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A98)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A98)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE98" t="str">
@@ -36891,7 +37206,7 @@
         <v>-2</v>
       </c>
       <c r="R99">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A99&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q99)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A99&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q99)</f>
         <v>-2</v>
       </c>
       <c r="S99">
@@ -36919,11 +37234,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y99">
-        <f>IF($A$1="",0,MAX(IF(W99&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W99,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W99&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W99,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X99&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X99,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X99&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X99,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W99&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W99,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W99&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W99,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X99&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X99,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X99&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X99,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z99">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A99)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A99)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A99)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A99)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A99)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A99)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A99)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A99)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A99)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A99)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE99" t="str">
@@ -37009,7 +37324,7 @@
         <v>7</v>
       </c>
       <c r="R100">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A100&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q100)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A100&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q100)</f>
         <v>7</v>
       </c>
       <c r="S100">
@@ -37037,11 +37352,11 @@
         <v>Hard CC</v>
       </c>
       <c r="Y100">
-        <f>IF($A$1="",0,MAX(IF(W100&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W100,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W100&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W100,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X100&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X100,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X100&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X100,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W100&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W100,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W100&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W100,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X100&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X100,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X100&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X100,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z100">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A100)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A100)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A100)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A100)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A100)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A100)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A100)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A100)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A100)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A100)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE100" t="str">
@@ -37127,7 +37442,7 @@
         <v>0</v>
       </c>
       <c r="R101">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A101&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q101)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A101&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q101)</f>
         <v>0</v>
       </c>
       <c r="S101">
@@ -37155,11 +37470,11 @@
         <v>Hard CC</v>
       </c>
       <c r="Y101">
-        <f>IF($A$1="",0,MAX(IF(W101&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W101,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W101&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W101,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X101&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X101,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X101&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X101,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W101&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W101,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W101&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W101,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X101&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X101,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X101&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X101,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z101">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A101)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A101)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A101)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A101)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A101)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A101)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A101)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A101)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A101)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A101)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE101" t="str">
@@ -37245,7 +37560,7 @@
         <v>2</v>
       </c>
       <c r="R102">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A102&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q102)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A102&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q102)</f>
         <v>2</v>
       </c>
       <c r="S102">
@@ -37273,11 +37588,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y102">
-        <f>IF($A$1="",0,MAX(IF(W102&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W102,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W102&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W102,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X102&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X102,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X102&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X102,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W102&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W102,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W102&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W102,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X102&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X102,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X102&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X102,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z102">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A102)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A102)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A102)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A102)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A102)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A102)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A102)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A102)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A102)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A102)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE102" t="str">
@@ -37363,7 +37678,7 @@
         <v>1</v>
       </c>
       <c r="R103">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A103&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q103)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A103&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q103)</f>
         <v>1</v>
       </c>
       <c r="S103">
@@ -37391,11 +37706,11 @@
         <v>Dash/Blink</v>
       </c>
       <c r="Y103">
-        <f>IF($A$1="",0,MAX(IF(W103&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W103,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W103&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W103,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X103&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X103,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X103&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X103,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W103&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W103,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W103&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W103,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X103&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X103,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X103&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X103,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z103">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A103)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A103)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A103)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A103)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A103)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A103)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A103)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A103)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A103)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A103)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE103" t="str">
@@ -37481,7 +37796,7 @@
         <v>-5.5</v>
       </c>
       <c r="R104">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A104&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q104)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A104&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q104)</f>
         <v>-5.5</v>
       </c>
       <c r="S104">
@@ -37509,11 +37824,11 @@
         <v>Burst</v>
       </c>
       <c r="Y104">
-        <f>IF($A$1="",0,MAX(IF(W104&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W104,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W104&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W104,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X104&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X104,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X104&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X104,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W104&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W104,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W104&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W104,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X104&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X104,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X104&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X104,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z104">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A104)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A104)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A104)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A104)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A104)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A104)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A104)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A104)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A104)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A104)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE104" t="str">
@@ -37599,7 +37914,7 @@
         <v>9.5</v>
       </c>
       <c r="R105">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A105&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q105)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A105&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q105)</f>
         <v>9.5</v>
       </c>
       <c r="S105">
@@ -37627,11 +37942,11 @@
         <v>Targeted CC</v>
       </c>
       <c r="Y105">
-        <f>IF($A$1="",0,MAX(IF(W105&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W105,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W105&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W105,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X105&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X105,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X105&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X105,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W105&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W105,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W105&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W105,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X105&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X105,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X105&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X105,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z105">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A105)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A105)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A105)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A105)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A105)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A105)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A105)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A105)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A105)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A105)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE105" t="str">
@@ -37717,7 +38032,7 @@
         <v>-1.5</v>
       </c>
       <c r="R106">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A106&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q106)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A106&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q106)</f>
         <v>-1.5</v>
       </c>
       <c r="S106">
@@ -37745,11 +38060,11 @@
         <v>Burst</v>
       </c>
       <c r="Y106">
-        <f>IF($A$1="",0,MAX(IF(W106&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W106,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W106&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W106,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X106&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X106,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X106&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X106,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W106&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W106,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W106&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W106,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X106&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X106,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X106&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X106,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z106">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A106)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A106)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A106)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A106)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A106)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A106)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A106)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A106)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A106)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A106)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE106" t="str">
@@ -37835,7 +38150,7 @@
         <v>13</v>
       </c>
       <c r="R107">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A107&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q107)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A107&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q107)</f>
         <v>13</v>
       </c>
       <c r="S107">
@@ -37863,11 +38178,11 @@
         <v>Burst</v>
       </c>
       <c r="Y107">
-        <f>IF($A$1="",0,MAX(IF(W107&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W107,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W107&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W107,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X107&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X107,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X107&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X107,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W107&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W107,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W107&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W107,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X107&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X107,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X107&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X107,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z107">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A107)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A107)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A107)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A107)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A107)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A107)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A107)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A107)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A107)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A107)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE107" t="str">
@@ -37953,7 +38268,7 @@
         <v>3</v>
       </c>
       <c r="R108">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A108&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q108)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A108&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q108)</f>
         <v>3</v>
       </c>
       <c r="S108">
@@ -37981,11 +38296,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y108">
-        <f>IF($A$1="",0,MAX(IF(W108&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W108,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W108&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W108,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X108&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X108,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X108&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X108,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W108&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W108,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W108&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W108,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X108&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X108,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X108&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X108,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z108">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A108)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A108)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A108)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A108)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A108)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A108)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A108)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A108)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A108)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A108)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE108" t="str">
@@ -38071,7 +38386,7 @@
         <v>-0.5</v>
       </c>
       <c r="R109">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A109&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q109)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A109&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q109)</f>
         <v>-0.5</v>
       </c>
       <c r="S109">
@@ -38099,11 +38414,11 @@
         <v>Sustain</v>
       </c>
       <c r="Y109">
-        <f>IF($A$1="",0,MAX(IF(W109&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W109,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W109&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W109,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X109&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X109,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X109&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X109,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W109&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W109,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W109&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W109,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X109&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X109,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X109&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X109,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z109">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A109)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A109)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A109)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A109)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A109)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A109)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A109)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A109)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A109)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A109)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE109" t="str">
@@ -38189,7 +38504,7 @@
         <v>7</v>
       </c>
       <c r="R110">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A110&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q110)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A110&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q110)</f>
         <v>7</v>
       </c>
       <c r="S110">
@@ -38217,11 +38532,11 @@
         <v>Burst</v>
       </c>
       <c r="Y110">
-        <f>IF($A$1="",0,MAX(IF(W110&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W110,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W110&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W110,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X110&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X110,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X110&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X110,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W110&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W110,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W110&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W110,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X110&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X110,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X110&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X110,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>10</v>
       </c>
       <c r="Z110">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A110)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A110)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A110)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A110)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A110)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A110)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A110)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A110)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A110)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A110)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE110" t="str">
@@ -38307,7 +38622,7 @@
         <v>4.5</v>
       </c>
       <c r="R111">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A111&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q111)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A111&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q111)</f>
         <v>4.5</v>
       </c>
       <c r="S111">
@@ -38335,11 +38650,11 @@
         <v>Sustain</v>
       </c>
       <c r="Y111">
-        <f>IF($A$1="",0,MAX(IF(W111&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W111,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W111&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W111,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X111&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X111,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X111&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X111,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W111&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W111,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W111&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W111,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X111&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X111,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X111&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X111,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z111">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A111)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A111)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A111)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A111)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A111)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A111)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A111)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A111)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A111)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A111)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE111" t="str">
@@ -38425,7 +38740,7 @@
         <v>25.5</v>
       </c>
       <c r="R112">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A112&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q112)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A112&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q112)</f>
         <v>25.5</v>
       </c>
       <c r="S112">
@@ -38453,11 +38768,11 @@
         <v>Hard CC</v>
       </c>
       <c r="Y112">
-        <f>IF($A$1="",0,MAX(IF(W112&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W112,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W112&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W112,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X112&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X112,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X112&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X112,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W112&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W112,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W112&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W112,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X112&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X112,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X112&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X112,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z112">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A112)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A112)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A112)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A112)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A112)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A112)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A112)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A112)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A112)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A112)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE112" t="str">
@@ -38540,19 +38855,19 @@
       </c>
       <c r="Q113">
         <f t="shared" si="42"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R113">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A113&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q113)</f>
-        <v>0</v>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A113&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q113)</f>
+        <v>16</v>
       </c>
       <c r="S113">
         <f t="shared" si="43"/>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T113">
         <f t="shared" si="44"/>
-        <v>1.13E-5</v>
+        <v>16.000011300000001</v>
       </c>
       <c r="U113" t="str">
         <f>Heroes!$M113</f>
@@ -38571,12 +38886,12 @@
         <v>Soft CC</v>
       </c>
       <c r="Y113">
-        <f>IF($A$1="",0,MAX(IF(W113&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W113,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W113&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W113,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X113&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X113,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X113&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X113,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W113&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W113,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W113&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W113,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X113&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X113,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X113&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X113,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z113">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A113)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A113)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A113)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A113)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A113)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
-        <v>0</v>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A113)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A113)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A113)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A113)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A113)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
+        <v>16</v>
       </c>
       <c r="AE113" t="str">
         <f>Heroes!$R113</f>
@@ -38661,7 +38976,7 @@
         <v>3</v>
       </c>
       <c r="R114">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A114&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q114)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A114&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q114)</f>
         <v>3</v>
       </c>
       <c r="S114">
@@ -38689,11 +39004,11 @@
         <v>Burst</v>
       </c>
       <c r="Y114">
-        <f>IF($A$1="",0,MAX(IF(W114&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W114,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W114&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W114,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X114&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X114,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X114&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X114,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W114&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W114,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W114&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W114,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X114&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X114,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X114&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X114,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z114">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A114)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A114)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A114)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A114)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A114)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A114)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A114)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A114)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A114)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A114)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE114" t="str">
@@ -38779,7 +39094,7 @@
         <v>12.5</v>
       </c>
       <c r="R115">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A115&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q115)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A115&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q115)</f>
         <v>12.5</v>
       </c>
       <c r="S115">
@@ -38807,11 +39122,11 @@
         <v>DPS</v>
       </c>
       <c r="Y115">
-        <f>IF($A$1="",0,MAX(IF(W115&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W115,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W115&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W115,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X115&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X115,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X115&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X115,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W115&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W115,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W115&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W115,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X115&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X115,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X115&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X115,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z115">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A115)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A115)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A115)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A115)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A115)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A115)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A115)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A115)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A115)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A115)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE115" t="str">
@@ -38897,7 +39212,7 @@
         <v>5</v>
       </c>
       <c r="R116">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A116&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q116)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A116&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q116)</f>
         <v>5</v>
       </c>
       <c r="S116">
@@ -38925,11 +39240,11 @@
         <v>Burst</v>
       </c>
       <c r="Y116">
-        <f>IF($A$1="",0,MAX(IF(W116&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W116,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W116&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W116,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X116&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X116,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X116&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X116,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W116&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W116,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W116&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W116,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X116&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X116,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X116&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X116,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z116">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A116)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A116)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A116)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A116)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A116)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A116)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A116)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A116)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A116)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A116)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE116" t="str">
@@ -39015,7 +39330,7 @@
         <v>14.5</v>
       </c>
       <c r="R117">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A117&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q117)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A117&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q117)</f>
         <v>14.5</v>
       </c>
       <c r="S117">
@@ -39043,11 +39358,11 @@
         <v>I-Frame</v>
       </c>
       <c r="Y117">
-        <f>IF($A$1="",0,MAX(IF(W117&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W117,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W117&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W117,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X117&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X117,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X117&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X117,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W117&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W117,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W117&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W117,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X117&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X117,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X117&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X117,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>10</v>
       </c>
       <c r="Z117">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A117)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A117)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A117)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A117)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A117)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A117)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A117)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A117)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A117)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A117)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE117" t="str">
@@ -39133,7 +39448,7 @@
         <v>6.5</v>
       </c>
       <c r="R118">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A118&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q118)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A118&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q118)</f>
         <v>6.5</v>
       </c>
       <c r="S118">
@@ -39161,11 +39476,11 @@
         <v>AoE CC</v>
       </c>
       <c r="Y118">
-        <f>IF($A$1="",0,MAX(IF(W118&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W118,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W118&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W118,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X118&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X118,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X118&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X118,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W118&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W118,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W118&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W118,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X118&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X118,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X118&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X118,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z118">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A118)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A118)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A118)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A118)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A118)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A118)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A118)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A118)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A118)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A118)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE118" t="str">
@@ -39251,7 +39566,7 @@
         <v>2</v>
       </c>
       <c r="R119">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A119&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q119)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A119&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q119)</f>
         <v>2</v>
       </c>
       <c r="S119">
@@ -39279,11 +39594,11 @@
         <v>Shield</v>
       </c>
       <c r="Y119">
-        <f>IF($A$1="",0,MAX(IF(W119&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W119,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W119&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W119,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X119&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X119,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X119&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X119,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W119&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W119,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W119&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W119,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X119&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X119,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X119&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X119,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z119">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A119)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A119)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A119)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A119)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A119)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A119)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A119)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A119)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A119)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A119)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE119" t="str">
@@ -39369,7 +39684,7 @@
         <v>2</v>
       </c>
       <c r="R120">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A120&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q120)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A120&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q120)</f>
         <v>2</v>
       </c>
       <c r="S120">
@@ -39397,11 +39712,11 @@
         <v>Poke</v>
       </c>
       <c r="Y120">
-        <f>IF($A$1="",0,MAX(IF(W120&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W120,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W120&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W120,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X120&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X120,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X120&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X120,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W120&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W120,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W120&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W120,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X120&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X120,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X120&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X120,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z120">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A120)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A120)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A120)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A120)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A120)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A120)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A120)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A120)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A120)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A120)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE120" t="str">
@@ -39487,7 +39802,7 @@
         <v>1.5</v>
       </c>
       <c r="R121">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A121&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q121)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A121&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q121)</f>
         <v>1.5</v>
       </c>
       <c r="S121">
@@ -39515,11 +39830,11 @@
         <v>Sustain</v>
       </c>
       <c r="Y121">
-        <f>IF($A$1="",0,MAX(IF(W121&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W121,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W121&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W121,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X121&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X121,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X121&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X121,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W121&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W121,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W121&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W121,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X121&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X121,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X121&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X121,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z121">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A121)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A121)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A121)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A121)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A121)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A121)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A121)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A121)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A121)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A121)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE121" t="str">
@@ -39605,7 +39920,7 @@
         <v>3</v>
       </c>
       <c r="R122">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A122&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q122)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A122&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q122)</f>
         <v>3</v>
       </c>
       <c r="S122">
@@ -39633,11 +39948,11 @@
         <v>DPS</v>
       </c>
       <c r="Y122">
-        <f>IF($A$1="",0,MAX(IF(W122&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W122,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W122&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W122,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X122&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X122,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X122&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X122,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W122&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W122,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W122&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W122,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X122&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X122,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X122&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X122,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z122">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A122)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A122)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A122)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A122)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A122)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A122)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A122)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A122)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A122)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A122)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE122" t="str">
@@ -39723,7 +40038,7 @@
         <v>-8</v>
       </c>
       <c r="R123">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A123&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q123)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A123&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q123)</f>
         <v>-8</v>
       </c>
       <c r="S123">
@@ -39751,11 +40066,11 @@
         <v>Burst</v>
       </c>
       <c r="Y123">
-        <f>IF($A$1="",0,MAX(IF(W123&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W123,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W123&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W123,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X123&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X123,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X123&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X123,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W123&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W123,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W123&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W123,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X123&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X123,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X123&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X123,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z123">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A123)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A123)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A123)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A123)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A123)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A123)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A123)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A123)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A123)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A123)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE123" t="str">
@@ -39841,7 +40156,7 @@
         <v>0.5</v>
       </c>
       <c r="R124">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A124&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q124)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A124&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q124)</f>
         <v>0.5</v>
       </c>
       <c r="S124">
@@ -39869,11 +40184,11 @@
         <v>High Mobility</v>
       </c>
       <c r="Y124">
-        <f>IF($A$1="",0,MAX(IF(W124&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W124,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W124&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W124,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X124&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X124,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X124&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X124,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W124&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W124,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W124&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W124,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X124&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X124,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X124&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X124,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z124">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A124)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A124)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A124)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A124)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A124)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A124)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A124)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A124)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A124)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A124)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE124" t="str">
@@ -39959,7 +40274,7 @@
         <v>7</v>
       </c>
       <c r="R125">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A125&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q125)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A125&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q125)</f>
         <v>7</v>
       </c>
       <c r="S125">
@@ -39987,11 +40302,11 @@
         <v>Hard CC</v>
       </c>
       <c r="Y125">
-        <f>IF($A$1="",0,MAX(IF(W125&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W125,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W125&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W125,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X125&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X125,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X125&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X125,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W125&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W125,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W125&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W125,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X125&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X125,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X125&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X125,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z125">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A125)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A125)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A125)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A125)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A125)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A125)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A125)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A125)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A125)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A125)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE125" t="str">
@@ -40077,7 +40392,7 @@
         <v>4</v>
       </c>
       <c r="R126">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A126&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q126)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A126&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q126)</f>
         <v>4</v>
       </c>
       <c r="S126">
@@ -40105,11 +40420,11 @@
         <v>Poke</v>
       </c>
       <c r="Y126">
-        <f>IF($A$1="",0,MAX(IF(W126&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W126,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W126&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W126,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X126&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X126,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X126&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X126,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W126&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W126,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W126&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W126,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X126&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X126,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X126&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X126,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z126">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A126)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A126)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A126)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A126)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A126)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A126)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A126)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A126)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A126)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A126)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE126" t="str">
@@ -40195,7 +40510,7 @@
         <v>3.5</v>
       </c>
       <c r="R127">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A127&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q127)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A127&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q127)</f>
         <v>3.5</v>
       </c>
       <c r="S127">
@@ -40223,11 +40538,11 @@
         <v>Damage Reduction</v>
       </c>
       <c r="Y127">
-        <f>IF($A$1="",0,MAX(IF(W127&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W127,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W127&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W127,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X127&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X127,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X127&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X127,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W127&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W127,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W127&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W127,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X127&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X127,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X127&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X127,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z127">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A127)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A127)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A127)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A127)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A127)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A127)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A127)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A127)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A127)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A127)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE127" t="str">
@@ -40313,7 +40628,7 @@
         <v>1.5</v>
       </c>
       <c r="R128">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A128&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q128)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A128&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q128)</f>
         <v>1.5</v>
       </c>
       <c r="S128">
@@ -40341,11 +40656,11 @@
         <v>Sustain</v>
       </c>
       <c r="Y128">
-        <f>IF($A$1="",0,MAX(IF(W128&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W128,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W128&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W128,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X128&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X128,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X128&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X128,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W128&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W128,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W128&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W128,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X128&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X128,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X128&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X128,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z128">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A128)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A128)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A128)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A128)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A128)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A128)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A128)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A128)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A128)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A128)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE128" t="str">
@@ -40431,7 +40746,7 @@
         <v>4</v>
       </c>
       <c r="R129">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A129&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q129)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A129&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q129)</f>
         <v>4</v>
       </c>
       <c r="S129">
@@ -40459,11 +40774,11 @@
         <v>Healing</v>
       </c>
       <c r="Y129">
-        <f>IF($A$1="",0,MAX(IF(W129&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W129,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W129&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W129,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X129&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X129,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X129&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X129,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W129&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W129,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W129&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W129,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X129&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X129,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X129&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X129,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>5</v>
       </c>
       <c r="Z129">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A129)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A129)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A129)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A129)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A129)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A129)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A129)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A129)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A129)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A129)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE129" t="str">
@@ -40549,7 +40864,7 @@
         <v>2.5</v>
       </c>
       <c r="R130">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A130&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q130)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A130&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q130)</f>
         <v>2.5</v>
       </c>
       <c r="S130">
@@ -40577,11 +40892,11 @@
         <v>AoE Damage</v>
       </c>
       <c r="Y130">
-        <f>IF($A$1="",0,MAX(IF(W130&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W130,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W130&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W130,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X130&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X130,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X130&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X130,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W130&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W130,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W130&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W130,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X130&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X130,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X130&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X130,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z130">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A130)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A130)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A130)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A130)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A130)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A130)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A130)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A130)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A130)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A130)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE130" t="str">
@@ -40667,7 +40982,7 @@
         <v>-2</v>
       </c>
       <c r="R131">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A131&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q131)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A131&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q131)</f>
         <v>-2</v>
       </c>
       <c r="S131">
@@ -40695,11 +41010,11 @@
         <v>Poke</v>
       </c>
       <c r="Y131">
-        <f>IF($A$1="",0,MAX(IF(W131&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W131,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W131&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W131,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X131&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X131,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X131&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X131,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W131&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W131,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W131&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W131,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X131&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X131,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X131&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X131,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z131">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A131)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A131)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A131)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A131)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A131)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A131)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A131)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A131)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A131)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A131)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE131" t="str">
@@ -40785,7 +41100,7 @@
         <v>1.5</v>
       </c>
       <c r="R132">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A132&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q132)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A132&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q132)</f>
         <v>1.5</v>
       </c>
       <c r="S132">
@@ -40813,11 +41128,11 @@
         <v>Dash/Blink</v>
       </c>
       <c r="Y132">
-        <f>IF($A$1="",0,MAX(IF(W132&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W132,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W132&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W132,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X132&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X132,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X132&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X132,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W132&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W132,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W132&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W132,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X132&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X132,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X132&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X132,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z132">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A132)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A132)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A132)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A132)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A132)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A132)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A132)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A132)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A132)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A132)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE132" t="str">
@@ -40903,7 +41218,7 @@
         <v>-5.5</v>
       </c>
       <c r="R133">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A133&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q133)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A133&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q133)</f>
         <v>-5.5</v>
       </c>
       <c r="S133">
@@ -40931,11 +41246,11 @@
         <v>Hard CC</v>
       </c>
       <c r="Y133">
-        <f>IF($A$1="",0,MAX(IF(W133&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W133,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W133&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W133,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X133&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X133,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X133&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X133,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W133&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W133,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W133&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W133,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X133&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X133,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X133&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X133,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z133">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A133)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A133)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A133)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A133)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A133)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A133)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A133)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A133)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A133)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A133)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE133" t="str">
@@ -41021,7 +41336,7 @@
         <v>-6</v>
       </c>
       <c r="R134">
-        <f>IFERROR(INDEX('Data-Input'!$C$190:$C$1189,MATCH(A134&amp;"|"&amp;$A$1,'Data-Input'!$E$190:$E$1189,0)),Q134)</f>
+        <f>IFERROR(INDEX('Data-Input'!$C$191:$C$1190,MATCH(A134&amp;"|"&amp;$A$1,'Data-Input'!$E$191:$E$1190,0)),Q134)</f>
         <v>-6</v>
       </c>
       <c r="S134">
@@ -41049,11 +41364,11 @@
         <v>High Mobility</v>
       </c>
       <c r="Y134">
-        <f>IF($A$1="",0,MAX(IF(W134&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W134,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(W134&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(W134,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(X134&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X134,'Data-Input'!$A$164:$A$185,0),MATCH($K$1,'Data-Input'!$B$163:$W$163,0)),0),0),IF(AND(X134&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$164:$W$185,MATCH(X134,'Data-Input'!$A$164:$A$185,0),MATCH($L$1,'Data-Input'!$B$163:$W$163,0)),0),0))*$M$1)</f>
+        <f>IF($A$1="",0,MAX(IF(W134&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W134,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(W134&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(W134,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(X134&lt;&gt;"",IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X134,'Data-Input'!$A$165:$A$186,0),MATCH($K$1,'Data-Input'!$B$164:$W$164,0)),0),0),IF(AND(X134&lt;&gt;"",$L$1&lt;&gt;""),IFERROR(INDEX('Data-Input'!$B$165:$W$186,MATCH(X134,'Data-Input'!$A$165:$A$186,0),MATCH($L$1,'Data-Input'!$B$164:$W$164,0)),0),0))*$M$1)</f>
         <v>0</v>
       </c>
       <c r="Z134">
-        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$128=A134)*('Data-Input'!$B$29:$B$128="Tag")*((('Data-Input'!$C$29:$C$128=$K$1)+('Data-Input'!$C$29:$C$128=$L$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A134)*('Data-Input'!$B$29:$B$128="Hero")*('Data-Input'!$C$29:$C$128=$A$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A134)*('Data-Input'!$B$29:$B$128="Role")*((('Data-Input'!$C$29:$C$128=$B$1)+('Data-Input'!$C$29:$C$128=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A134)*('Data-Input'!$B$29:$B$128="DamageType")*('Data-Input'!$C$29:$C$128=$E$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128))+SUMPRODUCT(('Data-Input'!$A$29:$A$128=A134)*('Data-Input'!$B$29:$B$128="Resource")*('Data-Input'!$C$29:$C$128=$AB$1)*('Data-Input'!$D$29:$D$128-'Data-Input'!$E$29:$E$128)))</f>
+        <f>IF($A$1="",0,SUMPRODUCT(('Data-Input'!$A$29:$A$129=A134)*('Data-Input'!$B$29:$B$129="Tag")*((('Data-Input'!$C$29:$C$129=$K$1)+('Data-Input'!$C$29:$C$129=$L$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A134)*('Data-Input'!$B$29:$B$129="Hero")*('Data-Input'!$C$29:$C$129=$A$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A134)*('Data-Input'!$B$29:$B$129="Role")*((('Data-Input'!$C$29:$C$129=$B$1)+('Data-Input'!$C$29:$C$129=$AH$1))&gt;0)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A134)*('Data-Input'!$B$29:$B$129="DamageType")*('Data-Input'!$C$29:$C$129=$E$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129))+SUMPRODUCT(('Data-Input'!$A$29:$A$129=A134)*('Data-Input'!$B$29:$B$129="Resource")*('Data-Input'!$C$29:$C$129=$AB$1)*('Data-Input'!$D$29:$D$129-'Data-Input'!$E$29:$E$129)))</f>
         <v>0</v>
       </c>
       <c r="AE134" t="str">

--- a/mobile_legends_heroes_updated.xlsx
+++ b/mobile_legends_heroes_updated.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CounterCalculator" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookup" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LookupCalc" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synergy" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -159,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -191,6 +192,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S134"/>
+  <dimension ref="A1:T134"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="5"/>
@@ -581,6 +585,11 @@
           <t>has_true_damage</t>
         </is>
       </c>
+      <c r="T1" s="23" t="inlineStr">
+        <is>
+          <t>teamfight_contribution</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
@@ -658,6 +667,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T2" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -740,6 +752,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="T3" s="23" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -822,6 +837,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T4" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -904,6 +922,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T5" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -981,6 +1002,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T6" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -1058,6 +1082,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T7" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -1140,6 +1167,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="T8" s="23" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
@@ -1217,6 +1247,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T9" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -1294,6 +1327,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T10" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -1371,6 +1407,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T11" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
@@ -1458,6 +1497,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T12" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -1535,6 +1577,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T13" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -1612,6 +1657,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T14" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -1689,6 +1737,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T15" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
@@ -1766,6 +1817,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T16" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
@@ -1848,6 +1902,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T17" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
@@ -1925,6 +1982,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T18" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
@@ -2002,6 +2062,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T19" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
@@ -2084,6 +2147,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T20" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -2166,6 +2232,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T21" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
@@ -2243,6 +2312,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T22" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -2325,6 +2397,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T23" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
@@ -2402,6 +2477,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T24" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
@@ -2484,6 +2562,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T25" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
@@ -2561,6 +2642,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T26" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
@@ -2643,6 +2727,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T27" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
@@ -2725,6 +2812,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T28" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
@@ -2807,6 +2897,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="T29" s="23" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
@@ -2884,6 +2977,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T30" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
@@ -2966,6 +3062,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T31" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
@@ -3043,6 +3142,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T32" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
@@ -3125,6 +3227,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T33" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
@@ -3202,6 +3307,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T34" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
@@ -3279,6 +3387,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T35" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
@@ -3366,6 +3477,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T36" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
@@ -3443,6 +3557,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T37" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
@@ -3520,6 +3637,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T38" s="23" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
@@ -3597,6 +3717,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T39" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
@@ -3679,6 +3802,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T40" s="23" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
@@ -3756,6 +3882,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="T41" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
@@ -3843,6 +3972,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T42" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
@@ -3930,6 +4062,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T43" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
@@ -4007,6 +4142,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T44" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
@@ -4089,6 +4227,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T45" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
@@ -4166,6 +4307,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="T46" s="23" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
@@ -4243,6 +4387,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T47" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
@@ -4320,6 +4467,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T48" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
@@ -4397,6 +4547,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T49" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
@@ -4474,6 +4627,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T50" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
@@ -4551,6 +4707,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T51" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
@@ -4633,6 +4792,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T52" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
@@ -4710,6 +4872,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T53" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
@@ -4792,6 +4957,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="T54" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
@@ -4874,6 +5042,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T55" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
@@ -4951,6 +5122,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T56" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
@@ -5033,6 +5207,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T57" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
@@ -5110,6 +5287,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T58" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
@@ -5192,6 +5372,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T59" s="23" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
@@ -5269,6 +5452,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T60" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
@@ -5346,6 +5532,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T61" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
@@ -5423,6 +5612,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T62" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
@@ -5505,6 +5697,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T63" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
@@ -5592,6 +5787,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T64" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
@@ -5669,6 +5867,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T65" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
@@ -5746,6 +5947,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T66" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
@@ -5823,6 +6027,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T67" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
@@ -5900,6 +6107,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T68" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
@@ -5977,6 +6187,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="T69" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
@@ -6054,6 +6267,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T70" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
@@ -6131,6 +6347,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T71" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
@@ -6218,6 +6437,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T72" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
@@ -6295,6 +6517,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="T73" s="23" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
@@ -6377,6 +6602,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T74" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
@@ -6459,6 +6687,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T75" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
@@ -6541,6 +6772,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T76" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
@@ -6628,6 +6862,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T77" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
@@ -6710,6 +6947,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T78" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
@@ -6787,6 +7027,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T79" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
@@ -6864,6 +7107,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T80" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
@@ -6941,6 +7187,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T81" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
@@ -7018,6 +7267,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T82" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
@@ -7100,6 +7352,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="T83" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
@@ -7177,6 +7432,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="T84" s="23" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
@@ -7254,6 +7512,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T85" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
@@ -7336,6 +7597,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="T86" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
@@ -7413,6 +7677,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T87" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
@@ -7495,6 +7762,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T88" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
@@ -7577,6 +7847,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T89" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
@@ -7654,6 +7927,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T90" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
@@ -7731,6 +8007,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T91" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
@@ -7808,6 +8087,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T92" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
@@ -7890,6 +8172,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T93" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
@@ -7967,6 +8252,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T94" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
@@ -8049,6 +8337,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T95" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
@@ -8126,6 +8417,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T96" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
@@ -8203,6 +8497,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T97" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
@@ -8285,6 +8582,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T98" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
@@ -8367,6 +8667,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T99" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
@@ -8449,6 +8752,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T100" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
@@ -8526,6 +8832,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T101" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
@@ -8603,6 +8912,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T102" s="23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
@@ -8685,6 +8997,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T103" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
@@ -8767,6 +9082,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T104" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
@@ -8849,6 +9167,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T105" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
@@ -8926,6 +9247,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T106" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
@@ -9003,6 +9327,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T107" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
@@ -9080,6 +9407,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T108" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
@@ -9157,6 +9487,9 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="T109" s="23" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
@@ -9234,6 +9567,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T110" s="23" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
@@ -9311,6 +9647,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T111" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
@@ -9398,6 +9737,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T112" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
@@ -9475,6 +9817,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T113" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
@@ -9562,6 +9907,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T114" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
@@ -9639,6 +9987,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T115" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
@@ -9716,6 +10067,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T116" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
@@ -9803,6 +10157,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T117" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
@@ -9885,6 +10242,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T118" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
@@ -9962,6 +10322,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T119" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
@@ -10039,6 +10402,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T120" s="23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
@@ -10121,6 +10487,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T121" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
@@ -10198,6 +10567,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T122" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
@@ -10275,6 +10647,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T123" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
@@ -10352,6 +10727,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T124" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
@@ -10434,6 +10812,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T125" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
@@ -10511,6 +10892,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T126" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
@@ -10593,6 +10977,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T127" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
@@ -10675,6 +11062,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T128" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
@@ -10757,6 +11147,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T129" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
@@ -10834,6 +11227,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T130" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
@@ -10911,6 +11307,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T131" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
@@ -10993,6 +11392,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T132" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
@@ -11070,6 +11472,9 @@
           <t>No</t>
         </is>
       </c>
+      <c r="T133" s="23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
@@ -11146,6 +11551,9 @@
         <is>
           <t>No</t>
         </is>
+      </c>
+      <c r="T134" s="23" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -44088,4 +44496,806 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>hero_a</t>
+        </is>
+      </c>
+      <c r="B1" s="22" t="inlineStr">
+        <is>
+          <t>hero_b</t>
+        </is>
+      </c>
+      <c r="C1" s="22" t="inlineStr">
+        <is>
+          <t>synergy</t>
+        </is>
+      </c>
+      <c r="D1" s="22" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>Johnson</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>Odette</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>Classic drive-by ult combo — Odette rides Johnson for a mobile nuke</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>Faramis</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Pharsa</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>Resurrect lets Pharsa play hyper-aggressive, revive + full AoE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>Faramis</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Yve</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>Same as Pharsa — Yve zone control with revive safety net</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>Tigreal</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Pharsa</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>Tigreal setup into Pharsa raining death = teamfight wipe</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Pharsa</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>Fatal Links into Pharsa meteors = guaranteed full combo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Odette</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>Fatal Links + Blue Nova = multi-man stun into full channel</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Tigreal</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Odette</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>Implosion setup into Odette ult</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>Lolita</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>Shield blocks enemy projectiles while Claude shreds</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>Lolita</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Chang'e</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>Same mechanic — Chang'e poke/ult behind Lolita shield</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>Mathilda</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Lancelot</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>Guiding Wind lets Lancelot dive deeper + reset more safely</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Mathilda</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Hayabusa</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>Same — Mathilda ult follows Haya shadow for chain dives</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Mathilda</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Ling</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>Ling + Mathilda = unmatched backline access</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Mathilda</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>Alucard</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>Dive + lifesteal synergy, Alucard gets in and stays in</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>Kaja</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Hayabusa</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>Kaja suppress + Hayabusa full Ougi = guaranteed kill</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>Kaja</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>Aldous</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>Kaja suppress + Aldous ult = uncontested punch</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Kaja</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Helcurt</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>Suppress + silence = no escape, no counterplay</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>Chou</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Lancelot</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>Chou setup knock-up into Lancelot reset chain</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>Esmeralda</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>Angela link + shield lets Esme dive without dying</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Thamuz</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>Thamuz becomes unkillable with Angela rot, wins manfights</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Uranus</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>Already durable Uranus becomes immortal with Angela</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>Angela</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Terizla</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>Terizla slow + Angela speed = sticky frontliner</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>Estes</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Belerick</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>Estes chain heal + Belerick taunt = never-dying frontline</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>Estes</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>Uranus</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>Same — Uranus with Estes heals is nearly impossible to burst</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>Estes</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Esmeralda</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>Esme + Estes = infinite shield rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>Franco</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Aldous</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>Hook + Aldous ult = guaranteed kill on any hooked target</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>Franco</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Selena</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>Hook + Selena arrow = infinite chain CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>Selena</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Helcurt</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>Selena stun + Helcurt silence = no escape window</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>Selena</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Hayabusa</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>Selena arrow into Haya Ougi = dead before stun ends</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>Helcurt</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>Global silence prevents all counterplay vs Atlas engage</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>Helcurt</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Tigreal</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>Same — silence + Implosion = no skills to escape</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>Helcurt</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>Pharsa</t>
+        </is>
+      </c>
+      <c r="C32" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>Silence into Pharsa rain = no skills to dodge</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>Helcurt</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Kaja</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>Silence + suppress = absolute lockdown, no counterplay</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>Johnson</t>
+        </is>
+      </c>
+      <c r="B34" s="23" t="inlineStr">
+        <is>
+          <t>Faramis</t>
+        </is>
+      </c>
+      <c r="C34" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>Taxi(Johnson) + revive(Faramis) = supreme rotation threat</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>Rafaela</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Aldous</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>Rafaela speed boost + Aldous ult = global pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>Rafaela</t>
+        </is>
+      </c>
+      <c r="B36" s="23" t="inlineStr">
+        <is>
+          <t>Lunox</t>
+        </is>
+      </c>
+      <c r="C36" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>Speed + sustain helps Lunox position for chaos ult</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>Diggie</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>Diggie egg + purify saves Claude from dive attempts</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>Diggie</t>
+        </is>
+      </c>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>Beatrix</t>
+        </is>
+      </c>
+      <c r="C38" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>Same — Diggie disengages divers for Beatrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>Diggie</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Lunox</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>Diggie ult lets Lunox play aggressive, immune to CC</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/mobile_legends_heroes_updated.xlsx
+++ b/mobile_legends_heroes_updated.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -115,6 +115,11 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00CC4444"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -160,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -196,6 +201,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11571,7 +11577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1190"/>
+  <dimension ref="A1:W1191"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12180,32 +12186,12 @@
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Khufra</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Dash/Blink</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>Bouncing Ball cancels dashes/blinks mid-animation, hard-locking mobility divers.</t>
-        </is>
-      </c>
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="3" t="n"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Energy</t>
@@ -12213,32 +12199,12 @@
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Khufra</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>High Mobility</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>-13</v>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Sturdiness plus Charging Roar punish sustained-mobility assassins.</t>
-        </is>
-      </c>
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="3" t="n"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>None</t>
@@ -27435,6 +27401,13 @@
       <c r="E1190">
         <f>A1190&amp;"|"&amp;B1190</f>
         <v/>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="25" t="inlineStr">
+        <is>
+          <t>CONVENTION: Hard counter rules default to symmetric values (bonus_to_attacker = -penalty_to_defender). Asymmetric values are allowed when a specific matchup requires the attacker to benefit more (or less) than the defender is penalized, but this should be the exception, not the rule.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/mobile_legends_heroes_updated.xlsx
+++ b/mobile_legends_heroes_updated.xlsx
@@ -165,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,6 +202,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -44477,7 +44480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -44689,22 +44692,22 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>Mathilda</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>Lancelot</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="n">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Lolita</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Hanabi</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="D11" s="24" t="inlineStr">
-        <is>
-          <t>Guiding Wind lets Lancelot dive deeper + reset more safely</t>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>Lolita shield blocks projectiles while Hanabi bouncing attacks punish clumped enemies</t>
         </is>
       </c>
     </row>
@@ -44716,7 +44719,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>Hayabusa</t>
+          <t>Lancelot</t>
         </is>
       </c>
       <c r="C12" s="23" t="n">
@@ -44724,7 +44727,7 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>Same — Mathilda ult follows Haya shadow for chain dives</t>
+          <t>Guiding Wind lets Lancelot dive deeper + reset more safely</t>
         </is>
       </c>
     </row>
@@ -44736,7 +44739,7 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>Ling</t>
+          <t>Hayabusa</t>
         </is>
       </c>
       <c r="C13" s="23" t="n">
@@ -44744,7 +44747,7 @@
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>Ling + Mathilda = unmatched backline access</t>
+          <t>Same — Mathilda ult follows Haya shadow for chain dives</t>
         </is>
       </c>
     </row>
@@ -44756,35 +44759,35 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>Alucard</t>
+          <t>Ling</t>
         </is>
       </c>
       <c r="C14" s="23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>Dive + lifesteal synergy, Alucard gets in and stays in</t>
+          <t>Ling + Mathilda = unmatched backline access</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>Kaja</t>
+          <t>Mathilda</t>
         </is>
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>Hayabusa</t>
+          <t>Alucard</t>
         </is>
       </c>
       <c r="C15" s="23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>Kaja suppress + Hayabusa full Ougi = guaranteed kill</t>
+          <t>Dive + lifesteal synergy, Alucard gets in and stays in</t>
         </is>
       </c>
     </row>
@@ -44796,7 +44799,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Aldous</t>
+          <t>Hayabusa</t>
         </is>
       </c>
       <c r="C16" s="23" t="n">
@@ -44804,7 +44807,7 @@
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>Kaja suppress + Aldous ult = uncontested punch</t>
+          <t>Kaja suppress + Hayabusa full Ougi = guaranteed kill</t>
         </is>
       </c>
     </row>
@@ -44816,7 +44819,7 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>Helcurt</t>
+          <t>Aldous</t>
         </is>
       </c>
       <c r="C17" s="23" t="n">
@@ -44824,39 +44827,39 @@
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>Suppress + silence = no escape, no counterplay</t>
+          <t>Kaja suppress + Aldous ult = uncontested punch</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="23" t="inlineStr">
         <is>
-          <t>Chou</t>
+          <t>Kaja</t>
         </is>
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>Lancelot</t>
+          <t>Helcurt</t>
         </is>
       </c>
       <c r="C18" s="23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
-          <t>Chou setup knock-up into Lancelot reset chain</t>
+          <t>Suppress + silence = no escape, no counterplay</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>Angela</t>
+          <t>Chou</t>
         </is>
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>Esmeralda</t>
+          <t>Lancelot</t>
         </is>
       </c>
       <c r="C19" s="23" t="n">
@@ -44864,7 +44867,7 @@
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
-          <t>Angela link + shield lets Esme dive without dying</t>
+          <t>Chou setup knock-up into Lancelot reset chain</t>
         </is>
       </c>
     </row>
@@ -44876,15 +44879,15 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>Thamuz</t>
+          <t>Esmeralda</t>
         </is>
       </c>
       <c r="C20" s="23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="24" t="inlineStr">
         <is>
-          <t>Thamuz becomes unkillable with Angela rot, wins manfights</t>
+          <t>Angela link + shield lets Esme dive without dying</t>
         </is>
       </c>
     </row>
@@ -44896,15 +44899,15 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>Uranus</t>
+          <t>Thamuz</t>
         </is>
       </c>
       <c r="C21" s="23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D21" s="24" t="inlineStr">
         <is>
-          <t>Already durable Uranus becomes immortal with Angela</t>
+          <t>Thamuz becomes unkillable with Angela rot, wins manfights</t>
         </is>
       </c>
     </row>
@@ -44916,7 +44919,7 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>Terizla</t>
+          <t>Uranus</t>
         </is>
       </c>
       <c r="C22" s="23" t="n">
@@ -44924,19 +44927,19 @@
       </c>
       <c r="D22" s="24" t="inlineStr">
         <is>
-          <t>Terizla slow + Angela speed = sticky frontliner</t>
+          <t>Already durable Uranus becomes immortal with Angela</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
         <is>
-          <t>Estes</t>
+          <t>Angela</t>
         </is>
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>Belerick</t>
+          <t>Terizla</t>
         </is>
       </c>
       <c r="C23" s="23" t="n">
@@ -44944,7 +44947,7 @@
       </c>
       <c r="D23" s="24" t="inlineStr">
         <is>
-          <t>Estes chain heal + Belerick taunt = never-dying frontline</t>
+          <t>Terizla slow + Angela speed = sticky frontliner</t>
         </is>
       </c>
     </row>
@@ -44956,7 +44959,7 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>Uranus</t>
+          <t>Belerick</t>
         </is>
       </c>
       <c r="C24" s="23" t="n">
@@ -44964,7 +44967,7 @@
       </c>
       <c r="D24" s="24" t="inlineStr">
         <is>
-          <t>Same — Uranus with Estes heals is nearly impossible to burst</t>
+          <t>Estes chain heal + Belerick taunt = never-dying frontline</t>
         </is>
       </c>
     </row>
@@ -44976,7 +44979,7 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>Esmeralda</t>
+          <t>Uranus</t>
         </is>
       </c>
       <c r="C25" s="23" t="n">
@@ -44984,27 +44987,27 @@
       </c>
       <c r="D25" s="24" t="inlineStr">
         <is>
-          <t>Esme + Estes = infinite shield rotation</t>
+          <t>Same — Uranus with Estes heals is nearly impossible to burst</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>Franco</t>
+          <t>Estes</t>
         </is>
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Aldous</t>
+          <t>Esmeralda</t>
         </is>
       </c>
       <c r="C26" s="23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="24" t="inlineStr">
         <is>
-          <t>Hook + Aldous ult = guaranteed kill on any hooked target</t>
+          <t>Esme + Estes = infinite shield rotation</t>
         </is>
       </c>
     </row>
@@ -45016,7 +45019,7 @@
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>Selena</t>
+          <t>Aldous</t>
         </is>
       </c>
       <c r="C27" s="23" t="n">
@@ -45024,27 +45027,27 @@
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>Hook + Selena arrow = infinite chain CC</t>
+          <t>Hook + Aldous ult = guaranteed kill on any hooked target</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="23" t="inlineStr">
         <is>
+          <t>Franco</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
           <t>Selena</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
-        <is>
-          <t>Helcurt</t>
-        </is>
-      </c>
       <c r="C28" s="23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D28" s="24" t="inlineStr">
         <is>
-          <t>Selena stun + Helcurt silence = no escape window</t>
+          <t>Hook + Selena arrow = infinite chain CC</t>
         </is>
       </c>
     </row>
@@ -45056,7 +45059,7 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>Hayabusa</t>
+          <t>Helcurt</t>
         </is>
       </c>
       <c r="C29" s="23" t="n">
@@ -45064,27 +45067,27 @@
       </c>
       <c r="D29" s="24" t="inlineStr">
         <is>
-          <t>Selena arrow into Haya Ougi = dead before stun ends</t>
+          <t>Selena stun + Helcurt silence = no escape window</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>Helcurt</t>
+          <t>Selena</t>
         </is>
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>Hayabusa</t>
         </is>
       </c>
       <c r="C30" s="23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" s="24" t="inlineStr">
         <is>
-          <t>Global silence prevents all counterplay vs Atlas engage</t>
+          <t>Selena arrow into Haya Ougi = dead before stun ends</t>
         </is>
       </c>
     </row>
@@ -45096,7 +45099,7 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>Tigreal</t>
+          <t>Atlas</t>
         </is>
       </c>
       <c r="C31" s="23" t="n">
@@ -45104,7 +45107,7 @@
       </c>
       <c r="D31" s="24" t="inlineStr">
         <is>
-          <t>Same — silence + Implosion = no skills to escape</t>
+          <t>Global silence prevents all counterplay vs Atlas engage</t>
         </is>
       </c>
     </row>
@@ -45116,7 +45119,7 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>Pharsa</t>
+          <t>Tigreal</t>
         </is>
       </c>
       <c r="C32" s="23" t="n">
@@ -45124,7 +45127,7 @@
       </c>
       <c r="D32" s="24" t="inlineStr">
         <is>
-          <t>Silence into Pharsa rain = no skills to dodge</t>
+          <t>Same — silence + Implosion = no skills to escape</t>
         </is>
       </c>
     </row>
@@ -45136,47 +45139,47 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>Kaja</t>
+          <t>Pharsa</t>
         </is>
       </c>
       <c r="C33" s="23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D33" s="24" t="inlineStr">
         <is>
-          <t>Silence + suppress = absolute lockdown, no counterplay</t>
+          <t>Silence into Pharsa rain = no skills to dodge</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="23" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Helcurt</t>
         </is>
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>Faramis</t>
+          <t>Kaja</t>
         </is>
       </c>
       <c r="C34" s="23" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D34" s="24" t="inlineStr">
         <is>
-          <t>Taxi(Johnson) + revive(Faramis) = supreme rotation threat</t>
+          <t>Silence + suppress = absolute lockdown, no counterplay</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>Rafaela</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>Aldous</t>
+          <t>Faramis</t>
         </is>
       </c>
       <c r="C35" s="23" t="n">
@@ -45184,7 +45187,7 @@
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>Rafaela speed boost + Aldous ult = global pressure</t>
+          <t>Taxi(Johnson) + revive(Faramis) = supreme rotation threat</t>
         </is>
       </c>
     </row>
@@ -45196,7 +45199,7 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Lunox</t>
+          <t>Aldous</t>
         </is>
       </c>
       <c r="C36" s="23" t="n">
@@ -45204,27 +45207,27 @@
       </c>
       <c r="D36" s="24" t="inlineStr">
         <is>
-          <t>Speed + sustain helps Lunox position for chaos ult</t>
+          <t>Rafaela speed boost + Aldous ult = global pressure</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>Diggie</t>
+          <t>Rafaela</t>
         </is>
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>Claude</t>
+          <t>Lunox</t>
         </is>
       </c>
       <c r="C37" s="23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>Diggie egg + purify saves Claude from dive attempts</t>
+          <t>Speed + sustain helps Lunox position for chaos ult</t>
         </is>
       </c>
     </row>
@@ -45236,7 +45239,7 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>Beatrix</t>
+          <t>Claude</t>
         </is>
       </c>
       <c r="C38" s="23" t="n">
@@ -45244,7 +45247,7 @@
       </c>
       <c r="D38" s="24" t="inlineStr">
         <is>
-          <t>Same — Diggie disengages divers for Beatrix</t>
+          <t>Diggie egg + purify saves Claude from dive attempts</t>
         </is>
       </c>
     </row>
@@ -45256,13 +45259,33 @@
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>Lunox</t>
+          <t>Beatrix</t>
         </is>
       </c>
       <c r="C39" s="23" t="n">
         <v>8</v>
       </c>
       <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>Same — Diggie disengages divers for Beatrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Diggie</t>
+        </is>
+      </c>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>Lunox</t>
+        </is>
+      </c>
+      <c r="C40" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
         <is>
           <t>Diggie ult lets Lunox play aggressive, immune to CC</t>
         </is>

--- a/mobile_legends_heroes_updated.xlsx
+++ b/mobile_legends_heroes_updated.xlsx
@@ -44537,7 +44537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="21" min="1" max="2"/>
@@ -45347,6 +45347,66 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Bruno</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Diggie</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Diggie egg/shield protects Bruno from dive; Bruno burst punishes enemies who target Diggie</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Ixia</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Diggie</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Diggie egg shields Ixia from burst; Ixia AoE punishes enemies diving for Diggie</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Johnson</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Arlott</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>12</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Johnson Drive rides Arlott for mobile ganks; Arlott blink extends Johnson Drive range</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
